--- a/e1_urls.xlsx
+++ b/e1_urls.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="1081">
   <si>
     <t>x</t>
   </si>
@@ -1265,36 +1265,408 @@
     <t>416</t>
   </si>
   <si>
+    <t>417</t>
+  </si>
+  <si>
+    <t>418</t>
+  </si>
+  <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>420</t>
+  </si>
+  <si>
+    <t>421</t>
+  </si>
+  <si>
+    <t>422</t>
+  </si>
+  <si>
+    <t>423</t>
+  </si>
+  <si>
+    <t>424</t>
+  </si>
+  <si>
+    <t>425</t>
+  </si>
+  <si>
+    <t>426</t>
+  </si>
+  <si>
+    <t>427</t>
+  </si>
+  <si>
+    <t>428</t>
+  </si>
+  <si>
+    <t>429</t>
+  </si>
+  <si>
+    <t>430</t>
+  </si>
+  <si>
+    <t>431</t>
+  </si>
+  <si>
+    <t>432</t>
+  </si>
+  <si>
+    <t>433</t>
+  </si>
+  <si>
+    <t>434</t>
+  </si>
+  <si>
+    <t>435</t>
+  </si>
+  <si>
+    <t>436</t>
+  </si>
+  <si>
+    <t>437</t>
+  </si>
+  <si>
+    <t>438</t>
+  </si>
+  <si>
+    <t>439</t>
+  </si>
+  <si>
+    <t>440</t>
+  </si>
+  <si>
+    <t>441</t>
+  </si>
+  <si>
+    <t>442</t>
+  </si>
+  <si>
+    <t>443</t>
+  </si>
+  <si>
+    <t>444</t>
+  </si>
+  <si>
+    <t>445</t>
+  </si>
+  <si>
+    <t>446</t>
+  </si>
+  <si>
+    <t>447</t>
+  </si>
+  <si>
+    <t>448</t>
+  </si>
+  <si>
+    <t>449</t>
+  </si>
+  <si>
+    <t>450</t>
+  </si>
+  <si>
+    <t>451</t>
+  </si>
+  <si>
+    <t>452</t>
+  </si>
+  <si>
+    <t>453</t>
+  </si>
+  <si>
+    <t>454</t>
+  </si>
+  <si>
+    <t>455</t>
+  </si>
+  <si>
+    <t>456</t>
+  </si>
+  <si>
+    <t>457</t>
+  </si>
+  <si>
+    <t>458</t>
+  </si>
+  <si>
+    <t>459</t>
+  </si>
+  <si>
+    <t>460</t>
+  </si>
+  <si>
+    <t>461</t>
+  </si>
+  <si>
+    <t>462</t>
+  </si>
+  <si>
+    <t>463</t>
+  </si>
+  <si>
+    <t>464</t>
+  </si>
+  <si>
+    <t>465</t>
+  </si>
+  <si>
+    <t>466</t>
+  </si>
+  <si>
+    <t>467</t>
+  </si>
+  <si>
+    <t>468</t>
+  </si>
+  <si>
+    <t>469</t>
+  </si>
+  <si>
+    <t>470</t>
+  </si>
+  <si>
+    <t>471</t>
+  </si>
+  <si>
+    <t>472</t>
+  </si>
+  <si>
+    <t>473</t>
+  </si>
+  <si>
+    <t>474</t>
+  </si>
+  <si>
+    <t>475</t>
+  </si>
+  <si>
+    <t>476</t>
+  </si>
+  <si>
+    <t>477</t>
+  </si>
+  <si>
+    <t>478</t>
+  </si>
+  <si>
+    <t>479</t>
+  </si>
+  <si>
+    <t>480</t>
+  </si>
+  <si>
+    <t>481</t>
+  </si>
+  <si>
+    <t>482</t>
+  </si>
+  <si>
+    <t>483</t>
+  </si>
+  <si>
+    <t>484</t>
+  </si>
+  <si>
+    <t>485</t>
+  </si>
+  <si>
+    <t>486</t>
+  </si>
+  <si>
+    <t>487</t>
+  </si>
+  <si>
+    <t>488</t>
+  </si>
+  <si>
+    <t>489</t>
+  </si>
+  <si>
+    <t>490</t>
+  </si>
+  <si>
+    <t>491</t>
+  </si>
+  <si>
+    <t>492</t>
+  </si>
+  <si>
+    <t>493</t>
+  </si>
+  <si>
+    <t>494</t>
+  </si>
+  <si>
+    <t>495</t>
+  </si>
+  <si>
+    <t>496</t>
+  </si>
+  <si>
+    <t>497</t>
+  </si>
+  <si>
+    <t>498</t>
+  </si>
+  <si>
+    <t>499</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>501</t>
+  </si>
+  <si>
+    <t>502</t>
+  </si>
+  <si>
+    <t>503</t>
+  </si>
+  <si>
+    <t>504</t>
+  </si>
+  <si>
+    <t>505</t>
+  </si>
+  <si>
+    <t>506</t>
+  </si>
+  <si>
+    <t>507</t>
+  </si>
+  <si>
+    <t>508</t>
+  </si>
+  <si>
+    <t>509</t>
+  </si>
+  <si>
+    <t>510</t>
+  </si>
+  <si>
+    <t>511</t>
+  </si>
+  <si>
+    <t>512</t>
+  </si>
+  <si>
+    <t>513</t>
+  </si>
+  <si>
+    <t>514</t>
+  </si>
+  <si>
+    <t>515</t>
+  </si>
+  <si>
+    <t>516</t>
+  </si>
+  <si>
+    <t>517</t>
+  </si>
+  <si>
+    <t>518</t>
+  </si>
+  <si>
+    <t>519</t>
+  </si>
+  <si>
+    <t>520</t>
+  </si>
+  <si>
+    <t>521</t>
+  </si>
+  <si>
+    <t>522</t>
+  </si>
+  <si>
+    <t>523</t>
+  </si>
+  <si>
+    <t>524</t>
+  </si>
+  <si>
+    <t>525</t>
+  </si>
+  <si>
+    <t>526</t>
+  </si>
+  <si>
+    <t>527</t>
+  </si>
+  <si>
+    <t>528</t>
+  </si>
+  <si>
+    <t>529</t>
+  </si>
+  <si>
+    <t>530</t>
+  </si>
+  <si>
+    <t>531</t>
+  </si>
+  <si>
+    <t>532</t>
+  </si>
+  <si>
+    <t>533</t>
+  </si>
+  <si>
+    <t>534</t>
+  </si>
+  <si>
+    <t>535</t>
+  </si>
+  <si>
+    <t>536</t>
+  </si>
+  <si>
+    <t>537</t>
+  </si>
+  <si>
+    <t>538</t>
+  </si>
+  <si>
+    <t>539</t>
+  </si>
+  <si>
+    <t>540</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/1ae41d3c/Blackburn-Rovers-Derby-County-August-9-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/8ef33ae3/Preston-North-End-Sheffield-United-August-9-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/537561a8/Millwall-Watford-August-10-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9e3914bb/Cardiff-City-Sunderland-August-10-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ffa37749/Queens-Park-Rangers-West-Bromwich-Albion-August-10-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/342cfc84/Middlesbrough-Swansea-City-August-10-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3ee7f7ab/Hull-City-Bristol-City-August-10-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0ffd5479/Oxford-United-Norwich-City-August-10-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/342cfc84/Middlesbrough-Swansea-City-August-10-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/3ee7f7ab/Hull-City-Bristol-City-August-10-2024-Championship</t>
+    <t>https://fbref.com/en/matches/fc3ff616/Leeds-United-Portsmouth-August-10-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/47f3a55d/Stoke-City-Coventry-City-August-10-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/537561a8/Millwall-Watford-August-10-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/9e3914bb/Cardiff-City-Sunderland-August-10-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/fc3ff616/Leeds-United-Portsmouth-August-10-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ffa37749/Queens-Park-Rangers-West-Bromwich-Albion-August-10-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/7a780f54/Sheffield-Wednesday-Plymouth-Argyle-August-11-2024-Championship</t>
   </si>
   <si>
@@ -1304,72 +1676,72 @@
     <t>https://fbref.com/en/matches/e2a0f634/Coventry-City-Oxford-United-August-16-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/cc91bd09/Portsmouth-Luton-Town-August-17-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/6cc636f7/West-Bromwich-Albion-Leeds-United-August-17-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/7b5e3cb2/Derby-County-Middlesbrough-August-17-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/cc91bd09/Portsmouth-Luton-Town-August-17-2024-Championship</t>
+    <t>https://fbref.com/en/matches/d7ca5cbb/Bristol-City-Millwall-August-17-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b84fdcb5/Swansea-City-Preston-North-End-August-17-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f207fdeb/Burnley-Cardiff-City-August-17-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/80b3e0c0/Plymouth-Argyle-Hull-City-August-17-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6abd6f80/Norwich-City-Blackburn-Rovers-August-17-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/4d1d8962/Sheffield-United-Queens-Park-Rangers-August-17-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/6abd6f80/Norwich-City-Blackburn-Rovers-August-17-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/6e180658/Watford-Stoke-City-August-17-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/80b3e0c0/Plymouth-Argyle-Hull-City-August-17-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/b84fdcb5/Swansea-City-Preston-North-End-August-17-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d7ca5cbb/Bristol-City-Millwall-August-17-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/f207fdeb/Burnley-Cardiff-City-August-17-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/ab1574d3/Sunderland-Sheffield-Wednesday-August-18-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/ced9ecd0/Sheffield-Wednesday-Leeds-United-August-23-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/56b95bb5/Queens-Park-Rangers-Plymouth-Argyle-August-24-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/958fdf9f/Hull-City-Millwall-August-24-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/499a9d69/Bristol-City-Coventry-City-August-24-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/56b95bb5/Queens-Park-Rangers-Plymouth-Argyle-August-24-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/958fdf9f/Hull-City-Millwall-August-24-2024-Championship</t>
+    <t>https://fbref.com/en/matches/2375d0ce/Sunderland-Burnley-August-24-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9aef1d9c/Preston-North-End-Luton-Town-August-24-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4b94620e/Watford-Derby-County-August-24-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d548e35e/Blackburn-Rovers-Oxford-United-August-24-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/da9feef3/Stoke-City-West-Bromwich-Albion-August-24-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/202967ff/Middlesbrough-Portsmouth-August-24-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/008769e1/Norwich-City-Sheffield-United-August-24-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/202967ff/Middlesbrough-Portsmouth-August-24-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/2375d0ce/Sunderland-Burnley-August-24-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/4b94620e/Watford-Derby-County-August-24-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/9aef1d9c/Preston-North-End-Luton-Town-August-24-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d548e35e/Blackburn-Rovers-Oxford-United-August-24-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/da9feef3/Stoke-City-West-Bromwich-Albion-August-24-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/112ed598/Swansea-City-Cardiff-City-August-25-2024-Championship</t>
   </si>
   <si>
@@ -1385,49 +1757,52 @@
     <t>https://fbref.com/en/matches/a2eaf014/Coventry-City-Norwich-City-August-31-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/26ebbffe/Portsmouth-Sunderland-August-31-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fbaa8c37/Derby-County-Bristol-City-August-31-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/507f8537/Leeds-United-Hull-City-August-31-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/10cf5da6/Oxford-United-Preston-North-End-August-31-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/26ebbffe/Portsmouth-Sunderland-August-31-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/3d1defc6/West-Bromwich-Albion-Swansea-City-August-31-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/507f8537/Leeds-United-Hull-City-August-31-2024-Championship</t>
+    <t>https://fbref.com/en/matches/f7aeb7f3/Millwall-Sheffield-Wednesday-August-31-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/9be32a93/Plymouth-Argyle-Stoke-City-August-31-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f7aeb7f3/Millwall-Sheffield-Wednesday-August-31-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/fbaa8c37/Derby-County-Bristol-City-August-31-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/080b0dd7/Sheffield-United-Watford-September-1-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/6cfbf05a/Hull-City-Sheffield-United-September-13-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f25562c7/Oxford-United-Stoke-City-September-14-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0af79e36/Leeds-United-Burnley-September-14-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/d7224f0c/Millwall-Luton-Town-September-14-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f25562c7/Oxford-United-Stoke-City-September-14-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/3faa8e14/Swansea-City-Norwich-City-September-14-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/6c3cd68e/Derby-County-Cardiff-City-September-14-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/665bf0d4/Sheffield-Wednesday-Queens-Park-Rangers-September-14-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/6c3cd68e/Derby-County-Cardiff-City-September-14-2024-Championship</t>
+    <t>https://fbref.com/en/matches/ee019e58/Blackburn-Rovers-Bristol-City-September-14-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/a8188355/Watford-Coventry-City-September-14-2024-Championship</t>
@@ -1439,117 +1814,114 @@
     <t>https://fbref.com/en/matches/d2fd59c2/Middlesbrough-Preston-North-End-September-14-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/ee019e58/Blackburn-Rovers-Bristol-City-September-14-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/068be4f0/Portsmouth-West-Bromwich-Albion-September-15-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/f54132df/Stoke-City-Hull-City-September-20-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/7a241470/Queens-Park-Rangers-Millwall-September-21-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/713c8ff3/Norwich-City-Watford-September-21-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/084412ff/Sunderland-Middlesbrough-September-21-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/713c8ff3/Norwich-City-Watford-September-21-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/7a241470/Queens-Park-Rangers-Millwall-September-21-2024-Championship</t>
+    <t>https://fbref.com/en/matches/f75f5ece/West-Bromwich-Albion-Plymouth-Argyle-September-21-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5bb0782c/Luton-Town-Sheffield-Wednesday-September-21-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/27125a56/Bristol-City-Oxford-United-September-21-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/5bb0782c/Luton-Town-Sheffield-Wednesday-September-21-2024-Championship</t>
+    <t>https://fbref.com/en/matches/98d165eb/Sheffield-United-Derby-County-September-21-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a8b889f8/Burnley-Portsmouth-September-21-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9a8712b1/Coventry-City-Swansea-City-September-21-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/5cae7b0c/Cardiff-City-Leeds-United-September-21-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/98d165eb/Sheffield-United-Derby-County-September-21-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/9a8712b1/Coventry-City-Swansea-City-September-21-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/a8b889f8/Burnley-Portsmouth-September-21-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/f75f5ece/West-Bromwich-Albion-Plymouth-Argyle-September-21-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/8843bf80/Preston-North-End-Blackburn-Rovers-September-22-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/195bc214/Plymouth-Argyle-Luton-Town-September-27-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/901c1b82/Blackburn-Rovers-Queens-Park-Rangers-September-28-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0fd10cd6/Derby-County-Norwich-City-September-28-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/901c1b82/Blackburn-Rovers-Queens-Park-Rangers-September-28-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/bdad062b/Sheffield-Wednesday-West-Bromwich-Albion-September-28-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/5878c137/Leeds-United-Coventry-City-September-28-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4b6683f4/Watford-Sunderland-September-28-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/597b09d3/Millwall-Preston-North-End-September-28-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/1592fcfa/Middlesbrough-Stoke-City-September-28-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4b6683f4/Watford-Sunderland-September-28-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/5878c137/Leeds-United-Coventry-City-September-28-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/597b09d3/Millwall-Preston-North-End-September-28-2024-Championship</t>
+    <t>https://fbref.com/en/matches/75a9500f/Oxford-United-Burnley-September-28-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d8d01d42/Portsmouth-Sheffield-United-September-28-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/65f173f3/Hull-City-Cardiff-City-September-28-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/75a9500f/Oxford-United-Burnley-September-28-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d8d01d42/Portsmouth-Sheffield-United-September-28-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/6dc67563/Swansea-City-Bristol-City-September-29-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/15e46af7/Burnley-Plymouth-Argyle-October-1-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/59700177/Queens-Park-Rangers-Hull-City-October-1-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3a71cd8d/Sunderland-Derby-County-October-1-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ee04264d/Luton-Town-Oxford-United-October-1-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/05de17a9/Coventry-City-Blackburn-Rovers-October-1-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/15e46af7/Burnley-Plymouth-Argyle-October-1-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/3a71cd8d/Sunderland-Derby-County-October-1-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/59700177/Queens-Park-Rangers-Hull-City-October-1-2024-Championship</t>
+    <t>https://fbref.com/en/matches/c0cad892/Cardiff-City-Millwall-October-1-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/a67955c6/Norwich-City-Leeds-United-October-1-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/c0cad892/Cardiff-City-Millwall-October-1-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ee04264d/Luton-Town-Oxford-United-October-1-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/9afc6e0a/West-Bromwich-Albion-Middlesbrough-October-1-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/389c3828/Stoke-City-Portsmouth-October-2-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/84ae4d2d/Sheffield-United-Swansea-City-October-2-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4f8b9672/Preston-North-End-Watford-October-2-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/84ae4d2d/Sheffield-United-Swansea-City-October-2-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/81814d03/Bristol-City-Sheffield-Wednesday-October-2-2024-Championship</t>
   </si>
   <si>
@@ -1568,96 +1940,96 @@
     <t>https://fbref.com/en/matches/097ffcdc/Plymouth-Argyle-Blackburn-Rovers-October-5-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/ee17be41/Watford-Middlesbrough-October-5-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2b1d0c9c/Swansea-City-Stoke-City-October-5-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2ad57659/Sheffield-United-Luton-Town-October-5-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/2b1d0c9c/Swansea-City-Stoke-City-October-5-2024-Championship</t>
+    <t>https://fbref.com/en/matches/efe76973/Derby-County-Queens-Park-Rangers-October-5-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/cc42dab5/Coventry-City-Sheffield-Wednesday-October-5-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/c3ecef59/West-Bromwich-Albion-Millwall-October-5-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/cc42dab5/Coventry-City-Sheffield-Wednesday-October-5-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ee17be41/Watford-Middlesbrough-October-5-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/efe76973/Derby-County-Queens-Park-Rangers-October-5-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/c80518e2/Bristol-City-Cardiff-City-October-6-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/5f025982/Leeds-United-Sheffield-United-October-18-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/3c430fad/Oxford-United-West-Bromwich-Albion-October-19-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fdda86b0/Cardiff-City-Plymouth-Argyle-October-19-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/bdfb6a22/Luton-Town-Watford-October-19-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/078a8d15/Preston-North-End-Coventry-City-October-19-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3c430fad/Oxford-United-West-Bromwich-Albion-October-19-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/bdfb6a22/Luton-Town-Watford-October-19-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/fdda86b0/Cardiff-City-Plymouth-Argyle-October-19-2024-Championship</t>
+    <t>https://fbref.com/en/matches/63eae343/Millwall-Derby-County-October-19-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a3a93f3c/Queens-Park-Rangers-Portsmouth-October-19-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/66b6fdb2/Stoke-City-Norwich-City-October-19-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e0813f05/Middlesbrough-Bristol-City-October-19-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/71349150/Sheffield-Wednesday-Burnley-October-19-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/5c05d9e2/Blackburn-Rovers-Swansea-City-October-19-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/63eae343/Millwall-Derby-County-October-19-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/66b6fdb2/Stoke-City-Norwich-City-October-19-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/71349150/Sheffield-Wednesday-Burnley-October-19-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/a3a93f3c/Queens-Park-Rangers-Portsmouth-October-19-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e0813f05/Middlesbrough-Bristol-City-October-19-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/1663864f/Hull-City-Sunderland-October-20-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/fdd55c49/Stoke-City-Bristol-City-October-22-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e4b76915/Oxford-United-Derby-County-October-22-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2125576d/Leeds-United-Watford-October-22-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/4ffe09d7/Preston-North-End-Norwich-City-October-22-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/b54f51be/Cardiff-City-Portsmouth-October-22-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/a3c253b7/Sheffield-Wednesday-Swansea-City-October-22-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b54f51be/Cardiff-City-Portsmouth-October-22-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e4b76915/Oxford-United-Derby-County-October-22-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/fdd55c49/Stoke-City-Bristol-City-October-22-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/7a4d13fc/Queens-Park-Rangers-Coventry-City-October-22-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/36fd56f6/Millwall-Plymouth-Argyle-October-23-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/b2475a0d/Luton-Town-Sunderland-October-23-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ec61f7ad/Blackburn-Rovers-West-Bromwich-Albion-October-23-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/8f6e9889/Hull-City-Burnley-October-23-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b2475a0d/Luton-Town-Sunderland-October-23-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ec61f7ad/Blackburn-Rovers-West-Bromwich-Albion-October-23-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/8cef1a6f/Middlesbrough-Sheffield-United-October-23-2024-Championship</t>
   </si>
   <si>
@@ -1673,24 +2045,24 @@
     <t>https://fbref.com/en/matches/cc9c1708/Watford-Blackburn-Rovers-October-26-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/c59beda8/Burnley-Queens-Park-Rangers-October-26-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ce15e1fd/Plymouth-Argyle-Preston-North-End-October-26-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b521d7f8/Sheffield-United-Stoke-City-October-26-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/da73045d/Sunderland-Oxford-United-October-26-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b2383efd/Swansea-City-Millwall-October-26-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/7ca6685d/West-Bromwich-Albion-Cardiff-City-October-26-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b2383efd/Swansea-City-Millwall-October-26-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/b521d7f8/Sheffield-United-Stoke-City-October-26-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/c59beda8/Burnley-Queens-Park-Rangers-October-26-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ce15e1fd/Plymouth-Argyle-Preston-North-End-October-26-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/da73045d/Sunderland-Oxford-United-October-26-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/fdf11982/Derby-County-Hull-City-October-26-2024-Championship</t>
   </si>
   <si>
@@ -1703,36 +2075,39 @@
     <t>https://fbref.com/en/matches/15e1a067/Oxford-United-Swansea-City-November-2-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/9ae712b2/Blackburn-Rovers-Sheffield-United-November-2-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/6512ad6f/Stoke-City-Derby-County-November-2-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/9ae712b2/Blackburn-Rovers-Sheffield-United-November-2-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/331e188b/Cardiff-City-Norwich-City-November-2-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/5724c63e/Sheffield-Wednesday-Watford-November-2-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/a92a4e36/Preston-North-End-Bristol-City-November-2-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/a50bc6db/Hull-City-Portsmouth-November-2-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/a92a4e36/Preston-North-End-Bristol-City-November-2-2024-Championship</t>
+    <t>https://fbref.com/en/matches/ed5ce326/Queens-Park-Rangers-Sunderland-November-2-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d65f705a/Middlesbrough-Coventry-City-November-2-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/c46862e8/Leeds-United-Plymouth-Argyle-November-2-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d65f705a/Middlesbrough-Coventry-City-November-2-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ed5ce326/Queens-Park-Rangers-Sunderland-November-2-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/d3ddeada/Millwall-Burnley-November-3-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/fe832864/Queens-Park-Rangers-Middlesbrough-November-5-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/29df15a5/Sheffield-Wednesday-Norwich-City-November-5-2024-Championship</t>
   </si>
   <si>
@@ -1742,57 +2117,54 @@
     <t>https://fbref.com/en/matches/eaf5cd97/Oxford-United-Hull-City-November-5-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/fe832864/Queens-Park-Rangers-Middlesbrough-November-5-2024-Championship</t>
+    <t>https://fbref.com/en/matches/953c4971/Plymouth-Argyle-Portsmouth-November-5-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/22eb30ed/Swansea-City-Watford-November-5-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/953c4971/Plymouth-Argyle-Portsmouth-November-5-2024-Championship</t>
+    <t>https://fbref.com/en/matches/df8b3ccd/Blackburn-Rovers-Stoke-City-November-6-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8b9a8fba/Millwall-Leeds-United-November-6-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/7d54dd3e/Coventry-City-Derby-County-November-6-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/8b9a8fba/Millwall-Leeds-United-November-6-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/df8b3ccd/Blackburn-Rovers-Stoke-City-November-6-2024-Championship</t>
+    <t>https://fbref.com/en/matches/d71db0bd/Preston-North-End-Sunderland-November-6-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/49939421/Luton-Town-Cardiff-City-November-6-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d71db0bd/Preston-North-End-Sunderland-November-6-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/ad67dd64/West-Bromwich-Albion-Burnley-November-7-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/92f63f8c/Watford-Oxford-United-November-8-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/7b5755e7/Stoke-City-Millwall-November-9-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/cb4638bf/Middlesbrough-Luton-Town-November-9-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/65d87a4a/Cardiff-City-Blackburn-Rovers-November-9-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/7b5755e7/Stoke-City-Millwall-November-9-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/cb4638bf/Middlesbrough-Luton-Town-November-9-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/16ceac84/Portsmouth-Preston-North-End-November-9-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/636ca36b/Leeds-United-Queens-Park-Rangers-November-9-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/738708a0/Norwich-City-Bristol-City-November-9-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/693e7a3b/Derby-County-Plymouth-Argyle-November-9-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/738708a0/Norwich-City-Bristol-City-November-9-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/7eb39ed1/Sunderland-Coventry-City-November-9-2024-Championship</t>
   </si>
   <si>
@@ -1808,99 +2180,99 @@
     <t>https://fbref.com/en/matches/e5b4b14e/Plymouth-Argyle-Watford-November-22-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d13c4fcb/Bristol-City-Burnley-November-23-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a30accf8/Sheffield-Wednesday-Cardiff-City-November-23-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/5268fe49/Coventry-City-Sheffield-United-November-23-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/a30accf8/Sheffield-Wednesday-Cardiff-City-November-23-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d13c4fcb/Bristol-City-Burnley-November-23-2024-Championship</t>
+    <t>https://fbref.com/en/matches/fcc57ad4/Queens-Park-Rangers-Stoke-City-November-23-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/22c4db48/Millwall-Sunderland-November-23-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/048593c6/Luton-Town-Hull-City-November-23-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/7deb4475/Preston-North-End-Derby-County-November-23-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ed18cac7/Oxford-United-Middlesbrough-November-23-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/20144329/West-Bromwich-Albion-Norwich-City-November-23-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/22c4db48/Millwall-Sunderland-November-23-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/7deb4475/Preston-North-End-Derby-County-November-23-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ed18cac7/Oxford-United-Middlesbrough-November-23-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/fcc57ad4/Queens-Park-Rangers-Stoke-City-November-23-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/2de1c7be/Swansea-City-Leeds-United-November-24-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/6d224963/Watford-Bristol-City-November-26-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f79d2555/Burnley-Coventry-City-November-26-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c4d51048/Sheffield-United-Oxford-United-November-26-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a97d0c2c/Stoke-City-Preston-North-End-November-26-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/279aacc3/Norwich-City-Plymouth-Argyle-November-26-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/258e60bf/Hull-City-Sheffield-Wednesday-November-26-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/279aacc3/Norwich-City-Plymouth-Argyle-November-26-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/6d224963/Watford-Bristol-City-November-26-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/a97d0c2c/Stoke-City-Preston-North-End-November-26-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/c4d51048/Sheffield-United-Oxford-United-November-26-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/f79d2555/Burnley-Coventry-City-November-26-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/bef97610/Sunderland-West-Bromwich-Albion-November-26-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/32d56228/Cardiff-City-Queens-Park-Rangers-November-27-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/cd0b5197/Middlesbrough-Blackburn-Rovers-November-27-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/64c1c03d/Leeds-United-Luton-Town-November-27-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/cd0b5197/Middlesbrough-Blackburn-Rovers-November-27-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/2c44769b/Derby-County-Swansea-City-November-27-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/9b5f9a05/Sheffield-United-Sunderland-November-29-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/dfbf361d/Middlesbrough-Hull-City-November-30-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/98a1f8bf/Watford-Queens-Park-Rangers-November-30-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/dfbf361d/Middlesbrough-Hull-City-November-30-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/e4b2993a/Oxford-United-Millwall-November-30-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/7639346b/Blackburn-Rovers-Leeds-United-November-30-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/65e74ac5/Stoke-City-Burnley-November-30-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a514142e/Swansea-City-Portsmouth-November-30-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/97a98dcb/Coventry-City-Cardiff-City-November-30-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/1072a6ef/Norwich-City-Luton-Town-November-30-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/65e74ac5/Stoke-City-Burnley-November-30-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/97a98dcb/Coventry-City-Cardiff-City-November-30-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/98b613b5/Bristol-City-Plymouth-Argyle-November-30-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/a514142e/Swansea-City-Portsmouth-November-30-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/bac18c34/Preston-North-End-West-Bromwich-Albion-November-30-2024-Championship</t>
   </si>
   <si>
@@ -1910,51 +2282,51 @@
     <t>https://fbref.com/en/matches/b4b73ea3/Burnley-Middlesbrough-December-6-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/a7315485/Sunderland-Stoke-City-December-7-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ee5e4901/Leeds-United-Derby-County-December-7-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/65930788/Sheffield-Wednesday-Preston-North-End-December-7-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/a7315485/Sunderland-Stoke-City-December-7-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ee5e4901/Leeds-United-Derby-County-December-7-2024-Championship</t>
+    <t>https://fbref.com/en/matches/7632b821/Hull-City-Blackburn-Rovers-December-7-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a463bdbd/Queens-Park-Rangers-Norwich-City-December-7-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/65e73e28/Millwall-Coventry-City-December-7-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/06f1af0e/Portsmouth-Bristol-City-December-7-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/65e73e28/Millwall-Coventry-City-December-7-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/7632b821/Hull-City-Blackburn-Rovers-December-7-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/a463bdbd/Queens-Park-Rangers-Norwich-City-December-7-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/00bde56f/Luton-Town-Swansea-City-December-7-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/117145e9/West-Bromwich-Albion-Sheffield-United-December-8-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/72be2692/Luton-Town-Stoke-City-December-10-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/030787a7/Sheffield-Wednesday-Blackburn-Rovers-December-10-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/6919f41c/Burnley-Derby-County-December-10-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c19ee21e/Plymouth-Argyle-Swansea-City-December-10-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8e079dab/Portsmouth-Norwich-City-December-10-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/10b201b3/Sunderland-Bristol-City-December-10-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/6919f41c/Burnley-Derby-County-December-10-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/72be2692/Luton-Town-Stoke-City-December-10-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/8e079dab/Portsmouth-Norwich-City-December-10-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/c19ee21e/Plymouth-Argyle-Swansea-City-December-10-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/89ae2ea9/Leeds-United-Middlesbrough-December-10-2024-Championship</t>
   </si>
   <si>
@@ -1976,30 +2348,30 @@
     <t>https://fbref.com/en/matches/689caba4/Derby-County-Portsmouth-December-13-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/9d409aa7/Bristol-City-Queens-Park-Rangers-December-14-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2d86037b/Coventry-City-Hull-City-December-14-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/82347777/Preston-North-End-Leeds-United-December-14-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/9d409aa7/Bristol-City-Queens-Park-Rangers-December-14-2024-Championship</t>
+    <t>https://fbref.com/en/matches/6dfcd542/Swansea-City-Sunderland-December-14-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d54bd769/Stoke-City-Cardiff-City-December-14-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5ecd1cd0/Blackburn-Rovers-Luton-Town-December-14-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/de7471e1/Middlesbrough-Millwall-December-14-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/5bbcc700/Sheffield-United-Plymouth-Argyle-December-14-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/5ecd1cd0/Blackburn-Rovers-Luton-Town-December-14-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/6dfcd542/Swansea-City-Sunderland-December-14-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d54bd769/Stoke-City-Cardiff-City-December-14-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/de7471e1/Middlesbrough-Millwall-December-14-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/f252becc/Oxford-United-Sheffield-Wednesday-December-14-2024-Championship</t>
   </si>
   <si>
@@ -2012,13 +2384,22 @@
     <t>https://fbref.com/en/matches/03c07a2b/Luton-Town-Derby-County-December-20-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/c7bc9fcf/Hull-City-Swansea-City-December-21-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/17d57a50/Sheffield-Wednesday-Stoke-City-December-21-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/396226c7/Portsmouth-Coventry-City-December-21-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/c7bc9fcf/Hull-City-Swansea-City-December-21-2024-Championship</t>
+    <t>https://fbref.com/en/matches/804090af/Burnley-Watford-December-21-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/cfe916e0/Queens-Park-Rangers-Preston-North-End-December-21-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/cd4a9c20/Millwall-Blackburn-Rovers-December-21-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/32d87cee/Leeds-United-Oxford-United-December-21-2024-Championship</t>
@@ -2033,45 +2414,36 @@
     <t>https://fbref.com/en/matches/5a979a0e/Sunderland-Norwich-City-December-21-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/804090af/Burnley-Watford-December-21-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/cd4a9c20/Millwall-Blackburn-Rovers-December-21-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/cfe916e0/Queens-Park-Rangers-Preston-North-End-December-21-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/03897f64/West-Bromwich-Albion-Bristol-City-December-22-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/27846fc3/Watford-Portsmouth-December-26-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/626ca148/Norwich-City-Millwall-December-26-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/817f7602/Middlesbrough-Sheffield-Wednesday-December-26-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/df91770a/Preston-North-End-Hull-City-December-26-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/1b87ae4e/Oxford-United-Cardiff-City-December-26-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/27846fc3/Watford-Portsmouth-December-26-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/2d5f934d/Coventry-City-Plymouth-Argyle-December-26-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/830a20f2/Blackburn-Rovers-Sunderland-December-26-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/57658a1b/Sheffield-United-Burnley-December-26-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/56fd60ab/Bristol-City-Luton-Town-December-26-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/57658a1b/Sheffield-United-Burnley-December-26-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/626ca148/Norwich-City-Millwall-December-26-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/817f7602/Middlesbrough-Sheffield-Wednesday-December-26-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/830a20f2/Blackburn-Rovers-Sunderland-December-26-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/df91770a/Preston-North-End-Hull-City-December-26-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/fa013ad1/Swansea-City-Queens-Park-Rangers-December-26-2024-Championship</t>
   </si>
   <si>
@@ -2081,33 +2453,33 @@
     <t>https://fbref.com/en/matches/c6ec6c22/Stoke-City-Leeds-United-December-26-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/abfd255f/Sheffield-United-West-Bromwich-Albion-December-29-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/bc77e84c/Norwich-City-Queens-Park-Rangers-December-29-2024-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/298cad22/Preston-North-End-Sheffield-Wednesday-December-29-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/abfd255f/Sheffield-United-West-Bromwich-Albion-December-29-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/bc77e84c/Norwich-City-Queens-Park-Rangers-December-29-2024-Championship</t>
+    <t>https://fbref.com/en/matches/5ee726ec/Watford-Cardiff-City-December-29-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7432f1aa/Oxford-United-Plymouth-Argyle-December-29-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/891c9c61/Blackburn-Rovers-Hull-City-December-29-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e3b28954/Stoke-City-Sunderland-December-29-2024-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0abefaf7/Swansea-City-Luton-Town-December-29-2024-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/06d8e201/Coventry-City-Millwall-December-29-2024-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/0abefaf7/Swansea-City-Luton-Town-December-29-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/5ee726ec/Watford-Cardiff-City-December-29-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/7432f1aa/Oxford-United-Plymouth-Argyle-December-29-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/891c9c61/Blackburn-Rovers-Hull-City-December-29-2024-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e3b28954/Stoke-City-Sunderland-December-29-2024-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/f82e3425/Bristol-City-Portsmouth-December-29-2024-Championship</t>
   </si>
   <si>
@@ -2117,84 +2489,84 @@
     <t>https://fbref.com/en/matches/8212113a/Middlesbrough-Burnley-December-29-2024-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f7209634/Plymouth-Argyle-Bristol-City-January-1-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/3dfdab7f/Queens-Park-Rangers-Watford-January-1-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/f7209634/Plymouth-Argyle-Bristol-City-January-1-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/7f289f6f/Millwall-Oxford-United-January-1-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/28b05ab1/Portsmouth-Swansea-City-January-1-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/92814fd1/Cardiff-City-Coventry-City-January-1-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a00ee65e/Luton-Town-Norwich-City-January-1-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/06dc7273/West-Bromwich-Albion-Preston-North-End-January-1-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/28b05ab1/Portsmouth-Swansea-City-January-1-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/771f767e/Leeds-United-Blackburn-Rovers-January-1-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/92814fd1/Cardiff-City-Coventry-City-January-1-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/a00ee65e/Luton-Town-Norwich-City-January-1-2025-Championship</t>
+    <t>https://fbref.com/en/matches/ed9fc8df/Sheffield-Wednesday-Derby-County-January-1-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/b77d677f/Burnley-Stoke-City-January-1-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/ed9fc8df/Sheffield-Wednesday-Derby-County-January-1-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/362f9403/Hull-City-Middlesbrough-January-1-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/96c203d4/Sunderland-Sheffield-United-January-1-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/95fdeff3/Stoke-City-Plymouth-Argyle-January-4-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0eca2d6d/Blackburn-Rovers-Burnley-January-4-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/95fdeff3/Stoke-City-Plymouth-Argyle-January-4-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/c443693e/Swansea-City-West-Bromwich-Albion-January-4-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/0866f0e8/Hull-City-Leeds-United-January-4-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d4043d35/Bristol-City-Derby-County-January-4-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2fba75cc/Watford-Sheffield-United-January-4-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/5b5dc90a/Norwich-City-Coventry-City-January-4-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4dbd6c1c/Sheffield-Wednesday-Millwall-January-4-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/5b5dc90a/Norwich-City-Coventry-City-January-4-2025-Championship</t>
+    <t>https://fbref.com/en/matches/f99a5810/Preston-North-End-Oxford-United-January-4-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/cab9f51c/Middlesbrough-Cardiff-City-January-4-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d4043d35/Bristol-City-Derby-County-January-4-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/f99a5810/Preston-North-End-Oxford-United-January-4-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/1081e8eb/Sunderland-Portsmouth-January-5-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/c6d49b49/Queens-Park-Rangers-Luton-Town-January-6-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/3b814624/Cardiff-City-Watford-January-14-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/28a61bce/Plymouth-Argyle-Oxford-United-January-14-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3b814624/Cardiff-City-Watford-January-14-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/0523a3cf/Blackburn-Rovers-Portsmouth-January-15-2025-Championship</t>
   </si>
   <si>
@@ -2204,105 +2576,105 @@
     <t>https://fbref.com/en/matches/22b86724/Millwall-Hull-City-January-18-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/92864cd0/Cardiff-City-Swansea-City-January-18-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/36d7a096/Plymouth-Argyle-Queens-Park-Rangers-January-18-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/92864cd0/Cardiff-City-Swansea-City-January-18-2025-Championship</t>
+    <t>https://fbref.com/en/matches/2b09b517/Portsmouth-Middlesbrough-January-18-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/0d7c9805/Luton-Town-Preston-North-End-January-18-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/2b09b517/Portsmouth-Middlesbrough-January-18-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/2f1090ee/Sheffield-United-Norwich-City-January-18-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/dbf14941/Oxford-United-Blackburn-Rovers-January-18-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/dda05a01/West-Bromwich-Albion-Stoke-City-January-18-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/87090dd7/Coventry-City-Bristol-City-January-18-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/a3ff1571/Derby-County-Watford-January-18-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/dbf14941/Oxford-United-Blackburn-Rovers-January-18-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/dda05a01/West-Bromwich-Albion-Stoke-City-January-18-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/a3c61f15/Leeds-United-Sheffield-Wednesday-January-19-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/1089831e/Swansea-City-Sheffield-United-January-21-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/3a00f804/Derby-County-Sunderland-January-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2f7e3fdf/Oxford-United-Luton-Town-January-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/86962acd/Watford-Preston-North-End-January-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ec925e82/Middlesbrough-West-Bromwich-Albion-January-21-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2010d495/Blackburn-Rovers-Coventry-City-January-21-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/2f7e3fdf/Oxford-United-Luton-Town-January-21-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/3a00f804/Derby-County-Sunderland-January-21-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/86962acd/Watford-Preston-North-End-January-21-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/d165ded3/Hull-City-Queens-Park-Rangers-January-21-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/ec925e82/Middlesbrough-West-Bromwich-Albion-January-21-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/03875940/Millwall-Cardiff-City-January-21-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/7c2ed22e/Leeds-United-Norwich-City-January-22-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7b3282ad/Portsmouth-Stoke-City-January-22-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/015123b5/Sheffield-Wednesday-Bristol-City-January-22-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/7b3282ad/Portsmouth-Stoke-City-January-22-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/7c2ed22e/Leeds-United-Norwich-City-January-22-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/e073d138/Plymouth-Argyle-Burnley-January-22-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/676625b2/Sheffield-United-Hull-City-January-24-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/9750780a/Luton-Town-Millwall-January-25-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/4d148bd0/Stoke-City-Oxford-United-January-25-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/9750780a/Luton-Town-Millwall-January-25-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/ee7cee1a/Norwich-City-Swansea-City-January-25-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/f29ae45c/Sunderland-Plymouth-Argyle-January-25-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/37d0fd0a/Queens-Park-Rangers-Sheffield-Wednesday-January-25-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/453d44fb/Cardiff-City-Derby-County-January-25-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e34baed6/Preston-North-End-Middlesbrough-January-25-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b3e3cff6/Bristol-City-Blackburn-Rovers-January-25-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/081a93be/Coventry-City-Watford-January-25-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/1320361b/West-Bromwich-Albion-Portsmouth-January-25-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/37d0fd0a/Queens-Park-Rangers-Sheffield-Wednesday-January-25-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/453d44fb/Cardiff-City-Derby-County-January-25-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/b3e3cff6/Bristol-City-Blackburn-Rovers-January-25-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e34baed6/Preston-North-End-Middlesbrough-January-25-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/f29ae45c/Sunderland-Plymouth-Argyle-January-25-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/379dd246/Burnley-Leeds-United-January-27-2025-Championship</t>
   </si>
   <si>
@@ -2312,93 +2684,93 @@
     <t>https://fbref.com/en/matches/4e774b6a/Blackburn-Rovers-Preston-North-End-January-31-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/693c4650/Oxford-United-Bristol-City-February-1-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2a8e8207/Plymouth-Argyle-West-Bromwich-Albion-February-1-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/693c4650/Oxford-United-Bristol-City-February-1-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/c6bc68a0/Watford-Norwich-City-February-1-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/b6544fd3/Hull-City-Stoke-City-February-1-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4af3b214/Derby-County-Sheffield-United-February-1-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3e641a82/Portsmouth-Burnley-February-1-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/cdbcdf2d/Millwall-Queens-Park-Rangers-February-1-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/01cb8524/Leeds-United-Cardiff-City-February-1-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3e641a82/Portsmouth-Burnley-February-1-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/46eb866c/Sheffield-Wednesday-Luton-Town-February-1-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4af3b214/Derby-County-Sheffield-United-February-1-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/5c204e63/Swansea-City-Coventry-City-February-1-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b6544fd3/Hull-City-Stoke-City-February-1-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/cdbcdf2d/Millwall-Queens-Park-Rangers-February-1-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/44a22bbe/Middlesbrough-Sunderland-February-3-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d199c9ed/Burnley-Oxford-United-February-4-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/cb595c0c/Queens-Park-Rangers-Blackburn-Rovers-February-4-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d199c9ed/Burnley-Oxford-United-February-4-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/52113d47/Coventry-City-Leeds-United-February-5-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/754becae/Sunderland-Watford-February-8-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/6415ea58/West-Bromwich-Albion-Sheffield-Wednesday-February-8-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/754becae/Sunderland-Watford-February-8-2025-Championship</t>
+    <t>https://fbref.com/en/matches/fd5d22fc/Sheffield-United-Portsmouth-February-8-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/30d7eb6e/Norwich-City-Derby-County-February-8-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/fd5d22fc/Sheffield-United-Portsmouth-February-8-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/90efef14/Bristol-City-Swansea-City-February-9-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/dcf356c3/Derby-County-Oxford-United-February-11-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/40f0de2e/Watford-Leeds-United-February-11-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/22056835/Portsmouth-Cardiff-City-February-11-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/40f0de2e/Watford-Leeds-United-February-11-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/a8d666ff/Coventry-City-Queens-Park-Rangers-February-11-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/dcf356c3/Derby-County-Oxford-United-February-11-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/665065cf/Norwich-City-Preston-North-End-February-11-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/940f7015/Swansea-City-Sheffield-Wednesday-February-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5abfcdd3/Sunderland-Luton-Town-February-12-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/2c690538/Plymouth-Argyle-Millwall-February-12-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/5abfcdd3/Sunderland-Luton-Town-February-12-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/5fde3b3c/Burnley-Hull-City-February-12-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/646bd382/Bristol-City-Stoke-City-February-12-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/940f7015/Swansea-City-Sheffield-Wednesday-February-12-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/3971d9e9/Sheffield-United-Middlesbrough-February-12-2025-Championship</t>
   </si>
   <si>
@@ -2408,36 +2780,36 @@
     <t>https://fbref.com/en/matches/4c4d1e26/Queens-Park-Rangers-Derby-County-February-14-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/fb8a94c9/Oxford-United-Portsmouth-February-15-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/5c8b7c80/Preston-North-End-Burnley-February-15-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/dde41712/Cardiff-City-Bristol-City-February-15-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/fb8a94c9/Oxford-United-Portsmouth-February-15-2025-Championship</t>
+    <t>https://fbref.com/en/matches/3d8eee10/Millwall-West-Bromwich-Albion-February-15-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c15e28f0/Stoke-City-Swansea-City-February-15-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/1482fce5/Hull-City-Norwich-City-February-15-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/3d8eee10/Millwall-West-Bromwich-Albion-February-15-2025-Championship</t>
+    <t>https://fbref.com/en/matches/ac64abef/Luton-Town-Sheffield-United-February-15-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/83e4ecc0/Blackburn-Rovers-Plymouth-Argyle-February-15-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9e120549/Middlesbrough-Watford-February-15-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/5fcc05ba/Sheffield-Wednesday-Coventry-City-February-15-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/83e4ecc0/Blackburn-Rovers-Plymouth-Argyle-February-15-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/9e120549/Middlesbrough-Watford-February-15-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ac64abef/Luton-Town-Sheffield-United-February-15-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/c15e28f0/Stoke-City-Swansea-City-February-15-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/4c52d12d/Leeds-United-Sunderland-February-17-2025-Championship</t>
   </si>
   <si>
@@ -2453,13 +2825,16 @@
     <t>https://fbref.com/en/matches/d26a076b/Burnley-Sheffield-Wednesday-February-21-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/ca35285b/Plymouth-Argyle-Cardiff-City-February-22-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/bd090a23/Sunderland-Hull-City-February-22-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/bef12b49/Derby-County-Millwall-February-22-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/ca35285b/Plymouth-Argyle-Cardiff-City-February-22-2025-Championship</t>
+    <t>https://fbref.com/en/matches/e2ff48d9/West-Bromwich-Albion-Oxford-United-February-22-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/18c86aa7/Portsmouth-Queens-Park-Rangers-February-22-2025-Championship</t>
@@ -2468,15 +2843,12 @@
     <t>https://fbref.com/en/matches/9ba1a257/Coventry-City-Preston-North-End-February-22-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/e94b1f3b/Norwich-City-Stoke-City-February-22-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/b9838a91/Swansea-City-Blackburn-Rovers-February-22-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/e2ff48d9/West-Bromwich-Albion-Oxford-United-February-22-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/e94b1f3b/Norwich-City-Stoke-City-February-22-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/1957403a/Watford-Luton-Town-February-23-2025-Championship</t>
   </si>
   <si>
@@ -2492,25 +2864,397 @@
     <t>https://fbref.com/en/matches/21d09548/Sheffield-Wednesday-Sunderland-February-28-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/ec2c8f92/Oxford-United-Coventry-City-March-1-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/58f69ae9/Blackburn-Rovers-Norwich-City-March-1-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/ea38fe7d/Leeds-United-West-Bromwich-Albion-March-1-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/ec2c8f92/Oxford-United-Coventry-City-March-1-2025-Championship</t>
+    <t>https://fbref.com/en/matches/56fe2e0e/Middlesbrough-Derby-County-March-1-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/456d45f3/Luton-Town-Portsmouth-March-1-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/312652e5/Stoke-City-Watford-March-1-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/456d45f3/Luton-Town-Portsmouth-March-1-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/56fe2e0e/Middlesbrough-Derby-County-March-1-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/eda542fe/Queens-Park-Rangers-Sheffield-United-March-1-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/de5cb18a/Millwall-Bristol-City-March-4-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f7459d88/Hull-City-Plymouth-Argyle-March-4-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f04ca2f0/Preston-North-End-Swansea-City-March-4-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fa6aac7d/Cardiff-City-Burnley-March-4-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fc270c88/Norwich-City-Oxford-United-March-7-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2506e1ff/Watford-Millwall-March-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ad234706/Coventry-City-Stoke-City-March-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/348c4e52/West-Bromwich-Albion-Queens-Park-Rangers-March-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/cdb29532/Plymouth-Argyle-Sheffield-Wednesday-March-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3cda1eda/Burnley-Luton-Town-March-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/7c6242bf/Swansea-City-Middlesbrough-March-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/39a87866/Bristol-City-Hull-City-March-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8aad9013/Sunderland-Cardiff-City-March-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b8a3a8bc/Derby-County-Blackburn-Rovers-March-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ad4b81c9/Sheffield-United-Preston-North-End-March-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/72e61aac/Portsmouth-Leeds-United-March-9-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/55353ce6/Norwich-City-Sheffield-Wednesday-March-11-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fd10594b/Sunderland-Preston-North-End-March-11-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5285eea3/Derby-County-Coventry-City-March-11-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2800520b/Burnley-West-Bromwich-Albion-March-11-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/98d5f553/Middlesbrough-Queens-Park-Rangers-March-11-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/488aece8/Cardiff-City-Luton-Town-March-11-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/92af7be1/Sheffield-United-Bristol-City-March-11-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e5996b49/Leeds-United-Millwall-March-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/44fc2117/Watford-Swansea-City-March-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3e113b55/Portsmouth-Plymouth-Argyle-March-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/df15d048/Hull-City-Oxford-United-March-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/28bb9091/Stoke-City-Blackburn-Rovers-March-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5caf91c2/Bristol-City-Norwich-City-March-14-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6b09adaa/Queens-Park-Rangers-Leeds-United-March-15-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/36547e5f/Millwall-Stoke-City-March-15-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d580fda4/West-Bromwich-Albion-Hull-City-March-15-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d6e445c7/Luton-Town-Middlesbrough-March-15-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d7f4d1f6/Preston-North-End-Portsmouth-March-15-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/29ce02a8/Oxford-United-Watford-March-15-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/78cd2156/Coventry-City-Sunderland-March-15-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8b8d7d61/Blackburn-Rovers-Cardiff-City-March-15-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1adcc16e/Plymouth-Argyle-Derby-County-March-15-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0630637f/Swansea-City-Burnley-March-15-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/672cd8bb/Sheffield-Wednesday-Sheffield-United-March-16-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/69f33790/Sheffield-United-Coventry-City-March-28-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f72d25de/Hull-City-Luton-Town-March-29-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/65e2d8c1/Watford-Plymouth-Argyle-March-29-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d86286e2/Burnley-Bristol-City-March-29-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d9a8daac/Norwich-City-West-Bromwich-Albion-March-29-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/006cb0da/Cardiff-City-Sheffield-Wednesday-March-29-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/85f34678/Leeds-United-Swansea-City-March-29-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a48a14ae/Portsmouth-Blackburn-Rovers-March-29-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/bab3cde7/Sunderland-Millwall-March-29-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/bba2ba88/Middlesbrough-Oxford-United-March-29-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e0b67b63/Stoke-City-Queens-Park-Rangers-March-29-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e5f0b0a5/Derby-County-Preston-North-End-April-2-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/73491ffb/Blackburn-Rovers-Middlesbrough-April-4-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f9469484/Luton-Town-Leeds-United-April-5-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/70cb87c6/West-Bromwich-Albion-Sunderland-April-5-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/99b80154/Coventry-City-Burnley-April-5-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0082c8c9/Queens-Park-Rangers-Cardiff-City-April-5-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e2500563/Preston-North-End-Stoke-City-April-5-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0c6cd5e5/Plymouth-Argyle-Norwich-City-April-5-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4dacf49d/Bristol-City-Watford-April-5-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b804041c/Sheffield-Wednesday-Hull-City-April-5-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/bcc58133/Oxford-United-Sheffield-United-April-5-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/47f297e6/Swansea-City-Derby-County-April-5-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/40b21c1e/Millwall-Portsmouth-April-5-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/775936ee/Watford-Hull-City-April-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/753559ac/Norwich-City-Sunderland-April-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6adc522c/Preston-North-End-Cardiff-City-April-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ee95ce7f/Blackburn-Rovers-Sheffield-Wednesday-April-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/61bafc4b/Derby-County-Burnley-April-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3ae95ae5/Stoke-City-Luton-Town-April-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ca321728/Sheffield-United-Millwall-April-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d27a7302/Bristol-City-West-Bromwich-Albion-April-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a9cefab7/Middlesbrough-Leeds-United-April-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/36c37df0/Swansea-City-Plymouth-Argyle-April-9-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/23ae8663/Oxford-United-Queens-Park-Rangers-April-9-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/659fa4c7/Coventry-City-Portsmouth-April-9-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b0e44312/Burnley-Norwich-City-April-11-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/216c2d61/Leeds-United-Preston-North-End-April-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/024b1e2d/Plymouth-Argyle-Sheffield-United-April-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/48133119/Sunderland-Swansea-City-April-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4fe28233/Cardiff-City-Stoke-City-April-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/59456b0e/Sheffield-Wednesday-Oxford-United-April-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/65f40457/West-Bromwich-Albion-Watford-April-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/02f0ebee/Millwall-Middlesbrough-April-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ffcc7041/Portsmouth-Derby-County-April-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/bfa310fb/Luton-Town-Blackburn-Rovers-April-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d223e752/Queens-Park-Rangers-Bristol-City-April-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d7a15a0d/Hull-City-Coventry-City-April-14-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9dbd2be7/Derby-County-Luton-Town-April-18-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8d986475/Norwich-City-Portsmouth-April-18-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/459d9f88/Middlesbrough-Plymouth-Argyle-April-18-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4b2f813d/Watford-Burnley-April-18-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b3c9fe09/Blackburn-Rovers-Millwall-April-18-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3fa3fbcb/Coventry-City-West-Bromwich-Albion-April-18-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/e9422481/Stoke-City-Sheffield-Wednesday-April-18-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fb8a56f6/Swansea-City-Hull-City-April-18-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/359b9b8f/Preston-North-End-Queens-Park-Rangers-April-18-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/2c584b14/Bristol-City-Sunderland-April-18-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/434b2e5d/Sheffield-United-Cardiff-City-April-18-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/799c9a7e/Oxford-United-Leeds-United-April-18-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/83fd7cc8/Hull-City-Preston-North-End-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/04eac7b9/Luton-Town-Bristol-City-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f68c4ec2/Plymouth-Argyle-Coventry-City-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/50cb5210/Portsmouth-Watford-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5139d9b9/Cardiff-City-Oxford-United-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5222ce24/Leeds-United-Stoke-City-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/adc899d6/Sunderland-Blackburn-Rovers-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5fbd1555/West-Bromwich-Albion-Derby-County-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c1fddb70/Sheffield-Wednesday-Middlesbrough-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/252bc206/Millwall-Norwich-City-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a9dad4df/Queens-Park-Rangers-Swansea-City-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/0e3f9629/Burnley-Sheffield-United-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6bacbea4/Stoke-City-Sheffield-United-April-25-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/da258a5f/Luton-Town-Coventry-City-April-26-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/70d9d49b/Queens-Park-Rangers-Burnley-April-26-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/bd8b1982/Middlesbrough-Norwich-City-April-26-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/8c23c086/Blackburn-Rovers-Watford-April-26-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/89fcfad9/Oxford-United-Sunderland-April-26-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/96820f6e/Preston-North-End-Plymouth-Argyle-April-26-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ca192ba8/Cardiff-City-West-Bromwich-Albion-April-26-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6c4af4ab/Hull-City-Derby-County-April-26-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9a3324af/Sheffield-Wednesday-Portsmouth-April-26-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/eecd5fc9/Millwall-Swansea-City-April-26-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ad54bd5e/Leeds-United-Bristol-City-April-28-2025-Championship</t>
   </si>
 </sst>
 </file>
@@ -2569,7 +3313,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>417</v>
+        <v>541</v>
       </c>
     </row>
     <row r="3">
@@ -2577,7 +3321,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>418</v>
+        <v>542</v>
       </c>
     </row>
     <row r="4">
@@ -2585,7 +3329,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>419</v>
+        <v>543</v>
       </c>
     </row>
     <row r="5">
@@ -2593,7 +3337,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>420</v>
+        <v>544</v>
       </c>
     </row>
     <row r="6">
@@ -2601,7 +3345,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>421</v>
+        <v>545</v>
       </c>
     </row>
     <row r="7">
@@ -2609,7 +3353,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>422</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -2617,7 +3361,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>423</v>
+        <v>547</v>
       </c>
     </row>
     <row r="9">
@@ -2625,7 +3369,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>424</v>
+        <v>548</v>
       </c>
     </row>
     <row r="10">
@@ -2633,7 +3377,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>425</v>
+        <v>549</v>
       </c>
     </row>
     <row r="11">
@@ -2641,7 +3385,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>426</v>
+        <v>550</v>
       </c>
     </row>
     <row r="12">
@@ -2649,7 +3393,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>427</v>
+        <v>551</v>
       </c>
     </row>
     <row r="13">
@@ -2657,7 +3401,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>428</v>
+        <v>552</v>
       </c>
     </row>
     <row r="14">
@@ -2665,7 +3409,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>429</v>
+        <v>553</v>
       </c>
     </row>
     <row r="15">
@@ -2673,7 +3417,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>430</v>
+        <v>554</v>
       </c>
     </row>
     <row r="16">
@@ -2681,7 +3425,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>431</v>
+        <v>555</v>
       </c>
     </row>
     <row r="17">
@@ -2689,7 +3433,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>432</v>
+        <v>556</v>
       </c>
     </row>
     <row r="18">
@@ -2697,7 +3441,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>433</v>
+        <v>557</v>
       </c>
     </row>
     <row r="19">
@@ -2705,7 +3449,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>434</v>
+        <v>558</v>
       </c>
     </row>
     <row r="20">
@@ -2713,7 +3457,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>435</v>
+        <v>559</v>
       </c>
     </row>
     <row r="21">
@@ -2721,7 +3465,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>436</v>
+        <v>560</v>
       </c>
     </row>
     <row r="22">
@@ -2729,7 +3473,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>437</v>
+        <v>561</v>
       </c>
     </row>
     <row r="23">
@@ -2737,7 +3481,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>438</v>
+        <v>562</v>
       </c>
     </row>
     <row r="24">
@@ -2745,7 +3489,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>439</v>
+        <v>563</v>
       </c>
     </row>
     <row r="25">
@@ -2753,7 +3497,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>440</v>
+        <v>564</v>
       </c>
     </row>
     <row r="26">
@@ -2761,7 +3505,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>441</v>
+        <v>565</v>
       </c>
     </row>
     <row r="27">
@@ -2769,7 +3513,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>442</v>
+        <v>566</v>
       </c>
     </row>
     <row r="28">
@@ -2777,7 +3521,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>443</v>
+        <v>567</v>
       </c>
     </row>
     <row r="29">
@@ -2785,7 +3529,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>444</v>
+        <v>568</v>
       </c>
     </row>
     <row r="30">
@@ -2793,7 +3537,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>445</v>
+        <v>569</v>
       </c>
     </row>
     <row r="31">
@@ -2801,7 +3545,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>446</v>
+        <v>570</v>
       </c>
     </row>
     <row r="32">
@@ -2809,7 +3553,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>447</v>
+        <v>571</v>
       </c>
     </row>
     <row r="33">
@@ -2817,7 +3561,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>448</v>
+        <v>572</v>
       </c>
     </row>
     <row r="34">
@@ -2825,7 +3569,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>449</v>
+        <v>573</v>
       </c>
     </row>
     <row r="35">
@@ -2833,7 +3577,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>450</v>
+        <v>574</v>
       </c>
     </row>
     <row r="36">
@@ -2841,7 +3585,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>451</v>
+        <v>575</v>
       </c>
     </row>
     <row r="37">
@@ -2849,7 +3593,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>452</v>
+        <v>576</v>
       </c>
     </row>
     <row r="38">
@@ -2857,7 +3601,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>453</v>
+        <v>577</v>
       </c>
     </row>
     <row r="39">
@@ -2865,7 +3609,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>454</v>
+        <v>578</v>
       </c>
     </row>
     <row r="40">
@@ -2873,7 +3617,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>455</v>
+        <v>579</v>
       </c>
     </row>
     <row r="41">
@@ -2881,7 +3625,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>456</v>
+        <v>580</v>
       </c>
     </row>
     <row r="42">
@@ -2889,7 +3633,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>457</v>
+        <v>581</v>
       </c>
     </row>
     <row r="43">
@@ -2897,7 +3641,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>458</v>
+        <v>582</v>
       </c>
     </row>
     <row r="44">
@@ -2905,7 +3649,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>459</v>
+        <v>583</v>
       </c>
     </row>
     <row r="45">
@@ -2913,7 +3657,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>460</v>
+        <v>584</v>
       </c>
     </row>
     <row r="46">
@@ -2921,7 +3665,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>461</v>
+        <v>585</v>
       </c>
     </row>
     <row r="47">
@@ -2929,7 +3673,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>462</v>
+        <v>586</v>
       </c>
     </row>
     <row r="48">
@@ -2937,7 +3681,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>463</v>
+        <v>587</v>
       </c>
     </row>
     <row r="49">
@@ -2945,7 +3689,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>464</v>
+        <v>588</v>
       </c>
     </row>
     <row r="50">
@@ -2953,7 +3697,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>465</v>
+        <v>589</v>
       </c>
     </row>
     <row r="51">
@@ -2961,7 +3705,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>466</v>
+        <v>590</v>
       </c>
     </row>
     <row r="52">
@@ -2969,7 +3713,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>467</v>
+        <v>591</v>
       </c>
     </row>
     <row r="53">
@@ -2977,7 +3721,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>468</v>
+        <v>592</v>
       </c>
     </row>
     <row r="54">
@@ -2985,7 +3729,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>469</v>
+        <v>593</v>
       </c>
     </row>
     <row r="55">
@@ -2993,7 +3737,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>470</v>
+        <v>594</v>
       </c>
     </row>
     <row r="56">
@@ -3001,7 +3745,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>471</v>
+        <v>595</v>
       </c>
     </row>
     <row r="57">
@@ -3009,7 +3753,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>472</v>
+        <v>596</v>
       </c>
     </row>
     <row r="58">
@@ -3017,7 +3761,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>473</v>
+        <v>597</v>
       </c>
     </row>
     <row r="59">
@@ -3025,7 +3769,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>474</v>
+        <v>598</v>
       </c>
     </row>
     <row r="60">
@@ -3033,7 +3777,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>475</v>
+        <v>599</v>
       </c>
     </row>
     <row r="61">
@@ -3041,7 +3785,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>476</v>
+        <v>600</v>
       </c>
     </row>
     <row r="62">
@@ -3049,7 +3793,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>477</v>
+        <v>601</v>
       </c>
     </row>
     <row r="63">
@@ -3057,7 +3801,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>478</v>
+        <v>602</v>
       </c>
     </row>
     <row r="64">
@@ -3065,7 +3809,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>479</v>
+        <v>603</v>
       </c>
     </row>
     <row r="65">
@@ -3073,7 +3817,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>480</v>
+        <v>604</v>
       </c>
     </row>
     <row r="66">
@@ -3081,7 +3825,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>481</v>
+        <v>605</v>
       </c>
     </row>
     <row r="67">
@@ -3089,7 +3833,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>482</v>
+        <v>606</v>
       </c>
     </row>
     <row r="68">
@@ -3097,7 +3841,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>483</v>
+        <v>607</v>
       </c>
     </row>
     <row r="69">
@@ -3105,7 +3849,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>484</v>
+        <v>608</v>
       </c>
     </row>
     <row r="70">
@@ -3113,7 +3857,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>485</v>
+        <v>609</v>
       </c>
     </row>
     <row r="71">
@@ -3121,7 +3865,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>486</v>
+        <v>610</v>
       </c>
     </row>
     <row r="72">
@@ -3129,7 +3873,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>487</v>
+        <v>611</v>
       </c>
     </row>
     <row r="73">
@@ -3137,7 +3881,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>488</v>
+        <v>612</v>
       </c>
     </row>
     <row r="74">
@@ -3145,7 +3889,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>489</v>
+        <v>613</v>
       </c>
     </row>
     <row r="75">
@@ -3153,7 +3897,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>490</v>
+        <v>614</v>
       </c>
     </row>
     <row r="76">
@@ -3161,7 +3905,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>491</v>
+        <v>615</v>
       </c>
     </row>
     <row r="77">
@@ -3169,7 +3913,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>492</v>
+        <v>616</v>
       </c>
     </row>
     <row r="78">
@@ -3177,7 +3921,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>493</v>
+        <v>617</v>
       </c>
     </row>
     <row r="79">
@@ -3185,7 +3929,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>494</v>
+        <v>618</v>
       </c>
     </row>
     <row r="80">
@@ -3193,7 +3937,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>495</v>
+        <v>619</v>
       </c>
     </row>
     <row r="81">
@@ -3201,7 +3945,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>496</v>
+        <v>620</v>
       </c>
     </row>
     <row r="82">
@@ -3209,7 +3953,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>497</v>
+        <v>621</v>
       </c>
     </row>
     <row r="83">
@@ -3217,7 +3961,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>498</v>
+        <v>622</v>
       </c>
     </row>
     <row r="84">
@@ -3225,7 +3969,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>499</v>
+        <v>623</v>
       </c>
     </row>
     <row r="85">
@@ -3233,7 +3977,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>500</v>
+        <v>624</v>
       </c>
     </row>
     <row r="86">
@@ -3241,7 +3985,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>501</v>
+        <v>625</v>
       </c>
     </row>
     <row r="87">
@@ -3249,7 +3993,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>502</v>
+        <v>626</v>
       </c>
     </row>
     <row r="88">
@@ -3257,7 +4001,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>503</v>
+        <v>627</v>
       </c>
     </row>
     <row r="89">
@@ -3265,7 +4009,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>504</v>
+        <v>628</v>
       </c>
     </row>
     <row r="90">
@@ -3273,7 +4017,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>505</v>
+        <v>629</v>
       </c>
     </row>
     <row r="91">
@@ -3281,7 +4025,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>506</v>
+        <v>630</v>
       </c>
     </row>
     <row r="92">
@@ -3289,7 +4033,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>507</v>
+        <v>631</v>
       </c>
     </row>
     <row r="93">
@@ -3297,7 +4041,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>508</v>
+        <v>632</v>
       </c>
     </row>
     <row r="94">
@@ -3305,7 +4049,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>509</v>
+        <v>633</v>
       </c>
     </row>
     <row r="95">
@@ -3313,7 +4057,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>510</v>
+        <v>634</v>
       </c>
     </row>
     <row r="96">
@@ -3321,7 +4065,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>511</v>
+        <v>635</v>
       </c>
     </row>
     <row r="97">
@@ -3329,7 +4073,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>512</v>
+        <v>636</v>
       </c>
     </row>
     <row r="98">
@@ -3337,7 +4081,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>513</v>
+        <v>637</v>
       </c>
     </row>
     <row r="99">
@@ -3345,7 +4089,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>514</v>
+        <v>638</v>
       </c>
     </row>
     <row r="100">
@@ -3353,7 +4097,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>515</v>
+        <v>639</v>
       </c>
     </row>
     <row r="101">
@@ -3361,7 +4105,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>516</v>
+        <v>640</v>
       </c>
     </row>
     <row r="102">
@@ -3369,7 +4113,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>517</v>
+        <v>641</v>
       </c>
     </row>
     <row r="103">
@@ -3377,7 +4121,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>518</v>
+        <v>642</v>
       </c>
     </row>
     <row r="104">
@@ -3385,7 +4129,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>519</v>
+        <v>643</v>
       </c>
     </row>
     <row r="105">
@@ -3393,7 +4137,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>520</v>
+        <v>644</v>
       </c>
     </row>
     <row r="106">
@@ -3401,7 +4145,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>521</v>
+        <v>645</v>
       </c>
     </row>
     <row r="107">
@@ -3409,7 +4153,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>522</v>
+        <v>646</v>
       </c>
     </row>
     <row r="108">
@@ -3417,7 +4161,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>523</v>
+        <v>647</v>
       </c>
     </row>
     <row r="109">
@@ -3425,7 +4169,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>524</v>
+        <v>648</v>
       </c>
     </row>
     <row r="110">
@@ -3433,7 +4177,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>525</v>
+        <v>649</v>
       </c>
     </row>
     <row r="111">
@@ -3441,7 +4185,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>526</v>
+        <v>650</v>
       </c>
     </row>
     <row r="112">
@@ -3449,7 +4193,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>527</v>
+        <v>651</v>
       </c>
     </row>
     <row r="113">
@@ -3457,7 +4201,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>528</v>
+        <v>652</v>
       </c>
     </row>
     <row r="114">
@@ -3465,7 +4209,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>529</v>
+        <v>653</v>
       </c>
     </row>
     <row r="115">
@@ -3473,7 +4217,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>530</v>
+        <v>654</v>
       </c>
     </row>
     <row r="116">
@@ -3481,7 +4225,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>531</v>
+        <v>655</v>
       </c>
     </row>
     <row r="117">
@@ -3489,7 +4233,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>532</v>
+        <v>656</v>
       </c>
     </row>
     <row r="118">
@@ -3497,7 +4241,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>533</v>
+        <v>657</v>
       </c>
     </row>
     <row r="119">
@@ -3505,7 +4249,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>534</v>
+        <v>658</v>
       </c>
     </row>
     <row r="120">
@@ -3513,7 +4257,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>535</v>
+        <v>659</v>
       </c>
     </row>
     <row r="121">
@@ -3521,7 +4265,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>536</v>
+        <v>660</v>
       </c>
     </row>
     <row r="122">
@@ -3529,7 +4273,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>537</v>
+        <v>661</v>
       </c>
     </row>
     <row r="123">
@@ -3537,7 +4281,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>538</v>
+        <v>662</v>
       </c>
     </row>
     <row r="124">
@@ -3545,7 +4289,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>539</v>
+        <v>663</v>
       </c>
     </row>
     <row r="125">
@@ -3553,7 +4297,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>540</v>
+        <v>664</v>
       </c>
     </row>
     <row r="126">
@@ -3561,7 +4305,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>541</v>
+        <v>665</v>
       </c>
     </row>
     <row r="127">
@@ -3569,7 +4313,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>542</v>
+        <v>666</v>
       </c>
     </row>
     <row r="128">
@@ -3577,7 +4321,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>543</v>
+        <v>667</v>
       </c>
     </row>
     <row r="129">
@@ -3585,7 +4329,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>544</v>
+        <v>668</v>
       </c>
     </row>
     <row r="130">
@@ -3593,7 +4337,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>545</v>
+        <v>669</v>
       </c>
     </row>
     <row r="131">
@@ -3601,7 +4345,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>546</v>
+        <v>670</v>
       </c>
     </row>
     <row r="132">
@@ -3609,7 +4353,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>547</v>
+        <v>671</v>
       </c>
     </row>
     <row r="133">
@@ -3617,7 +4361,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>548</v>
+        <v>672</v>
       </c>
     </row>
     <row r="134">
@@ -3625,7 +4369,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>549</v>
+        <v>673</v>
       </c>
     </row>
     <row r="135">
@@ -3633,7 +4377,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>550</v>
+        <v>674</v>
       </c>
     </row>
     <row r="136">
@@ -3641,7 +4385,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>551</v>
+        <v>675</v>
       </c>
     </row>
     <row r="137">
@@ -3649,7 +4393,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>552</v>
+        <v>676</v>
       </c>
     </row>
     <row r="138">
@@ -3657,7 +4401,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>553</v>
+        <v>677</v>
       </c>
     </row>
     <row r="139">
@@ -3665,7 +4409,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>554</v>
+        <v>678</v>
       </c>
     </row>
     <row r="140">
@@ -3673,7 +4417,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>555</v>
+        <v>679</v>
       </c>
     </row>
     <row r="141">
@@ -3681,7 +4425,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>556</v>
+        <v>680</v>
       </c>
     </row>
     <row r="142">
@@ -3689,7 +4433,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>557</v>
+        <v>681</v>
       </c>
     </row>
     <row r="143">
@@ -3697,7 +4441,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>558</v>
+        <v>682</v>
       </c>
     </row>
     <row r="144">
@@ -3705,7 +4449,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>559</v>
+        <v>683</v>
       </c>
     </row>
     <row r="145">
@@ -3713,7 +4457,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>560</v>
+        <v>684</v>
       </c>
     </row>
     <row r="146">
@@ -3721,7 +4465,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>561</v>
+        <v>685</v>
       </c>
     </row>
     <row r="147">
@@ -3729,7 +4473,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>562</v>
+        <v>686</v>
       </c>
     </row>
     <row r="148">
@@ -3737,7 +4481,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>563</v>
+        <v>687</v>
       </c>
     </row>
     <row r="149">
@@ -3745,7 +4489,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>564</v>
+        <v>688</v>
       </c>
     </row>
     <row r="150">
@@ -3753,7 +4497,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>565</v>
+        <v>689</v>
       </c>
     </row>
     <row r="151">
@@ -3761,7 +4505,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>566</v>
+        <v>690</v>
       </c>
     </row>
     <row r="152">
@@ -3769,7 +4513,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>567</v>
+        <v>691</v>
       </c>
     </row>
     <row r="153">
@@ -3777,7 +4521,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>568</v>
+        <v>692</v>
       </c>
     </row>
     <row r="154">
@@ -3785,7 +4529,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>569</v>
+        <v>693</v>
       </c>
     </row>
     <row r="155">
@@ -3793,7 +4537,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>570</v>
+        <v>694</v>
       </c>
     </row>
     <row r="156">
@@ -3801,7 +4545,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>571</v>
+        <v>695</v>
       </c>
     </row>
     <row r="157">
@@ -3809,7 +4553,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>572</v>
+        <v>696</v>
       </c>
     </row>
     <row r="158">
@@ -3817,7 +4561,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>573</v>
+        <v>697</v>
       </c>
     </row>
     <row r="159">
@@ -3825,7 +4569,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>574</v>
+        <v>698</v>
       </c>
     </row>
     <row r="160">
@@ -3833,7 +4577,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>575</v>
+        <v>699</v>
       </c>
     </row>
     <row r="161">
@@ -3841,7 +4585,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>576</v>
+        <v>700</v>
       </c>
     </row>
     <row r="162">
@@ -3849,7 +4593,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>577</v>
+        <v>701</v>
       </c>
     </row>
     <row r="163">
@@ -3857,7 +4601,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>578</v>
+        <v>702</v>
       </c>
     </row>
     <row r="164">
@@ -3865,7 +4609,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>579</v>
+        <v>703</v>
       </c>
     </row>
     <row r="165">
@@ -3873,7 +4617,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>580</v>
+        <v>704</v>
       </c>
     </row>
     <row r="166">
@@ -3881,7 +4625,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>581</v>
+        <v>705</v>
       </c>
     </row>
     <row r="167">
@@ -3889,7 +4633,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>582</v>
+        <v>706</v>
       </c>
     </row>
     <row r="168">
@@ -3897,7 +4641,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>583</v>
+        <v>707</v>
       </c>
     </row>
     <row r="169">
@@ -3905,7 +4649,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>584</v>
+        <v>708</v>
       </c>
     </row>
     <row r="170">
@@ -3913,7 +4657,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>585</v>
+        <v>709</v>
       </c>
     </row>
     <row r="171">
@@ -3921,7 +4665,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>586</v>
+        <v>710</v>
       </c>
     </row>
     <row r="172">
@@ -3929,7 +4673,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>587</v>
+        <v>711</v>
       </c>
     </row>
     <row r="173">
@@ -3937,7 +4681,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>588</v>
+        <v>712</v>
       </c>
     </row>
     <row r="174">
@@ -3945,7 +4689,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>589</v>
+        <v>713</v>
       </c>
     </row>
     <row r="175">
@@ -3953,7 +4697,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>590</v>
+        <v>714</v>
       </c>
     </row>
     <row r="176">
@@ -3961,7 +4705,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>591</v>
+        <v>715</v>
       </c>
     </row>
     <row r="177">
@@ -3969,7 +4713,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>592</v>
+        <v>716</v>
       </c>
     </row>
     <row r="178">
@@ -3977,7 +4721,7 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>593</v>
+        <v>717</v>
       </c>
     </row>
     <row r="179">
@@ -3985,7 +4729,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>594</v>
+        <v>718</v>
       </c>
     </row>
     <row r="180">
@@ -3993,7 +4737,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>595</v>
+        <v>719</v>
       </c>
     </row>
     <row r="181">
@@ -4001,7 +4745,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>596</v>
+        <v>720</v>
       </c>
     </row>
     <row r="182">
@@ -4009,7 +4753,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>597</v>
+        <v>721</v>
       </c>
     </row>
     <row r="183">
@@ -4017,7 +4761,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>598</v>
+        <v>722</v>
       </c>
     </row>
     <row r="184">
@@ -4025,7 +4769,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>599</v>
+        <v>723</v>
       </c>
     </row>
     <row r="185">
@@ -4033,7 +4777,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>600</v>
+        <v>724</v>
       </c>
     </row>
     <row r="186">
@@ -4041,7 +4785,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>601</v>
+        <v>725</v>
       </c>
     </row>
     <row r="187">
@@ -4049,7 +4793,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>602</v>
+        <v>726</v>
       </c>
     </row>
     <row r="188">
@@ -4057,7 +4801,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>603</v>
+        <v>727</v>
       </c>
     </row>
     <row r="189">
@@ -4065,7 +4809,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>604</v>
+        <v>728</v>
       </c>
     </row>
     <row r="190">
@@ -4073,7 +4817,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>605</v>
+        <v>729</v>
       </c>
     </row>
     <row r="191">
@@ -4081,7 +4825,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>606</v>
+        <v>730</v>
       </c>
     </row>
     <row r="192">
@@ -4089,7 +4833,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>607</v>
+        <v>731</v>
       </c>
     </row>
     <row r="193">
@@ -4097,7 +4841,7 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>608</v>
+        <v>732</v>
       </c>
     </row>
     <row r="194">
@@ -4105,7 +4849,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>609</v>
+        <v>733</v>
       </c>
     </row>
     <row r="195">
@@ -4113,7 +4857,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>610</v>
+        <v>734</v>
       </c>
     </row>
     <row r="196">
@@ -4121,7 +4865,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>611</v>
+        <v>735</v>
       </c>
     </row>
     <row r="197">
@@ -4129,7 +4873,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>612</v>
+        <v>736</v>
       </c>
     </row>
     <row r="198">
@@ -4137,7 +4881,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>613</v>
+        <v>737</v>
       </c>
     </row>
     <row r="199">
@@ -4145,7 +4889,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>614</v>
+        <v>738</v>
       </c>
     </row>
     <row r="200">
@@ -4153,7 +4897,7 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>615</v>
+        <v>739</v>
       </c>
     </row>
     <row r="201">
@@ -4161,7 +4905,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>616</v>
+        <v>740</v>
       </c>
     </row>
     <row r="202">
@@ -4169,7 +4913,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>617</v>
+        <v>741</v>
       </c>
     </row>
     <row r="203">
@@ -4177,7 +4921,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>618</v>
+        <v>742</v>
       </c>
     </row>
     <row r="204">
@@ -4185,7 +4929,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>619</v>
+        <v>743</v>
       </c>
     </row>
     <row r="205">
@@ -4193,7 +4937,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>620</v>
+        <v>744</v>
       </c>
     </row>
     <row r="206">
@@ -4201,7 +4945,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>621</v>
+        <v>745</v>
       </c>
     </row>
     <row r="207">
@@ -4209,7 +4953,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>622</v>
+        <v>746</v>
       </c>
     </row>
     <row r="208">
@@ -4217,7 +4961,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>623</v>
+        <v>747</v>
       </c>
     </row>
     <row r="209">
@@ -4225,7 +4969,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>624</v>
+        <v>748</v>
       </c>
     </row>
     <row r="210">
@@ -4233,7 +4977,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>625</v>
+        <v>749</v>
       </c>
     </row>
     <row r="211">
@@ -4241,7 +4985,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>626</v>
+        <v>750</v>
       </c>
     </row>
     <row r="212">
@@ -4249,7 +4993,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>627</v>
+        <v>751</v>
       </c>
     </row>
     <row r="213">
@@ -4257,7 +5001,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>628</v>
+        <v>752</v>
       </c>
     </row>
     <row r="214">
@@ -4265,7 +5009,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>629</v>
+        <v>753</v>
       </c>
     </row>
     <row r="215">
@@ -4273,7 +5017,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>630</v>
+        <v>754</v>
       </c>
     </row>
     <row r="216">
@@ -4281,7 +5025,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>631</v>
+        <v>755</v>
       </c>
     </row>
     <row r="217">
@@ -4289,7 +5033,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>632</v>
+        <v>756</v>
       </c>
     </row>
     <row r="218">
@@ -4297,7 +5041,7 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>633</v>
+        <v>757</v>
       </c>
     </row>
     <row r="219">
@@ -4305,7 +5049,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>634</v>
+        <v>758</v>
       </c>
     </row>
     <row r="220">
@@ -4313,7 +5057,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>635</v>
+        <v>759</v>
       </c>
     </row>
     <row r="221">
@@ -4321,7 +5065,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>636</v>
+        <v>760</v>
       </c>
     </row>
     <row r="222">
@@ -4329,7 +5073,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>637</v>
+        <v>761</v>
       </c>
     </row>
     <row r="223">
@@ -4337,7 +5081,7 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>638</v>
+        <v>762</v>
       </c>
     </row>
     <row r="224">
@@ -4345,7 +5089,7 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>639</v>
+        <v>763</v>
       </c>
     </row>
     <row r="225">
@@ -4353,7 +5097,7 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>640</v>
+        <v>764</v>
       </c>
     </row>
     <row r="226">
@@ -4361,7 +5105,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>641</v>
+        <v>765</v>
       </c>
     </row>
     <row r="227">
@@ -4369,7 +5113,7 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>642</v>
+        <v>766</v>
       </c>
     </row>
     <row r="228">
@@ -4377,7 +5121,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>643</v>
+        <v>767</v>
       </c>
     </row>
     <row r="229">
@@ -4385,7 +5129,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>644</v>
+        <v>768</v>
       </c>
     </row>
     <row r="230">
@@ -4393,7 +5137,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>645</v>
+        <v>769</v>
       </c>
     </row>
     <row r="231">
@@ -4401,7 +5145,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>646</v>
+        <v>770</v>
       </c>
     </row>
     <row r="232">
@@ -4409,7 +5153,7 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>647</v>
+        <v>771</v>
       </c>
     </row>
     <row r="233">
@@ -4417,7 +5161,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>648</v>
+        <v>772</v>
       </c>
     </row>
     <row r="234">
@@ -4425,7 +5169,7 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>649</v>
+        <v>773</v>
       </c>
     </row>
     <row r="235">
@@ -4433,7 +5177,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>650</v>
+        <v>774</v>
       </c>
     </row>
     <row r="236">
@@ -4441,7 +5185,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>651</v>
+        <v>775</v>
       </c>
     </row>
     <row r="237">
@@ -4449,7 +5193,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>652</v>
+        <v>776</v>
       </c>
     </row>
     <row r="238">
@@ -4457,7 +5201,7 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>653</v>
+        <v>777</v>
       </c>
     </row>
     <row r="239">
@@ -4465,7 +5209,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>654</v>
+        <v>778</v>
       </c>
     </row>
     <row r="240">
@@ -4473,7 +5217,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>655</v>
+        <v>779</v>
       </c>
     </row>
     <row r="241">
@@ -4481,7 +5225,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>656</v>
+        <v>780</v>
       </c>
     </row>
     <row r="242">
@@ -4489,7 +5233,7 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>657</v>
+        <v>781</v>
       </c>
     </row>
     <row r="243">
@@ -4497,7 +5241,7 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>658</v>
+        <v>782</v>
       </c>
     </row>
     <row r="244">
@@ -4505,7 +5249,7 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>659</v>
+        <v>783</v>
       </c>
     </row>
     <row r="245">
@@ -4513,7 +5257,7 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>660</v>
+        <v>784</v>
       </c>
     </row>
     <row r="246">
@@ -4521,7 +5265,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>661</v>
+        <v>785</v>
       </c>
     </row>
     <row r="247">
@@ -4529,7 +5273,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>662</v>
+        <v>786</v>
       </c>
     </row>
     <row r="248">
@@ -4537,7 +5281,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>663</v>
+        <v>787</v>
       </c>
     </row>
     <row r="249">
@@ -4545,7 +5289,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>664</v>
+        <v>788</v>
       </c>
     </row>
     <row r="250">
@@ -4553,7 +5297,7 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>665</v>
+        <v>789</v>
       </c>
     </row>
     <row r="251">
@@ -4561,7 +5305,7 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>666</v>
+        <v>790</v>
       </c>
     </row>
     <row r="252">
@@ -4569,7 +5313,7 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>667</v>
+        <v>791</v>
       </c>
     </row>
     <row r="253">
@@ -4577,7 +5321,7 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>668</v>
+        <v>792</v>
       </c>
     </row>
     <row r="254">
@@ -4585,7 +5329,7 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>669</v>
+        <v>793</v>
       </c>
     </row>
     <row r="255">
@@ -4593,7 +5337,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>670</v>
+        <v>794</v>
       </c>
     </row>
     <row r="256">
@@ -4601,7 +5345,7 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>671</v>
+        <v>795</v>
       </c>
     </row>
     <row r="257">
@@ -4609,7 +5353,7 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>672</v>
+        <v>796</v>
       </c>
     </row>
     <row r="258">
@@ -4617,7 +5361,7 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>673</v>
+        <v>797</v>
       </c>
     </row>
     <row r="259">
@@ -4625,7 +5369,7 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>674</v>
+        <v>798</v>
       </c>
     </row>
     <row r="260">
@@ -4633,7 +5377,7 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>675</v>
+        <v>799</v>
       </c>
     </row>
     <row r="261">
@@ -4641,7 +5385,7 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>676</v>
+        <v>800</v>
       </c>
     </row>
     <row r="262">
@@ -4649,7 +5393,7 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>677</v>
+        <v>801</v>
       </c>
     </row>
     <row r="263">
@@ -4657,7 +5401,7 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>678</v>
+        <v>802</v>
       </c>
     </row>
     <row r="264">
@@ -4665,7 +5409,7 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>679</v>
+        <v>803</v>
       </c>
     </row>
     <row r="265">
@@ -4673,7 +5417,7 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>680</v>
+        <v>804</v>
       </c>
     </row>
     <row r="266">
@@ -4681,7 +5425,7 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>681</v>
+        <v>805</v>
       </c>
     </row>
     <row r="267">
@@ -4689,7 +5433,7 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>682</v>
+        <v>806</v>
       </c>
     </row>
     <row r="268">
@@ -4697,7 +5441,7 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>683</v>
+        <v>807</v>
       </c>
     </row>
     <row r="269">
@@ -4705,7 +5449,7 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>684</v>
+        <v>808</v>
       </c>
     </row>
     <row r="270">
@@ -4713,7 +5457,7 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>685</v>
+        <v>809</v>
       </c>
     </row>
     <row r="271">
@@ -4721,7 +5465,7 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>686</v>
+        <v>810</v>
       </c>
     </row>
     <row r="272">
@@ -4729,7 +5473,7 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>687</v>
+        <v>811</v>
       </c>
     </row>
     <row r="273">
@@ -4737,7 +5481,7 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>688</v>
+        <v>812</v>
       </c>
     </row>
     <row r="274">
@@ -4745,7 +5489,7 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>689</v>
+        <v>813</v>
       </c>
     </row>
     <row r="275">
@@ -4753,7 +5497,7 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>690</v>
+        <v>814</v>
       </c>
     </row>
     <row r="276">
@@ -4761,7 +5505,7 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>691</v>
+        <v>815</v>
       </c>
     </row>
     <row r="277">
@@ -4769,7 +5513,7 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>692</v>
+        <v>816</v>
       </c>
     </row>
     <row r="278">
@@ -4777,7 +5521,7 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>693</v>
+        <v>817</v>
       </c>
     </row>
     <row r="279">
@@ -4785,7 +5529,7 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>694</v>
+        <v>818</v>
       </c>
     </row>
     <row r="280">
@@ -4793,7 +5537,7 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>695</v>
+        <v>819</v>
       </c>
     </row>
     <row r="281">
@@ -4801,7 +5545,7 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>696</v>
+        <v>820</v>
       </c>
     </row>
     <row r="282">
@@ -4809,7 +5553,7 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>697</v>
+        <v>821</v>
       </c>
     </row>
     <row r="283">
@@ -4817,7 +5561,7 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>698</v>
+        <v>822</v>
       </c>
     </row>
     <row r="284">
@@ -4825,7 +5569,7 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>699</v>
+        <v>823</v>
       </c>
     </row>
     <row r="285">
@@ -4833,7 +5577,7 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>700</v>
+        <v>824</v>
       </c>
     </row>
     <row r="286">
@@ -4841,7 +5585,7 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>701</v>
+        <v>825</v>
       </c>
     </row>
     <row r="287">
@@ -4849,7 +5593,7 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>702</v>
+        <v>826</v>
       </c>
     </row>
     <row r="288">
@@ -4857,7 +5601,7 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>703</v>
+        <v>827</v>
       </c>
     </row>
     <row r="289">
@@ -4865,7 +5609,7 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>704</v>
+        <v>828</v>
       </c>
     </row>
     <row r="290">
@@ -4873,7 +5617,7 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>705</v>
+        <v>829</v>
       </c>
     </row>
     <row r="291">
@@ -4881,7 +5625,7 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>706</v>
+        <v>830</v>
       </c>
     </row>
     <row r="292">
@@ -4889,7 +5633,7 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>707</v>
+        <v>831</v>
       </c>
     </row>
     <row r="293">
@@ -4897,7 +5641,7 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>708</v>
+        <v>832</v>
       </c>
     </row>
     <row r="294">
@@ -4905,7 +5649,7 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>709</v>
+        <v>833</v>
       </c>
     </row>
     <row r="295">
@@ -4913,7 +5657,7 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>710</v>
+        <v>834</v>
       </c>
     </row>
     <row r="296">
@@ -4921,7 +5665,7 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>711</v>
+        <v>835</v>
       </c>
     </row>
     <row r="297">
@@ -4929,7 +5673,7 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>712</v>
+        <v>836</v>
       </c>
     </row>
     <row r="298">
@@ -4937,7 +5681,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>713</v>
+        <v>837</v>
       </c>
     </row>
     <row r="299">
@@ -4945,7 +5689,7 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>714</v>
+        <v>838</v>
       </c>
     </row>
     <row r="300">
@@ -4953,7 +5697,7 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>715</v>
+        <v>839</v>
       </c>
     </row>
     <row r="301">
@@ -4961,7 +5705,7 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>716</v>
+        <v>840</v>
       </c>
     </row>
     <row r="302">
@@ -4969,7 +5713,7 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>717</v>
+        <v>841</v>
       </c>
     </row>
     <row r="303">
@@ -4977,7 +5721,7 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>718</v>
+        <v>842</v>
       </c>
     </row>
     <row r="304">
@@ -4985,7 +5729,7 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>719</v>
+        <v>843</v>
       </c>
     </row>
     <row r="305">
@@ -4993,7 +5737,7 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>720</v>
+        <v>844</v>
       </c>
     </row>
     <row r="306">
@@ -5001,7 +5745,7 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>721</v>
+        <v>845</v>
       </c>
     </row>
     <row r="307">
@@ -5009,7 +5753,7 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>722</v>
+        <v>846</v>
       </c>
     </row>
     <row r="308">
@@ -5017,7 +5761,7 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>723</v>
+        <v>847</v>
       </c>
     </row>
     <row r="309">
@@ -5025,7 +5769,7 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>724</v>
+        <v>848</v>
       </c>
     </row>
     <row r="310">
@@ -5033,7 +5777,7 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>725</v>
+        <v>849</v>
       </c>
     </row>
     <row r="311">
@@ -5041,7 +5785,7 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>726</v>
+        <v>850</v>
       </c>
     </row>
     <row r="312">
@@ -5049,7 +5793,7 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>727</v>
+        <v>851</v>
       </c>
     </row>
     <row r="313">
@@ -5057,7 +5801,7 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>728</v>
+        <v>852</v>
       </c>
     </row>
     <row r="314">
@@ -5065,7 +5809,7 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>729</v>
+        <v>853</v>
       </c>
     </row>
     <row r="315">
@@ -5073,7 +5817,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>730</v>
+        <v>854</v>
       </c>
     </row>
     <row r="316">
@@ -5081,7 +5825,7 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>731</v>
+        <v>855</v>
       </c>
     </row>
     <row r="317">
@@ -5089,7 +5833,7 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>732</v>
+        <v>856</v>
       </c>
     </row>
     <row r="318">
@@ -5097,7 +5841,7 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>733</v>
+        <v>857</v>
       </c>
     </row>
     <row r="319">
@@ -5105,7 +5849,7 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>734</v>
+        <v>858</v>
       </c>
     </row>
     <row r="320">
@@ -5113,7 +5857,7 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>735</v>
+        <v>859</v>
       </c>
     </row>
     <row r="321">
@@ -5121,7 +5865,7 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>736</v>
+        <v>860</v>
       </c>
     </row>
     <row r="322">
@@ -5129,7 +5873,7 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>737</v>
+        <v>861</v>
       </c>
     </row>
     <row r="323">
@@ -5137,7 +5881,7 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>738</v>
+        <v>862</v>
       </c>
     </row>
     <row r="324">
@@ -5145,7 +5889,7 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>739</v>
+        <v>863</v>
       </c>
     </row>
     <row r="325">
@@ -5153,7 +5897,7 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>740</v>
+        <v>864</v>
       </c>
     </row>
     <row r="326">
@@ -5161,7 +5905,7 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>741</v>
+        <v>865</v>
       </c>
     </row>
     <row r="327">
@@ -5169,7 +5913,7 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>742</v>
+        <v>866</v>
       </c>
     </row>
     <row r="328">
@@ -5177,7 +5921,7 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>743</v>
+        <v>867</v>
       </c>
     </row>
     <row r="329">
@@ -5185,7 +5929,7 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>744</v>
+        <v>868</v>
       </c>
     </row>
     <row r="330">
@@ -5193,7 +5937,7 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>745</v>
+        <v>869</v>
       </c>
     </row>
     <row r="331">
@@ -5201,7 +5945,7 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>746</v>
+        <v>870</v>
       </c>
     </row>
     <row r="332">
@@ -5209,7 +5953,7 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>747</v>
+        <v>871</v>
       </c>
     </row>
     <row r="333">
@@ -5217,7 +5961,7 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>748</v>
+        <v>872</v>
       </c>
     </row>
     <row r="334">
@@ -5225,7 +5969,7 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>749</v>
+        <v>873</v>
       </c>
     </row>
     <row r="335">
@@ -5233,7 +5977,7 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>750</v>
+        <v>874</v>
       </c>
     </row>
     <row r="336">
@@ -5241,7 +5985,7 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>751</v>
+        <v>875</v>
       </c>
     </row>
     <row r="337">
@@ -5249,7 +5993,7 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>752</v>
+        <v>876</v>
       </c>
     </row>
     <row r="338">
@@ -5257,7 +6001,7 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>753</v>
+        <v>877</v>
       </c>
     </row>
     <row r="339">
@@ -5265,7 +6009,7 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>754</v>
+        <v>878</v>
       </c>
     </row>
     <row r="340">
@@ -5273,7 +6017,7 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>755</v>
+        <v>879</v>
       </c>
     </row>
     <row r="341">
@@ -5281,7 +6025,7 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>756</v>
+        <v>880</v>
       </c>
     </row>
     <row r="342">
@@ -5289,7 +6033,7 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>757</v>
+        <v>881</v>
       </c>
     </row>
     <row r="343">
@@ -5297,7 +6041,7 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>758</v>
+        <v>882</v>
       </c>
     </row>
     <row r="344">
@@ -5305,7 +6049,7 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>759</v>
+        <v>883</v>
       </c>
     </row>
     <row r="345">
@@ -5313,7 +6057,7 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>760</v>
+        <v>884</v>
       </c>
     </row>
     <row r="346">
@@ -5321,7 +6065,7 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>761</v>
+        <v>885</v>
       </c>
     </row>
     <row r="347">
@@ -5329,7 +6073,7 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>762</v>
+        <v>886</v>
       </c>
     </row>
     <row r="348">
@@ -5337,7 +6081,7 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>763</v>
+        <v>887</v>
       </c>
     </row>
     <row r="349">
@@ -5345,7 +6089,7 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>764</v>
+        <v>888</v>
       </c>
     </row>
     <row r="350">
@@ -5353,7 +6097,7 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>765</v>
+        <v>889</v>
       </c>
     </row>
     <row r="351">
@@ -5361,7 +6105,7 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>766</v>
+        <v>890</v>
       </c>
     </row>
     <row r="352">
@@ -5369,7 +6113,7 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>767</v>
+        <v>891</v>
       </c>
     </row>
     <row r="353">
@@ -5377,7 +6121,7 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>768</v>
+        <v>892</v>
       </c>
     </row>
     <row r="354">
@@ -5385,7 +6129,7 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>769</v>
+        <v>893</v>
       </c>
     </row>
     <row r="355">
@@ -5393,7 +6137,7 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>770</v>
+        <v>894</v>
       </c>
     </row>
     <row r="356">
@@ -5401,7 +6145,7 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>771</v>
+        <v>895</v>
       </c>
     </row>
     <row r="357">
@@ -5409,7 +6153,7 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>772</v>
+        <v>896</v>
       </c>
     </row>
     <row r="358">
@@ -5417,7 +6161,7 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>773</v>
+        <v>897</v>
       </c>
     </row>
     <row r="359">
@@ -5425,7 +6169,7 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>774</v>
+        <v>898</v>
       </c>
     </row>
     <row r="360">
@@ -5433,7 +6177,7 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>775</v>
+        <v>899</v>
       </c>
     </row>
     <row r="361">
@@ -5441,7 +6185,7 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>776</v>
+        <v>900</v>
       </c>
     </row>
     <row r="362">
@@ -5449,7 +6193,7 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>777</v>
+        <v>901</v>
       </c>
     </row>
     <row r="363">
@@ -5457,7 +6201,7 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>778</v>
+        <v>902</v>
       </c>
     </row>
     <row r="364">
@@ -5465,7 +6209,7 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>779</v>
+        <v>903</v>
       </c>
     </row>
     <row r="365">
@@ -5473,7 +6217,7 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>780</v>
+        <v>904</v>
       </c>
     </row>
     <row r="366">
@@ -5481,7 +6225,7 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>781</v>
+        <v>905</v>
       </c>
     </row>
     <row r="367">
@@ -5489,7 +6233,7 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>782</v>
+        <v>906</v>
       </c>
     </row>
     <row r="368">
@@ -5497,7 +6241,7 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>783</v>
+        <v>907</v>
       </c>
     </row>
     <row r="369">
@@ -5505,7 +6249,7 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>784</v>
+        <v>908</v>
       </c>
     </row>
     <row r="370">
@@ -5513,7 +6257,7 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>785</v>
+        <v>909</v>
       </c>
     </row>
     <row r="371">
@@ -5521,7 +6265,7 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>786</v>
+        <v>910</v>
       </c>
     </row>
     <row r="372">
@@ -5529,7 +6273,7 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>787</v>
+        <v>911</v>
       </c>
     </row>
     <row r="373">
@@ -5537,7 +6281,7 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>788</v>
+        <v>912</v>
       </c>
     </row>
     <row r="374">
@@ -5545,7 +6289,7 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>789</v>
+        <v>913</v>
       </c>
     </row>
     <row r="375">
@@ -5553,7 +6297,7 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>790</v>
+        <v>914</v>
       </c>
     </row>
     <row r="376">
@@ -5561,7 +6305,7 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>791</v>
+        <v>915</v>
       </c>
     </row>
     <row r="377">
@@ -5569,7 +6313,7 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>792</v>
+        <v>916</v>
       </c>
     </row>
     <row r="378">
@@ -5577,7 +6321,7 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>793</v>
+        <v>917</v>
       </c>
     </row>
     <row r="379">
@@ -5585,7 +6329,7 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>794</v>
+        <v>918</v>
       </c>
     </row>
     <row r="380">
@@ -5593,7 +6337,7 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>795</v>
+        <v>919</v>
       </c>
     </row>
     <row r="381">
@@ -5601,7 +6345,7 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>796</v>
+        <v>920</v>
       </c>
     </row>
     <row r="382">
@@ -5609,7 +6353,7 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>797</v>
+        <v>921</v>
       </c>
     </row>
     <row r="383">
@@ -5617,7 +6361,7 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>798</v>
+        <v>922</v>
       </c>
     </row>
     <row r="384">
@@ -5625,7 +6369,7 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>799</v>
+        <v>923</v>
       </c>
     </row>
     <row r="385">
@@ -5633,7 +6377,7 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>800</v>
+        <v>924</v>
       </c>
     </row>
     <row r="386">
@@ -5641,7 +6385,7 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>801</v>
+        <v>925</v>
       </c>
     </row>
     <row r="387">
@@ -5649,7 +6393,7 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>802</v>
+        <v>926</v>
       </c>
     </row>
     <row r="388">
@@ -5657,7 +6401,7 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>803</v>
+        <v>927</v>
       </c>
     </row>
     <row r="389">
@@ -5665,7 +6409,7 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>804</v>
+        <v>928</v>
       </c>
     </row>
     <row r="390">
@@ -5673,7 +6417,7 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>805</v>
+        <v>929</v>
       </c>
     </row>
     <row r="391">
@@ -5681,7 +6425,7 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>806</v>
+        <v>930</v>
       </c>
     </row>
     <row r="392">
@@ -5689,7 +6433,7 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>807</v>
+        <v>931</v>
       </c>
     </row>
     <row r="393">
@@ -5697,7 +6441,7 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>808</v>
+        <v>932</v>
       </c>
     </row>
     <row r="394">
@@ -5705,7 +6449,7 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>809</v>
+        <v>933</v>
       </c>
     </row>
     <row r="395">
@@ -5713,7 +6457,7 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>810</v>
+        <v>934</v>
       </c>
     </row>
     <row r="396">
@@ -5721,7 +6465,7 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>811</v>
+        <v>935</v>
       </c>
     </row>
     <row r="397">
@@ -5729,7 +6473,7 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>812</v>
+        <v>936</v>
       </c>
     </row>
     <row r="398">
@@ -5737,7 +6481,7 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>813</v>
+        <v>937</v>
       </c>
     </row>
     <row r="399">
@@ -5745,7 +6489,7 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>814</v>
+        <v>938</v>
       </c>
     </row>
     <row r="400">
@@ -5753,7 +6497,7 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>815</v>
+        <v>939</v>
       </c>
     </row>
     <row r="401">
@@ -5761,7 +6505,7 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>816</v>
+        <v>940</v>
       </c>
     </row>
     <row r="402">
@@ -5769,7 +6513,7 @@
         <v>401</v>
       </c>
       <c r="B402" t="s">
-        <v>817</v>
+        <v>941</v>
       </c>
     </row>
     <row r="403">
@@ -5777,7 +6521,7 @@
         <v>402</v>
       </c>
       <c r="B403" t="s">
-        <v>818</v>
+        <v>942</v>
       </c>
     </row>
     <row r="404">
@@ -5785,7 +6529,7 @@
         <v>403</v>
       </c>
       <c r="B404" t="s">
-        <v>819</v>
+        <v>943</v>
       </c>
     </row>
     <row r="405">
@@ -5793,7 +6537,7 @@
         <v>404</v>
       </c>
       <c r="B405" t="s">
-        <v>820</v>
+        <v>944</v>
       </c>
     </row>
     <row r="406">
@@ -5801,7 +6545,7 @@
         <v>405</v>
       </c>
       <c r="B406" t="s">
-        <v>821</v>
+        <v>945</v>
       </c>
     </row>
     <row r="407">
@@ -5809,7 +6553,7 @@
         <v>406</v>
       </c>
       <c r="B407" t="s">
-        <v>822</v>
+        <v>946</v>
       </c>
     </row>
     <row r="408">
@@ -5817,7 +6561,7 @@
         <v>407</v>
       </c>
       <c r="B408" t="s">
-        <v>823</v>
+        <v>947</v>
       </c>
     </row>
     <row r="409">
@@ -5825,7 +6569,7 @@
         <v>408</v>
       </c>
       <c r="B409" t="s">
-        <v>824</v>
+        <v>948</v>
       </c>
     </row>
     <row r="410">
@@ -5833,7 +6577,7 @@
         <v>409</v>
       </c>
       <c r="B410" t="s">
-        <v>825</v>
+        <v>949</v>
       </c>
     </row>
     <row r="411">
@@ -5841,7 +6585,7 @@
         <v>410</v>
       </c>
       <c r="B411" t="s">
-        <v>826</v>
+        <v>950</v>
       </c>
     </row>
     <row r="412">
@@ -5849,7 +6593,7 @@
         <v>411</v>
       </c>
       <c r="B412" t="s">
-        <v>827</v>
+        <v>951</v>
       </c>
     </row>
     <row r="413">
@@ -5857,7 +6601,7 @@
         <v>412</v>
       </c>
       <c r="B413" t="s">
-        <v>828</v>
+        <v>952</v>
       </c>
     </row>
     <row r="414">
@@ -5865,7 +6609,7 @@
         <v>413</v>
       </c>
       <c r="B414" t="s">
-        <v>829</v>
+        <v>953</v>
       </c>
     </row>
     <row r="415">
@@ -5873,7 +6617,7 @@
         <v>414</v>
       </c>
       <c r="B415" t="s">
-        <v>830</v>
+        <v>954</v>
       </c>
     </row>
     <row r="416">
@@ -5881,7 +6625,7 @@
         <v>415</v>
       </c>
       <c r="B416" t="s">
-        <v>831</v>
+        <v>955</v>
       </c>
     </row>
     <row r="417">
@@ -5889,7 +6633,999 @@
         <v>416</v>
       </c>
       <c r="B417" t="s">
-        <v>832</v>
+        <v>956</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="s">
+        <v>417</v>
+      </c>
+      <c r="B418" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="s">
+        <v>418</v>
+      </c>
+      <c r="B419" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="s">
+        <v>419</v>
+      </c>
+      <c r="B420" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="s">
+        <v>420</v>
+      </c>
+      <c r="B421" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="s">
+        <v>421</v>
+      </c>
+      <c r="B422" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="s">
+        <v>422</v>
+      </c>
+      <c r="B423" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="s">
+        <v>423</v>
+      </c>
+      <c r="B424" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="s">
+        <v>424</v>
+      </c>
+      <c r="B425" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="s">
+        <v>425</v>
+      </c>
+      <c r="B426" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="s">
+        <v>426</v>
+      </c>
+      <c r="B427" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="s">
+        <v>427</v>
+      </c>
+      <c r="B428" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="s">
+        <v>428</v>
+      </c>
+      <c r="B429" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="s">
+        <v>429</v>
+      </c>
+      <c r="B430" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="s">
+        <v>430</v>
+      </c>
+      <c r="B431" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="s">
+        <v>431</v>
+      </c>
+      <c r="B432" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="s">
+        <v>432</v>
+      </c>
+      <c r="B433" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="s">
+        <v>433</v>
+      </c>
+      <c r="B434" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="s">
+        <v>434</v>
+      </c>
+      <c r="B435" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="s">
+        <v>435</v>
+      </c>
+      <c r="B436" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="s">
+        <v>436</v>
+      </c>
+      <c r="B437" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="s">
+        <v>437</v>
+      </c>
+      <c r="B438" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="s">
+        <v>438</v>
+      </c>
+      <c r="B439" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="s">
+        <v>439</v>
+      </c>
+      <c r="B440" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="s">
+        <v>440</v>
+      </c>
+      <c r="B441" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="s">
+        <v>441</v>
+      </c>
+      <c r="B442" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="s">
+        <v>442</v>
+      </c>
+      <c r="B443" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="s">
+        <v>443</v>
+      </c>
+      <c r="B444" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="s">
+        <v>444</v>
+      </c>
+      <c r="B445" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="s">
+        <v>445</v>
+      </c>
+      <c r="B446" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="s">
+        <v>446</v>
+      </c>
+      <c r="B447" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="s">
+        <v>447</v>
+      </c>
+      <c r="B448" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="s">
+        <v>448</v>
+      </c>
+      <c r="B449" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="s">
+        <v>449</v>
+      </c>
+      <c r="B450" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="s">
+        <v>450</v>
+      </c>
+      <c r="B451" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="s">
+        <v>451</v>
+      </c>
+      <c r="B452" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="s">
+        <v>452</v>
+      </c>
+      <c r="B453" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="s">
+        <v>453</v>
+      </c>
+      <c r="B454" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="s">
+        <v>454</v>
+      </c>
+      <c r="B455" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="s">
+        <v>455</v>
+      </c>
+      <c r="B456" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="s">
+        <v>456</v>
+      </c>
+      <c r="B457" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="s">
+        <v>457</v>
+      </c>
+      <c r="B458" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="s">
+        <v>458</v>
+      </c>
+      <c r="B459" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="s">
+        <v>459</v>
+      </c>
+      <c r="B460" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="s">
+        <v>460</v>
+      </c>
+      <c r="B461" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="s">
+        <v>461</v>
+      </c>
+      <c r="B462" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="s">
+        <v>462</v>
+      </c>
+      <c r="B463" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="s">
+        <v>463</v>
+      </c>
+      <c r="B464" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="s">
+        <v>464</v>
+      </c>
+      <c r="B465" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="s">
+        <v>465</v>
+      </c>
+      <c r="B466" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="s">
+        <v>466</v>
+      </c>
+      <c r="B467" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="s">
+        <v>467</v>
+      </c>
+      <c r="B468" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="s">
+        <v>468</v>
+      </c>
+      <c r="B469" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="s">
+        <v>469</v>
+      </c>
+      <c r="B470" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="s">
+        <v>470</v>
+      </c>
+      <c r="B471" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="s">
+        <v>471</v>
+      </c>
+      <c r="B472" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="s">
+        <v>472</v>
+      </c>
+      <c r="B473" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="s">
+        <v>473</v>
+      </c>
+      <c r="B474" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="s">
+        <v>474</v>
+      </c>
+      <c r="B475" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="s">
+        <v>475</v>
+      </c>
+      <c r="B476" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="s">
+        <v>476</v>
+      </c>
+      <c r="B477" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="s">
+        <v>477</v>
+      </c>
+      <c r="B478" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="s">
+        <v>478</v>
+      </c>
+      <c r="B479" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="s">
+        <v>479</v>
+      </c>
+      <c r="B480" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="s">
+        <v>480</v>
+      </c>
+      <c r="B481" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="s">
+        <v>481</v>
+      </c>
+      <c r="B482" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="s">
+        <v>482</v>
+      </c>
+      <c r="B483" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="s">
+        <v>483</v>
+      </c>
+      <c r="B484" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="s">
+        <v>484</v>
+      </c>
+      <c r="B485" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="s">
+        <v>485</v>
+      </c>
+      <c r="B486" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="s">
+        <v>486</v>
+      </c>
+      <c r="B487" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="s">
+        <v>487</v>
+      </c>
+      <c r="B488" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="s">
+        <v>488</v>
+      </c>
+      <c r="B489" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="s">
+        <v>489</v>
+      </c>
+      <c r="B490" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="s">
+        <v>490</v>
+      </c>
+      <c r="B491" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="s">
+        <v>491</v>
+      </c>
+      <c r="B492" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="s">
+        <v>492</v>
+      </c>
+      <c r="B493" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="s">
+        <v>493</v>
+      </c>
+      <c r="B494" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="s">
+        <v>494</v>
+      </c>
+      <c r="B495" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="s">
+        <v>495</v>
+      </c>
+      <c r="B496" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="s">
+        <v>496</v>
+      </c>
+      <c r="B497" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="s">
+        <v>497</v>
+      </c>
+      <c r="B498" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="s">
+        <v>498</v>
+      </c>
+      <c r="B499" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="s">
+        <v>499</v>
+      </c>
+      <c r="B500" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="s">
+        <v>500</v>
+      </c>
+      <c r="B501" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="s">
+        <v>501</v>
+      </c>
+      <c r="B502" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="s">
+        <v>502</v>
+      </c>
+      <c r="B503" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="s">
+        <v>503</v>
+      </c>
+      <c r="B504" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="s">
+        <v>504</v>
+      </c>
+      <c r="B505" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="s">
+        <v>505</v>
+      </c>
+      <c r="B506" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="s">
+        <v>506</v>
+      </c>
+      <c r="B507" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="s">
+        <v>507</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="s">
+        <v>508</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="s">
+        <v>509</v>
+      </c>
+      <c r="B510" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="s">
+        <v>510</v>
+      </c>
+      <c r="B511" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="s">
+        <v>511</v>
+      </c>
+      <c r="B512" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="s">
+        <v>512</v>
+      </c>
+      <c r="B513" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="s">
+        <v>513</v>
+      </c>
+      <c r="B514" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="s">
+        <v>514</v>
+      </c>
+      <c r="B515" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="s">
+        <v>515</v>
+      </c>
+      <c r="B516" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="s">
+        <v>516</v>
+      </c>
+      <c r="B517" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="s">
+        <v>517</v>
+      </c>
+      <c r="B518" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="s">
+        <v>518</v>
+      </c>
+      <c r="B519" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="s">
+        <v>519</v>
+      </c>
+      <c r="B520" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="s">
+        <v>520</v>
+      </c>
+      <c r="B521" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="s">
+        <v>521</v>
+      </c>
+      <c r="B522" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="s">
+        <v>522</v>
+      </c>
+      <c r="B523" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="s">
+        <v>523</v>
+      </c>
+      <c r="B524" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="s">
+        <v>524</v>
+      </c>
+      <c r="B525" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="s">
+        <v>525</v>
+      </c>
+      <c r="B526" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="s">
+        <v>526</v>
+      </c>
+      <c r="B527" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="s">
+        <v>527</v>
+      </c>
+      <c r="B528" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="s">
+        <v>528</v>
+      </c>
+      <c r="B529" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="s">
+        <v>529</v>
+      </c>
+      <c r="B530" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="s">
+        <v>530</v>
+      </c>
+      <c r="B531" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="s">
+        <v>531</v>
+      </c>
+      <c r="B532" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="s">
+        <v>532</v>
+      </c>
+      <c r="B533" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="s">
+        <v>533</v>
+      </c>
+      <c r="B534" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="s">
+        <v>534</v>
+      </c>
+      <c r="B535" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="s">
+        <v>535</v>
+      </c>
+      <c r="B536" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="s">
+        <v>536</v>
+      </c>
+      <c r="B537" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="s">
+        <v>537</v>
+      </c>
+      <c r="B538" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="s">
+        <v>538</v>
+      </c>
+      <c r="B539" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="s">
+        <v>539</v>
+      </c>
+      <c r="B540" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="s">
+        <v>540</v>
+      </c>
+      <c r="B541" t="s">
+        <v>1080</v>
       </c>
     </row>
   </sheetData>

--- a/e1_urls.xlsx
+++ b/e1_urls.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="1081">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="1115">
   <si>
     <t>x</t>
   </si>
@@ -1637,6 +1637,57 @@
     <t>540</t>
   </si>
   <si>
+    <t>541</t>
+  </si>
+  <si>
+    <t>542</t>
+  </si>
+  <si>
+    <t>543</t>
+  </si>
+  <si>
+    <t>544</t>
+  </si>
+  <si>
+    <t>545</t>
+  </si>
+  <si>
+    <t>546</t>
+  </si>
+  <si>
+    <t>547</t>
+  </si>
+  <si>
+    <t>548</t>
+  </si>
+  <si>
+    <t>549</t>
+  </si>
+  <si>
+    <t>550</t>
+  </si>
+  <si>
+    <t>551</t>
+  </si>
+  <si>
+    <t>552</t>
+  </si>
+  <si>
+    <t>553</t>
+  </si>
+  <si>
+    <t>554</t>
+  </si>
+  <si>
+    <t>555</t>
+  </si>
+  <si>
+    <t>556</t>
+  </si>
+  <si>
+    <t>557</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/1ae41d3c/Blackburn-Rovers-Derby-County-August-9-2024-Championship</t>
   </si>
   <si>
@@ -3059,10 +3110,16 @@
     <t>https://fbref.com/en/matches/e2500563/Preston-North-End-Stoke-City-April-5-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/4dacf49d/Bristol-City-Watford-April-5-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/47f297e6/Swansea-City-Derby-County-April-5-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/0c6cd5e5/Plymouth-Argyle-Norwich-City-April-5-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4dacf49d/Bristol-City-Watford-April-5-2025-Championship</t>
+    <t>https://fbref.com/en/matches/40b21c1e/Millwall-Portsmouth-April-5-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/b804041c/Sheffield-Wednesday-Hull-City-April-5-2025-Championship</t>
@@ -3071,12 +3128,6 @@
     <t>https://fbref.com/en/matches/bcc58133/Oxford-United-Sheffield-United-April-5-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/47f297e6/Swansea-City-Derby-County-April-5-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/40b21c1e/Millwall-Portsmouth-April-5-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/775936ee/Watford-Hull-City-April-8-2025-Championship</t>
   </si>
   <si>
@@ -3095,12 +3146,12 @@
     <t>https://fbref.com/en/matches/3ae95ae5/Stoke-City-Luton-Town-April-8-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/d27a7302/Bristol-City-West-Bromwich-Albion-April-8-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/ca321728/Sheffield-United-Millwall-April-8-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/d27a7302/Bristol-City-West-Bromwich-Albion-April-8-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/a9cefab7/Middlesbrough-Leeds-United-April-8-2025-Championship</t>
   </si>
   <si>
@@ -3122,139 +3173,190 @@
     <t>https://fbref.com/en/matches/024b1e2d/Plymouth-Argyle-Sheffield-United-April-12-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/59456b0e/Sheffield-Wednesday-Oxford-United-April-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ffcc7041/Portsmouth-Derby-County-April-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d223e752/Queens-Park-Rangers-Bristol-City-April-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/65f40457/West-Bromwich-Albion-Watford-April-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/bfa310fb/Luton-Town-Blackburn-Rovers-April-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/4fe28233/Cardiff-City-Stoke-City-April-12-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/48133119/Sunderland-Swansea-City-April-12-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/4fe28233/Cardiff-City-Stoke-City-April-12-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/59456b0e/Sheffield-Wednesday-Oxford-United-April-12-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/65f40457/West-Bromwich-Albion-Watford-April-12-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/02f0ebee/Millwall-Middlesbrough-April-12-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/ffcc7041/Portsmouth-Derby-County-April-12-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/bfa310fb/Luton-Town-Blackburn-Rovers-April-12-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/d223e752/Queens-Park-Rangers-Bristol-City-April-12-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/d7a15a0d/Hull-City-Coventry-City-April-14-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/9dbd2be7/Derby-County-Luton-Town-April-18-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/2c584b14/Bristol-City-Sunderland-April-18-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/359b9b8f/Preston-North-End-Queens-Park-Rangers-April-18-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fb8a56f6/Swansea-City-Hull-City-April-18-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3fa3fbcb/Coventry-City-West-Bromwich-Albion-April-18-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/b3c9fe09/Blackburn-Rovers-Millwall-April-18-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/459d9f88/Middlesbrough-Plymouth-Argyle-April-18-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/8d986475/Norwich-City-Portsmouth-April-18-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/459d9f88/Middlesbrough-Plymouth-Argyle-April-18-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/4b2f813d/Watford-Burnley-April-18-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/b3c9fe09/Blackburn-Rovers-Millwall-April-18-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/3fa3fbcb/Coventry-City-West-Bromwich-Albion-April-18-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/e9422481/Stoke-City-Sheffield-Wednesday-April-18-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/fb8a56f6/Swansea-City-Hull-City-April-18-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/359b9b8f/Preston-North-End-Queens-Park-Rangers-April-18-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/2c584b14/Bristol-City-Sunderland-April-18-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/434b2e5d/Sheffield-United-Cardiff-City-April-18-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/799c9a7e/Oxford-United-Leeds-United-April-18-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/c1fddb70/Sheffield-Wednesday-Middlesbrough-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5fbd1555/West-Bromwich-Albion-Derby-County-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/a9dad4df/Queens-Park-Rangers-Swansea-City-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5222ce24/Leeds-United-Stoke-City-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/5139d9b9/Cardiff-City-Oxford-United-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/50cb5210/Portsmouth-Watford-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/f68c4ec2/Plymouth-Argyle-Coventry-City-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/252bc206/Millwall-Norwich-City-April-21-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/04eac7b9/Luton-Town-Bristol-City-April-21-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/83fd7cc8/Hull-City-Preston-North-End-April-21-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/04eac7b9/Luton-Town-Bristol-City-April-21-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/f68c4ec2/Plymouth-Argyle-Coventry-City-April-21-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/50cb5210/Portsmouth-Watford-April-21-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/5139d9b9/Cardiff-City-Oxford-United-April-21-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/5222ce24/Leeds-United-Stoke-City-April-21-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/adc899d6/Sunderland-Blackburn-Rovers-April-21-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/5fbd1555/West-Bromwich-Albion-Derby-County-April-21-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/c1fddb70/Sheffield-Wednesday-Middlesbrough-April-21-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/252bc206/Millwall-Norwich-City-April-21-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/a9dad4df/Queens-Park-Rangers-Swansea-City-April-21-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/0e3f9629/Burnley-Sheffield-United-April-21-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/6bacbea4/Stoke-City-Sheffield-United-April-25-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/70d9d49b/Queens-Park-Rangers-Burnley-April-26-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/da258a5f/Luton-Town-Coventry-City-April-26-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/70d9d49b/Queens-Park-Rangers-Burnley-April-26-2025-Championship</t>
+    <t>https://fbref.com/en/matches/9a3324af/Sheffield-Wednesday-Portsmouth-April-26-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/96820f6e/Preston-North-End-Plymouth-Argyle-April-26-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/eecd5fc9/Millwall-Swansea-City-April-26-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/89fcfad9/Oxford-United-Sunderland-April-26-2025-Championship</t>
   </si>
   <si>
     <t>https://fbref.com/en/matches/bd8b1982/Middlesbrough-Norwich-City-April-26-2025-Championship</t>
   </si>
   <si>
+    <t>https://fbref.com/en/matches/ca192ba8/Cardiff-City-West-Bromwich-Albion-April-26-2025-Championship</t>
+  </si>
+  <si>
     <t>https://fbref.com/en/matches/8c23c086/Blackburn-Rovers-Watford-April-26-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/89fcfad9/Oxford-United-Sunderland-April-26-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/96820f6e/Preston-North-End-Plymouth-Argyle-April-26-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/ca192ba8/Cardiff-City-West-Bromwich-Albion-April-26-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/6c4af4ab/Hull-City-Derby-County-April-26-2025-Championship</t>
   </si>
   <si>
-    <t>https://fbref.com/en/matches/9a3324af/Sheffield-Wednesday-Portsmouth-April-26-2025-Championship</t>
-  </si>
-  <si>
-    <t>https://fbref.com/en/matches/eecd5fc9/Millwall-Swansea-City-April-26-2025-Championship</t>
-  </si>
-  <si>
     <t>https://fbref.com/en/matches/ad54bd5e/Leeds-United-Bristol-City-April-28-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/44858abe/Sunderland-Queens-Park-Rangers-May-3-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d1666f71/Norwich-City-Cardiff-City-May-3-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fde8f30c/West-Bromwich-Albion-Luton-Town-May-3-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c4ab6716/Coventry-City-Middlesbrough-May-3-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/ff577a9b/Burnley-Millwall-May-3-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/17319531/Portsmouth-Hull-City-May-3-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c4056ff0/Bristol-City-Preston-North-End-May-3-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/c11b178f/Derby-County-Stoke-City-May-3-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/3edc57d8/Watford-Sheffield-Wednesday-May-3-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/aefbaaee/Sheffield-United-Blackburn-Rovers-May-3-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/9191b12e/Plymouth-Argyle-Leeds-United-May-3-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/edafdbee/Swansea-City-Oxford-United-May-3-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/6c9274e2/Bristol-City-Sheffield-United-May-8-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/fda378a2/Coventry-City-Sunderland-May-9-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/1b2e1d19/Sheffield-United-Bristol-City-May-12-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/cb8405b4/Sunderland-Coventry-City-May-13-2025-Championship</t>
+  </si>
+  <si>
+    <t>https://fbref.com/en/matches/d9d93103/Sheffield-United-Sunderland-May-24-2025-Championship</t>
   </si>
 </sst>
 </file>
@@ -3313,7 +3415,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>541</v>
+        <v>558</v>
       </c>
     </row>
     <row r="3">
@@ -3321,7 +3423,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>542</v>
+        <v>559</v>
       </c>
     </row>
     <row r="4">
@@ -3329,7 +3431,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>543</v>
+        <v>560</v>
       </c>
     </row>
     <row r="5">
@@ -3337,7 +3439,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>544</v>
+        <v>561</v>
       </c>
     </row>
     <row r="6">
@@ -3345,7 +3447,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>545</v>
+        <v>562</v>
       </c>
     </row>
     <row r="7">
@@ -3353,7 +3455,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>546</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
@@ -3361,7 +3463,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>547</v>
+        <v>564</v>
       </c>
     </row>
     <row r="9">
@@ -3369,7 +3471,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>548</v>
+        <v>565</v>
       </c>
     </row>
     <row r="10">
@@ -3377,7 +3479,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>549</v>
+        <v>566</v>
       </c>
     </row>
     <row r="11">
@@ -3385,7 +3487,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>550</v>
+        <v>567</v>
       </c>
     </row>
     <row r="12">
@@ -3393,7 +3495,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>551</v>
+        <v>568</v>
       </c>
     </row>
     <row r="13">
@@ -3401,7 +3503,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>552</v>
+        <v>569</v>
       </c>
     </row>
     <row r="14">
@@ -3409,7 +3511,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>553</v>
+        <v>570</v>
       </c>
     </row>
     <row r="15">
@@ -3417,7 +3519,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>554</v>
+        <v>571</v>
       </c>
     </row>
     <row r="16">
@@ -3425,7 +3527,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>555</v>
+        <v>572</v>
       </c>
     </row>
     <row r="17">
@@ -3433,7 +3535,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
     </row>
     <row r="18">
@@ -3441,7 +3543,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>557</v>
+        <v>574</v>
       </c>
     </row>
     <row r="19">
@@ -3449,7 +3551,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>558</v>
+        <v>575</v>
       </c>
     </row>
     <row r="20">
@@ -3457,7 +3559,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>559</v>
+        <v>576</v>
       </c>
     </row>
     <row r="21">
@@ -3465,7 +3567,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>560</v>
+        <v>577</v>
       </c>
     </row>
     <row r="22">
@@ -3473,7 +3575,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>561</v>
+        <v>578</v>
       </c>
     </row>
     <row r="23">
@@ -3481,7 +3583,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>562</v>
+        <v>579</v>
       </c>
     </row>
     <row r="24">
@@ -3489,7 +3591,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>563</v>
+        <v>580</v>
       </c>
     </row>
     <row r="25">
@@ -3497,7 +3599,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>564</v>
+        <v>581</v>
       </c>
     </row>
     <row r="26">
@@ -3505,7 +3607,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>565</v>
+        <v>582</v>
       </c>
     </row>
     <row r="27">
@@ -3513,7 +3615,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>566</v>
+        <v>583</v>
       </c>
     </row>
     <row r="28">
@@ -3521,7 +3623,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>567</v>
+        <v>584</v>
       </c>
     </row>
     <row r="29">
@@ -3529,7 +3631,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
     </row>
     <row r="30">
@@ -3537,7 +3639,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>569</v>
+        <v>586</v>
       </c>
     </row>
     <row r="31">
@@ -3545,7 +3647,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>570</v>
+        <v>587</v>
       </c>
     </row>
     <row r="32">
@@ -3553,7 +3655,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
     </row>
     <row r="33">
@@ -3561,7 +3663,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
     </row>
     <row r="34">
@@ -3569,7 +3671,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>573</v>
+        <v>590</v>
       </c>
     </row>
     <row r="35">
@@ -3577,7 +3679,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
     </row>
     <row r="36">
@@ -3585,7 +3687,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="37">
@@ -3593,7 +3695,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
     </row>
     <row r="38">
@@ -3601,7 +3703,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>577</v>
+        <v>594</v>
       </c>
     </row>
     <row r="39">
@@ -3609,7 +3711,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
     </row>
     <row r="40">
@@ -3617,7 +3719,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
     </row>
     <row r="41">
@@ -3625,7 +3727,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>580</v>
+        <v>597</v>
       </c>
     </row>
     <row r="42">
@@ -3633,7 +3735,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
     </row>
     <row r="43">
@@ -3641,7 +3743,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>582</v>
+        <v>599</v>
       </c>
     </row>
     <row r="44">
@@ -3649,7 +3751,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>583</v>
+        <v>600</v>
       </c>
     </row>
     <row r="45">
@@ -3657,7 +3759,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>584</v>
+        <v>601</v>
       </c>
     </row>
     <row r="46">
@@ -3665,7 +3767,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>585</v>
+        <v>602</v>
       </c>
     </row>
     <row r="47">
@@ -3673,7 +3775,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
     </row>
     <row r="48">
@@ -3681,7 +3783,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>587</v>
+        <v>604</v>
       </c>
     </row>
     <row r="49">
@@ -3689,7 +3791,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>588</v>
+        <v>605</v>
       </c>
     </row>
     <row r="50">
@@ -3697,7 +3799,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>589</v>
+        <v>606</v>
       </c>
     </row>
     <row r="51">
@@ -3705,7 +3807,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>590</v>
+        <v>607</v>
       </c>
     </row>
     <row r="52">
@@ -3713,7 +3815,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>591</v>
+        <v>608</v>
       </c>
     </row>
     <row r="53">
@@ -3721,7 +3823,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>592</v>
+        <v>609</v>
       </c>
     </row>
     <row r="54">
@@ -3729,7 +3831,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>593</v>
+        <v>610</v>
       </c>
     </row>
     <row r="55">
@@ -3737,7 +3839,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>594</v>
+        <v>611</v>
       </c>
     </row>
     <row r="56">
@@ -3745,7 +3847,7 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>595</v>
+        <v>612</v>
       </c>
     </row>
     <row r="57">
@@ -3753,7 +3855,7 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
     </row>
     <row r="58">
@@ -3761,7 +3863,7 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>597</v>
+        <v>614</v>
       </c>
     </row>
     <row r="59">
@@ -3769,7 +3871,7 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>598</v>
+        <v>615</v>
       </c>
     </row>
     <row r="60">
@@ -3777,7 +3879,7 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>599</v>
+        <v>616</v>
       </c>
     </row>
     <row r="61">
@@ -3785,7 +3887,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>600</v>
+        <v>617</v>
       </c>
     </row>
     <row r="62">
@@ -3793,7 +3895,7 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>601</v>
+        <v>618</v>
       </c>
     </row>
     <row r="63">
@@ -3801,7 +3903,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>602</v>
+        <v>619</v>
       </c>
     </row>
     <row r="64">
@@ -3809,7 +3911,7 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>603</v>
+        <v>620</v>
       </c>
     </row>
     <row r="65">
@@ -3817,7 +3919,7 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>604</v>
+        <v>621</v>
       </c>
     </row>
     <row r="66">
@@ -3825,7 +3927,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>605</v>
+        <v>622</v>
       </c>
     </row>
     <row r="67">
@@ -3833,7 +3935,7 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>606</v>
+        <v>623</v>
       </c>
     </row>
     <row r="68">
@@ -3841,7 +3943,7 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>607</v>
+        <v>624</v>
       </c>
     </row>
     <row r="69">
@@ -3849,7 +3951,7 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>608</v>
+        <v>625</v>
       </c>
     </row>
     <row r="70">
@@ -3857,7 +3959,7 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>609</v>
+        <v>626</v>
       </c>
     </row>
     <row r="71">
@@ -3865,7 +3967,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>610</v>
+        <v>627</v>
       </c>
     </row>
     <row r="72">
@@ -3873,7 +3975,7 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>611</v>
+        <v>628</v>
       </c>
     </row>
     <row r="73">
@@ -3881,7 +3983,7 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>612</v>
+        <v>629</v>
       </c>
     </row>
     <row r="74">
@@ -3889,7 +3991,7 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>613</v>
+        <v>630</v>
       </c>
     </row>
     <row r="75">
@@ -3897,7 +3999,7 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>614</v>
+        <v>631</v>
       </c>
     </row>
     <row r="76">
@@ -3905,7 +4007,7 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>615</v>
+        <v>632</v>
       </c>
     </row>
     <row r="77">
@@ -3913,7 +4015,7 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>616</v>
+        <v>633</v>
       </c>
     </row>
     <row r="78">
@@ -3921,7 +4023,7 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>617</v>
+        <v>634</v>
       </c>
     </row>
     <row r="79">
@@ -3929,7 +4031,7 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
     </row>
     <row r="80">
@@ -3937,7 +4039,7 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>619</v>
+        <v>636</v>
       </c>
     </row>
     <row r="81">
@@ -3945,7 +4047,7 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>620</v>
+        <v>637</v>
       </c>
     </row>
     <row r="82">
@@ -3953,7 +4055,7 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
     </row>
     <row r="83">
@@ -3961,7 +4063,7 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
     </row>
     <row r="84">
@@ -3969,7 +4071,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="85">
@@ -3977,7 +4079,7 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
     </row>
     <row r="86">
@@ -3985,7 +4087,7 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
     </row>
     <row r="87">
@@ -3993,7 +4095,7 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="88">
@@ -4001,7 +4103,7 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="89">
@@ -4009,7 +4111,7 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
     </row>
     <row r="90">
@@ -4017,7 +4119,7 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
     </row>
     <row r="91">
@@ -4025,7 +4127,7 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
     </row>
     <row r="92">
@@ -4033,7 +4135,7 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>631</v>
+        <v>648</v>
       </c>
     </row>
     <row r="93">
@@ -4041,7 +4143,7 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
     </row>
     <row r="94">
@@ -4049,7 +4151,7 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>633</v>
+        <v>650</v>
       </c>
     </row>
     <row r="95">
@@ -4057,7 +4159,7 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>634</v>
+        <v>651</v>
       </c>
     </row>
     <row r="96">
@@ -4065,7 +4167,7 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>635</v>
+        <v>652</v>
       </c>
     </row>
     <row r="97">
@@ -4073,7 +4175,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>636</v>
+        <v>653</v>
       </c>
     </row>
     <row r="98">
@@ -4081,7 +4183,7 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>637</v>
+        <v>654</v>
       </c>
     </row>
     <row r="99">
@@ -4089,7 +4191,7 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>638</v>
+        <v>655</v>
       </c>
     </row>
     <row r="100">
@@ -4097,7 +4199,7 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>639</v>
+        <v>656</v>
       </c>
     </row>
     <row r="101">
@@ -4105,7 +4207,7 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>640</v>
+        <v>657</v>
       </c>
     </row>
     <row r="102">
@@ -4113,7 +4215,7 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>641</v>
+        <v>658</v>
       </c>
     </row>
     <row r="103">
@@ -4121,7 +4223,7 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>642</v>
+        <v>659</v>
       </c>
     </row>
     <row r="104">
@@ -4129,7 +4231,7 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>643</v>
+        <v>660</v>
       </c>
     </row>
     <row r="105">
@@ -4137,7 +4239,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>644</v>
+        <v>661</v>
       </c>
     </row>
     <row r="106">
@@ -4145,7 +4247,7 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>645</v>
+        <v>662</v>
       </c>
     </row>
     <row r="107">
@@ -4153,7 +4255,7 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>646</v>
+        <v>663</v>
       </c>
     </row>
     <row r="108">
@@ -4161,7 +4263,7 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>647</v>
+        <v>664</v>
       </c>
     </row>
     <row r="109">
@@ -4169,7 +4271,7 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>648</v>
+        <v>665</v>
       </c>
     </row>
     <row r="110">
@@ -4177,7 +4279,7 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>649</v>
+        <v>666</v>
       </c>
     </row>
     <row r="111">
@@ -4185,7 +4287,7 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>650</v>
+        <v>667</v>
       </c>
     </row>
     <row r="112">
@@ -4193,7 +4295,7 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>651</v>
+        <v>668</v>
       </c>
     </row>
     <row r="113">
@@ -4201,7 +4303,7 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>652</v>
+        <v>669</v>
       </c>
     </row>
     <row r="114">
@@ -4209,7 +4311,7 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
     </row>
     <row r="115">
@@ -4217,7 +4319,7 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>654</v>
+        <v>671</v>
       </c>
     </row>
     <row r="116">
@@ -4225,7 +4327,7 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>655</v>
+        <v>672</v>
       </c>
     </row>
     <row r="117">
@@ -4233,7 +4335,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
     </row>
     <row r="118">
@@ -4241,7 +4343,7 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>657</v>
+        <v>674</v>
       </c>
     </row>
     <row r="119">
@@ -4249,7 +4351,7 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>658</v>
+        <v>675</v>
       </c>
     </row>
     <row r="120">
@@ -4257,7 +4359,7 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>659</v>
+        <v>676</v>
       </c>
     </row>
     <row r="121">
@@ -4265,7 +4367,7 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>660</v>
+        <v>677</v>
       </c>
     </row>
     <row r="122">
@@ -4273,7 +4375,7 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>661</v>
+        <v>678</v>
       </c>
     </row>
     <row r="123">
@@ -4281,7 +4383,7 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>662</v>
+        <v>679</v>
       </c>
     </row>
     <row r="124">
@@ -4289,7 +4391,7 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>663</v>
+        <v>680</v>
       </c>
     </row>
     <row r="125">
@@ -4297,7 +4399,7 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>664</v>
+        <v>681</v>
       </c>
     </row>
     <row r="126">
@@ -4305,7 +4407,7 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>665</v>
+        <v>682</v>
       </c>
     </row>
     <row r="127">
@@ -4313,7 +4415,7 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>666</v>
+        <v>683</v>
       </c>
     </row>
     <row r="128">
@@ -4321,7 +4423,7 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>667</v>
+        <v>684</v>
       </c>
     </row>
     <row r="129">
@@ -4329,7 +4431,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>668</v>
+        <v>685</v>
       </c>
     </row>
     <row r="130">
@@ -4337,7 +4439,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>669</v>
+        <v>686</v>
       </c>
     </row>
     <row r="131">
@@ -4345,7 +4447,7 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>670</v>
+        <v>687</v>
       </c>
     </row>
     <row r="132">
@@ -4353,7 +4455,7 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>671</v>
+        <v>688</v>
       </c>
     </row>
     <row r="133">
@@ -4361,7 +4463,7 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>672</v>
+        <v>689</v>
       </c>
     </row>
     <row r="134">
@@ -4369,7 +4471,7 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>673</v>
+        <v>690</v>
       </c>
     </row>
     <row r="135">
@@ -4377,7 +4479,7 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>674</v>
+        <v>691</v>
       </c>
     </row>
     <row r="136">
@@ -4385,7 +4487,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>675</v>
+        <v>692</v>
       </c>
     </row>
     <row r="137">
@@ -4393,7 +4495,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>676</v>
+        <v>693</v>
       </c>
     </row>
     <row r="138">
@@ -4401,7 +4503,7 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>677</v>
+        <v>694</v>
       </c>
     </row>
     <row r="139">
@@ -4409,7 +4511,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>678</v>
+        <v>695</v>
       </c>
     </row>
     <row r="140">
@@ -4417,7 +4519,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
     </row>
     <row r="141">
@@ -4425,7 +4527,7 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>680</v>
+        <v>697</v>
       </c>
     </row>
     <row r="142">
@@ -4433,7 +4535,7 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>681</v>
+        <v>698</v>
       </c>
     </row>
     <row r="143">
@@ -4441,7 +4543,7 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>682</v>
+        <v>699</v>
       </c>
     </row>
     <row r="144">
@@ -4449,7 +4551,7 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>683</v>
+        <v>700</v>
       </c>
     </row>
     <row r="145">
@@ -4457,7 +4559,7 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>684</v>
+        <v>701</v>
       </c>
     </row>
     <row r="146">
@@ -4465,7 +4567,7 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>685</v>
+        <v>702</v>
       </c>
     </row>
     <row r="147">
@@ -4473,7 +4575,7 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>686</v>
+        <v>703</v>
       </c>
     </row>
     <row r="148">
@@ -4481,7 +4583,7 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>687</v>
+        <v>704</v>
       </c>
     </row>
     <row r="149">
@@ -4489,7 +4591,7 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>688</v>
+        <v>705</v>
       </c>
     </row>
     <row r="150">
@@ -4497,7 +4599,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>689</v>
+        <v>706</v>
       </c>
     </row>
     <row r="151">
@@ -4505,7 +4607,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>690</v>
+        <v>707</v>
       </c>
     </row>
     <row r="152">
@@ -4513,7 +4615,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>691</v>
+        <v>708</v>
       </c>
     </row>
     <row r="153">
@@ -4521,7 +4623,7 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>692</v>
+        <v>709</v>
       </c>
     </row>
     <row r="154">
@@ -4529,7 +4631,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>693</v>
+        <v>710</v>
       </c>
     </row>
     <row r="155">
@@ -4537,7 +4639,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>694</v>
+        <v>711</v>
       </c>
     </row>
     <row r="156">
@@ -4545,7 +4647,7 @@
         <v>155</v>
       </c>
       <c r="B156" t="s">
-        <v>695</v>
+        <v>712</v>
       </c>
     </row>
     <row r="157">
@@ -4553,7 +4655,7 @@
         <v>156</v>
       </c>
       <c r="B157" t="s">
-        <v>696</v>
+        <v>713</v>
       </c>
     </row>
     <row r="158">
@@ -4561,7 +4663,7 @@
         <v>157</v>
       </c>
       <c r="B158" t="s">
-        <v>697</v>
+        <v>714</v>
       </c>
     </row>
     <row r="159">
@@ -4569,7 +4671,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>698</v>
+        <v>715</v>
       </c>
     </row>
     <row r="160">
@@ -4577,7 +4679,7 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
-        <v>699</v>
+        <v>716</v>
       </c>
     </row>
     <row r="161">
@@ -4585,7 +4687,7 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
-        <v>700</v>
+        <v>717</v>
       </c>
     </row>
     <row r="162">
@@ -4593,7 +4695,7 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
-        <v>701</v>
+        <v>718</v>
       </c>
     </row>
     <row r="163">
@@ -4601,7 +4703,7 @@
         <v>162</v>
       </c>
       <c r="B163" t="s">
-        <v>702</v>
+        <v>719</v>
       </c>
     </row>
     <row r="164">
@@ -4609,7 +4711,7 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>703</v>
+        <v>720</v>
       </c>
     </row>
     <row r="165">
@@ -4617,7 +4719,7 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>704</v>
+        <v>721</v>
       </c>
     </row>
     <row r="166">
@@ -4625,7 +4727,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>705</v>
+        <v>722</v>
       </c>
     </row>
     <row r="167">
@@ -4633,7 +4735,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>706</v>
+        <v>723</v>
       </c>
     </row>
     <row r="168">
@@ -4641,7 +4743,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>707</v>
+        <v>724</v>
       </c>
     </row>
     <row r="169">
@@ -4649,7 +4751,7 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>708</v>
+        <v>725</v>
       </c>
     </row>
     <row r="170">
@@ -4657,7 +4759,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>709</v>
+        <v>726</v>
       </c>
     </row>
     <row r="171">
@@ -4665,7 +4767,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>710</v>
+        <v>727</v>
       </c>
     </row>
     <row r="172">
@@ -4673,7 +4775,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>711</v>
+        <v>728</v>
       </c>
     </row>
     <row r="173">
@@ -4681,7 +4783,7 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>712</v>
+        <v>729</v>
       </c>
     </row>
     <row r="174">
@@ -4689,7 +4791,7 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>713</v>
+        <v>730</v>
       </c>
     </row>
     <row r="175">
@@ -4697,7 +4799,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>714</v>
+        <v>731</v>
       </c>
     </row>
     <row r="176">
@@ -4705,7 +4807,7 @@
         <v>175</v>
       </c>
       <c r="B176" t="s">
-        <v>715</v>
+        <v>732</v>
       </c>
     </row>
     <row r="177">
@@ -4713,7 +4815,7 @@
         <v>176</v>
       </c>
       <c r="B177" t="s">
-        <v>716</v>
+        <v>733</v>
       </c>
     </row>
     <row r="178">
@@ -4721,7 +4823,7 @@
         <v>177</v>
       </c>
       <c r="B178" t="s">
-        <v>717</v>
+        <v>734</v>
       </c>
     </row>
     <row r="179">
@@ -4729,7 +4831,7 @@
         <v>178</v>
       </c>
       <c r="B179" t="s">
-        <v>718</v>
+        <v>735</v>
       </c>
     </row>
     <row r="180">
@@ -4737,7 +4839,7 @@
         <v>179</v>
       </c>
       <c r="B180" t="s">
-        <v>719</v>
+        <v>736</v>
       </c>
     </row>
     <row r="181">
@@ -4745,7 +4847,7 @@
         <v>180</v>
       </c>
       <c r="B181" t="s">
-        <v>720</v>
+        <v>737</v>
       </c>
     </row>
     <row r="182">
@@ -4753,7 +4855,7 @@
         <v>181</v>
       </c>
       <c r="B182" t="s">
-        <v>721</v>
+        <v>738</v>
       </c>
     </row>
     <row r="183">
@@ -4761,7 +4863,7 @@
         <v>182</v>
       </c>
       <c r="B183" t="s">
-        <v>722</v>
+        <v>739</v>
       </c>
     </row>
     <row r="184">
@@ -4769,7 +4871,7 @@
         <v>183</v>
       </c>
       <c r="B184" t="s">
-        <v>723</v>
+        <v>740</v>
       </c>
     </row>
     <row r="185">
@@ -4777,7 +4879,7 @@
         <v>184</v>
       </c>
       <c r="B185" t="s">
-        <v>724</v>
+        <v>741</v>
       </c>
     </row>
     <row r="186">
@@ -4785,7 +4887,7 @@
         <v>185</v>
       </c>
       <c r="B186" t="s">
-        <v>725</v>
+        <v>742</v>
       </c>
     </row>
     <row r="187">
@@ -4793,7 +4895,7 @@
         <v>186</v>
       </c>
       <c r="B187" t="s">
-        <v>726</v>
+        <v>743</v>
       </c>
     </row>
     <row r="188">
@@ -4801,7 +4903,7 @@
         <v>187</v>
       </c>
       <c r="B188" t="s">
-        <v>727</v>
+        <v>744</v>
       </c>
     </row>
     <row r="189">
@@ -4809,7 +4911,7 @@
         <v>188</v>
       </c>
       <c r="B189" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
     </row>
     <row r="190">
@@ -4817,7 +4919,7 @@
         <v>189</v>
       </c>
       <c r="B190" t="s">
-        <v>729</v>
+        <v>746</v>
       </c>
     </row>
     <row r="191">
@@ -4825,7 +4927,7 @@
         <v>190</v>
       </c>
       <c r="B191" t="s">
-        <v>730</v>
+        <v>747</v>
       </c>
     </row>
     <row r="192">
@@ -4833,7 +4935,7 @@
         <v>191</v>
       </c>
       <c r="B192" t="s">
-        <v>731</v>
+        <v>748</v>
       </c>
     </row>
     <row r="193">
@@ -4841,7 +4943,7 @@
         <v>192</v>
       </c>
       <c r="B193" t="s">
-        <v>732</v>
+        <v>749</v>
       </c>
     </row>
     <row r="194">
@@ -4849,7 +4951,7 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
-        <v>733</v>
+        <v>750</v>
       </c>
     </row>
     <row r="195">
@@ -4857,7 +4959,7 @@
         <v>194</v>
       </c>
       <c r="B195" t="s">
-        <v>734</v>
+        <v>751</v>
       </c>
     </row>
     <row r="196">
@@ -4865,7 +4967,7 @@
         <v>195</v>
       </c>
       <c r="B196" t="s">
-        <v>735</v>
+        <v>752</v>
       </c>
     </row>
     <row r="197">
@@ -4873,7 +4975,7 @@
         <v>196</v>
       </c>
       <c r="B197" t="s">
-        <v>736</v>
+        <v>753</v>
       </c>
     </row>
     <row r="198">
@@ -4881,7 +4983,7 @@
         <v>197</v>
       </c>
       <c r="B198" t="s">
-        <v>737</v>
+        <v>754</v>
       </c>
     </row>
     <row r="199">
@@ -4889,7 +4991,7 @@
         <v>198</v>
       </c>
       <c r="B199" t="s">
-        <v>738</v>
+        <v>755</v>
       </c>
     </row>
     <row r="200">
@@ -4897,7 +4999,7 @@
         <v>199</v>
       </c>
       <c r="B200" t="s">
-        <v>739</v>
+        <v>756</v>
       </c>
     </row>
     <row r="201">
@@ -4905,7 +5007,7 @@
         <v>200</v>
       </c>
       <c r="B201" t="s">
-        <v>740</v>
+        <v>757</v>
       </c>
     </row>
     <row r="202">
@@ -4913,7 +5015,7 @@
         <v>201</v>
       </c>
       <c r="B202" t="s">
-        <v>741</v>
+        <v>758</v>
       </c>
     </row>
     <row r="203">
@@ -4921,7 +5023,7 @@
         <v>202</v>
       </c>
       <c r="B203" t="s">
-        <v>742</v>
+        <v>759</v>
       </c>
     </row>
     <row r="204">
@@ -4929,7 +5031,7 @@
         <v>203</v>
       </c>
       <c r="B204" t="s">
-        <v>743</v>
+        <v>760</v>
       </c>
     </row>
     <row r="205">
@@ -4937,7 +5039,7 @@
         <v>204</v>
       </c>
       <c r="B205" t="s">
-        <v>744</v>
+        <v>761</v>
       </c>
     </row>
     <row r="206">
@@ -4945,7 +5047,7 @@
         <v>205</v>
       </c>
       <c r="B206" t="s">
-        <v>745</v>
+        <v>762</v>
       </c>
     </row>
     <row r="207">
@@ -4953,7 +5055,7 @@
         <v>206</v>
       </c>
       <c r="B207" t="s">
-        <v>746</v>
+        <v>763</v>
       </c>
     </row>
     <row r="208">
@@ -4961,7 +5063,7 @@
         <v>207</v>
       </c>
       <c r="B208" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
     </row>
     <row r="209">
@@ -4969,7 +5071,7 @@
         <v>208</v>
       </c>
       <c r="B209" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
     </row>
     <row r="210">
@@ -4977,7 +5079,7 @@
         <v>209</v>
       </c>
       <c r="B210" t="s">
-        <v>749</v>
+        <v>766</v>
       </c>
     </row>
     <row r="211">
@@ -4985,7 +5087,7 @@
         <v>210</v>
       </c>
       <c r="B211" t="s">
-        <v>750</v>
+        <v>767</v>
       </c>
     </row>
     <row r="212">
@@ -4993,7 +5095,7 @@
         <v>211</v>
       </c>
       <c r="B212" t="s">
-        <v>751</v>
+        <v>768</v>
       </c>
     </row>
     <row r="213">
@@ -5001,7 +5103,7 @@
         <v>212</v>
       </c>
       <c r="B213" t="s">
-        <v>752</v>
+        <v>769</v>
       </c>
     </row>
     <row r="214">
@@ -5009,7 +5111,7 @@
         <v>213</v>
       </c>
       <c r="B214" t="s">
-        <v>753</v>
+        <v>770</v>
       </c>
     </row>
     <row r="215">
@@ -5017,7 +5119,7 @@
         <v>214</v>
       </c>
       <c r="B215" t="s">
-        <v>754</v>
+        <v>771</v>
       </c>
     </row>
     <row r="216">
@@ -5025,7 +5127,7 @@
         <v>215</v>
       </c>
       <c r="B216" t="s">
-        <v>755</v>
+        <v>772</v>
       </c>
     </row>
     <row r="217">
@@ -5033,7 +5135,7 @@
         <v>216</v>
       </c>
       <c r="B217" t="s">
-        <v>756</v>
+        <v>773</v>
       </c>
     </row>
     <row r="218">
@@ -5041,7 +5143,7 @@
         <v>217</v>
       </c>
       <c r="B218" t="s">
-        <v>757</v>
+        <v>774</v>
       </c>
     </row>
     <row r="219">
@@ -5049,7 +5151,7 @@
         <v>218</v>
       </c>
       <c r="B219" t="s">
-        <v>758</v>
+        <v>775</v>
       </c>
     </row>
     <row r="220">
@@ -5057,7 +5159,7 @@
         <v>219</v>
       </c>
       <c r="B220" t="s">
-        <v>759</v>
+        <v>776</v>
       </c>
     </row>
     <row r="221">
@@ -5065,7 +5167,7 @@
         <v>220</v>
       </c>
       <c r="B221" t="s">
-        <v>760</v>
+        <v>777</v>
       </c>
     </row>
     <row r="222">
@@ -5073,7 +5175,7 @@
         <v>221</v>
       </c>
       <c r="B222" t="s">
-        <v>761</v>
+        <v>778</v>
       </c>
     </row>
     <row r="223">
@@ -5081,7 +5183,7 @@
         <v>222</v>
       </c>
       <c r="B223" t="s">
-        <v>762</v>
+        <v>779</v>
       </c>
     </row>
     <row r="224">
@@ -5089,7 +5191,7 @@
         <v>223</v>
       </c>
       <c r="B224" t="s">
-        <v>763</v>
+        <v>780</v>
       </c>
     </row>
     <row r="225">
@@ -5097,7 +5199,7 @@
         <v>224</v>
       </c>
       <c r="B225" t="s">
-        <v>764</v>
+        <v>781</v>
       </c>
     </row>
     <row r="226">
@@ -5105,7 +5207,7 @@
         <v>225</v>
       </c>
       <c r="B226" t="s">
-        <v>765</v>
+        <v>782</v>
       </c>
     </row>
     <row r="227">
@@ -5113,7 +5215,7 @@
         <v>226</v>
       </c>
       <c r="B227" t="s">
-        <v>766</v>
+        <v>783</v>
       </c>
     </row>
     <row r="228">
@@ -5121,7 +5223,7 @@
         <v>227</v>
       </c>
       <c r="B228" t="s">
-        <v>767</v>
+        <v>784</v>
       </c>
     </row>
     <row r="229">
@@ -5129,7 +5231,7 @@
         <v>228</v>
       </c>
       <c r="B229" t="s">
-        <v>768</v>
+        <v>785</v>
       </c>
     </row>
     <row r="230">
@@ -5137,7 +5239,7 @@
         <v>229</v>
       </c>
       <c r="B230" t="s">
-        <v>769</v>
+        <v>786</v>
       </c>
     </row>
     <row r="231">
@@ -5145,7 +5247,7 @@
         <v>230</v>
       </c>
       <c r="B231" t="s">
-        <v>770</v>
+        <v>787</v>
       </c>
     </row>
     <row r="232">
@@ -5153,7 +5255,7 @@
         <v>231</v>
       </c>
       <c r="B232" t="s">
-        <v>771</v>
+        <v>788</v>
       </c>
     </row>
     <row r="233">
@@ -5161,7 +5263,7 @@
         <v>232</v>
       </c>
       <c r="B233" t="s">
-        <v>772</v>
+        <v>789</v>
       </c>
     </row>
     <row r="234">
@@ -5169,7 +5271,7 @@
         <v>233</v>
       </c>
       <c r="B234" t="s">
-        <v>773</v>
+        <v>790</v>
       </c>
     </row>
     <row r="235">
@@ -5177,7 +5279,7 @@
         <v>234</v>
       </c>
       <c r="B235" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
     </row>
     <row r="236">
@@ -5185,7 +5287,7 @@
         <v>235</v>
       </c>
       <c r="B236" t="s">
-        <v>775</v>
+        <v>792</v>
       </c>
     </row>
     <row r="237">
@@ -5193,7 +5295,7 @@
         <v>236</v>
       </c>
       <c r="B237" t="s">
-        <v>776</v>
+        <v>793</v>
       </c>
     </row>
     <row r="238">
@@ -5201,7 +5303,7 @@
         <v>237</v>
       </c>
       <c r="B238" t="s">
-        <v>777</v>
+        <v>794</v>
       </c>
     </row>
     <row r="239">
@@ -5209,7 +5311,7 @@
         <v>238</v>
       </c>
       <c r="B239" t="s">
-        <v>778</v>
+        <v>795</v>
       </c>
     </row>
     <row r="240">
@@ -5217,7 +5319,7 @@
         <v>239</v>
       </c>
       <c r="B240" t="s">
-        <v>779</v>
+        <v>796</v>
       </c>
     </row>
     <row r="241">
@@ -5225,7 +5327,7 @@
         <v>240</v>
       </c>
       <c r="B241" t="s">
-        <v>780</v>
+        <v>797</v>
       </c>
     </row>
     <row r="242">
@@ -5233,7 +5335,7 @@
         <v>241</v>
       </c>
       <c r="B242" t="s">
-        <v>781</v>
+        <v>798</v>
       </c>
     </row>
     <row r="243">
@@ -5241,7 +5343,7 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>782</v>
+        <v>799</v>
       </c>
     </row>
     <row r="244">
@@ -5249,7 +5351,7 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>783</v>
+        <v>800</v>
       </c>
     </row>
     <row r="245">
@@ -5257,7 +5359,7 @@
         <v>244</v>
       </c>
       <c r="B245" t="s">
-        <v>784</v>
+        <v>801</v>
       </c>
     </row>
     <row r="246">
@@ -5265,7 +5367,7 @@
         <v>245</v>
       </c>
       <c r="B246" t="s">
-        <v>785</v>
+        <v>802</v>
       </c>
     </row>
     <row r="247">
@@ -5273,7 +5375,7 @@
         <v>246</v>
       </c>
       <c r="B247" t="s">
-        <v>786</v>
+        <v>803</v>
       </c>
     </row>
     <row r="248">
@@ -5281,7 +5383,7 @@
         <v>247</v>
       </c>
       <c r="B248" t="s">
-        <v>787</v>
+        <v>804</v>
       </c>
     </row>
     <row r="249">
@@ -5289,7 +5391,7 @@
         <v>248</v>
       </c>
       <c r="B249" t="s">
-        <v>788</v>
+        <v>805</v>
       </c>
     </row>
     <row r="250">
@@ -5297,7 +5399,7 @@
         <v>249</v>
       </c>
       <c r="B250" t="s">
-        <v>789</v>
+        <v>806</v>
       </c>
     </row>
     <row r="251">
@@ -5305,7 +5407,7 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
-        <v>790</v>
+        <v>807</v>
       </c>
     </row>
     <row r="252">
@@ -5313,7 +5415,7 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
-        <v>791</v>
+        <v>808</v>
       </c>
     </row>
     <row r="253">
@@ -5321,7 +5423,7 @@
         <v>252</v>
       </c>
       <c r="B253" t="s">
-        <v>792</v>
+        <v>809</v>
       </c>
     </row>
     <row r="254">
@@ -5329,7 +5431,7 @@
         <v>253</v>
       </c>
       <c r="B254" t="s">
-        <v>793</v>
+        <v>810</v>
       </c>
     </row>
     <row r="255">
@@ -5337,7 +5439,7 @@
         <v>254</v>
       </c>
       <c r="B255" t="s">
-        <v>794</v>
+        <v>811</v>
       </c>
     </row>
     <row r="256">
@@ -5345,7 +5447,7 @@
         <v>255</v>
       </c>
       <c r="B256" t="s">
-        <v>795</v>
+        <v>812</v>
       </c>
     </row>
     <row r="257">
@@ -5353,7 +5455,7 @@
         <v>256</v>
       </c>
       <c r="B257" t="s">
-        <v>796</v>
+        <v>813</v>
       </c>
     </row>
     <row r="258">
@@ -5361,7 +5463,7 @@
         <v>257</v>
       </c>
       <c r="B258" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
     </row>
     <row r="259">
@@ -5369,7 +5471,7 @@
         <v>258</v>
       </c>
       <c r="B259" t="s">
-        <v>798</v>
+        <v>815</v>
       </c>
     </row>
     <row r="260">
@@ -5377,7 +5479,7 @@
         <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>799</v>
+        <v>816</v>
       </c>
     </row>
     <row r="261">
@@ -5385,7 +5487,7 @@
         <v>260</v>
       </c>
       <c r="B261" t="s">
-        <v>800</v>
+        <v>817</v>
       </c>
     </row>
     <row r="262">
@@ -5393,7 +5495,7 @@
         <v>261</v>
       </c>
       <c r="B262" t="s">
-        <v>801</v>
+        <v>818</v>
       </c>
     </row>
     <row r="263">
@@ -5401,7 +5503,7 @@
         <v>262</v>
       </c>
       <c r="B263" t="s">
-        <v>802</v>
+        <v>819</v>
       </c>
     </row>
     <row r="264">
@@ -5409,7 +5511,7 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
-        <v>803</v>
+        <v>820</v>
       </c>
     </row>
     <row r="265">
@@ -5417,7 +5519,7 @@
         <v>264</v>
       </c>
       <c r="B265" t="s">
-        <v>804</v>
+        <v>821</v>
       </c>
     </row>
     <row r="266">
@@ -5425,7 +5527,7 @@
         <v>265</v>
       </c>
       <c r="B266" t="s">
-        <v>805</v>
+        <v>822</v>
       </c>
     </row>
     <row r="267">
@@ -5433,7 +5535,7 @@
         <v>266</v>
       </c>
       <c r="B267" t="s">
-        <v>806</v>
+        <v>823</v>
       </c>
     </row>
     <row r="268">
@@ -5441,7 +5543,7 @@
         <v>267</v>
       </c>
       <c r="B268" t="s">
-        <v>807</v>
+        <v>824</v>
       </c>
     </row>
     <row r="269">
@@ -5449,7 +5551,7 @@
         <v>268</v>
       </c>
       <c r="B269" t="s">
-        <v>808</v>
+        <v>825</v>
       </c>
     </row>
     <row r="270">
@@ -5457,7 +5559,7 @@
         <v>269</v>
       </c>
       <c r="B270" t="s">
-        <v>809</v>
+        <v>826</v>
       </c>
     </row>
     <row r="271">
@@ -5465,7 +5567,7 @@
         <v>270</v>
       </c>
       <c r="B271" t="s">
-        <v>810</v>
+        <v>827</v>
       </c>
     </row>
     <row r="272">
@@ -5473,7 +5575,7 @@
         <v>271</v>
       </c>
       <c r="B272" t="s">
-        <v>811</v>
+        <v>828</v>
       </c>
     </row>
     <row r="273">
@@ -5481,7 +5583,7 @@
         <v>272</v>
       </c>
       <c r="B273" t="s">
-        <v>812</v>
+        <v>829</v>
       </c>
     </row>
     <row r="274">
@@ -5489,7 +5591,7 @@
         <v>273</v>
       </c>
       <c r="B274" t="s">
-        <v>813</v>
+        <v>830</v>
       </c>
     </row>
     <row r="275">
@@ -5497,7 +5599,7 @@
         <v>274</v>
       </c>
       <c r="B275" t="s">
-        <v>814</v>
+        <v>831</v>
       </c>
     </row>
     <row r="276">
@@ -5505,7 +5607,7 @@
         <v>275</v>
       </c>
       <c r="B276" t="s">
-        <v>815</v>
+        <v>832</v>
       </c>
     </row>
     <row r="277">
@@ -5513,7 +5615,7 @@
         <v>276</v>
       </c>
       <c r="B277" t="s">
-        <v>816</v>
+        <v>833</v>
       </c>
     </row>
     <row r="278">
@@ -5521,7 +5623,7 @@
         <v>277</v>
       </c>
       <c r="B278" t="s">
-        <v>817</v>
+        <v>834</v>
       </c>
     </row>
     <row r="279">
@@ -5529,7 +5631,7 @@
         <v>278</v>
       </c>
       <c r="B279" t="s">
-        <v>818</v>
+        <v>835</v>
       </c>
     </row>
     <row r="280">
@@ -5537,7 +5639,7 @@
         <v>279</v>
       </c>
       <c r="B280" t="s">
-        <v>819</v>
+        <v>836</v>
       </c>
     </row>
     <row r="281">
@@ -5545,7 +5647,7 @@
         <v>280</v>
       </c>
       <c r="B281" t="s">
-        <v>820</v>
+        <v>837</v>
       </c>
     </row>
     <row r="282">
@@ -5553,7 +5655,7 @@
         <v>281</v>
       </c>
       <c r="B282" t="s">
-        <v>821</v>
+        <v>838</v>
       </c>
     </row>
     <row r="283">
@@ -5561,7 +5663,7 @@
         <v>282</v>
       </c>
       <c r="B283" t="s">
-        <v>822</v>
+        <v>839</v>
       </c>
     </row>
     <row r="284">
@@ -5569,7 +5671,7 @@
         <v>283</v>
       </c>
       <c r="B284" t="s">
-        <v>823</v>
+        <v>840</v>
       </c>
     </row>
     <row r="285">
@@ -5577,7 +5679,7 @@
         <v>284</v>
       </c>
       <c r="B285" t="s">
-        <v>824</v>
+        <v>841</v>
       </c>
     </row>
     <row r="286">
@@ -5585,7 +5687,7 @@
         <v>285</v>
       </c>
       <c r="B286" t="s">
-        <v>825</v>
+        <v>842</v>
       </c>
     </row>
     <row r="287">
@@ -5593,7 +5695,7 @@
         <v>286</v>
       </c>
       <c r="B287" t="s">
-        <v>826</v>
+        <v>843</v>
       </c>
     </row>
     <row r="288">
@@ -5601,7 +5703,7 @@
         <v>287</v>
       </c>
       <c r="B288" t="s">
-        <v>827</v>
+        <v>844</v>
       </c>
     </row>
     <row r="289">
@@ -5609,7 +5711,7 @@
         <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>828</v>
+        <v>845</v>
       </c>
     </row>
     <row r="290">
@@ -5617,7 +5719,7 @@
         <v>289</v>
       </c>
       <c r="B290" t="s">
-        <v>829</v>
+        <v>846</v>
       </c>
     </row>
     <row r="291">
@@ -5625,7 +5727,7 @@
         <v>290</v>
       </c>
       <c r="B291" t="s">
-        <v>830</v>
+        <v>847</v>
       </c>
     </row>
     <row r="292">
@@ -5633,7 +5735,7 @@
         <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>831</v>
+        <v>848</v>
       </c>
     </row>
     <row r="293">
@@ -5641,7 +5743,7 @@
         <v>292</v>
       </c>
       <c r="B293" t="s">
-        <v>832</v>
+        <v>849</v>
       </c>
     </row>
     <row r="294">
@@ -5649,7 +5751,7 @@
         <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>833</v>
+        <v>850</v>
       </c>
     </row>
     <row r="295">
@@ -5657,7 +5759,7 @@
         <v>294</v>
       </c>
       <c r="B295" t="s">
-        <v>834</v>
+        <v>851</v>
       </c>
     </row>
     <row r="296">
@@ -5665,7 +5767,7 @@
         <v>295</v>
       </c>
       <c r="B296" t="s">
-        <v>835</v>
+        <v>852</v>
       </c>
     </row>
     <row r="297">
@@ -5673,7 +5775,7 @@
         <v>296</v>
       </c>
       <c r="B297" t="s">
-        <v>836</v>
+        <v>853</v>
       </c>
     </row>
     <row r="298">
@@ -5681,7 +5783,7 @@
         <v>297</v>
       </c>
       <c r="B298" t="s">
-        <v>837</v>
+        <v>854</v>
       </c>
     </row>
     <row r="299">
@@ -5689,7 +5791,7 @@
         <v>298</v>
       </c>
       <c r="B299" t="s">
-        <v>838</v>
+        <v>855</v>
       </c>
     </row>
     <row r="300">
@@ -5697,7 +5799,7 @@
         <v>299</v>
       </c>
       <c r="B300" t="s">
-        <v>839</v>
+        <v>856</v>
       </c>
     </row>
     <row r="301">
@@ -5705,7 +5807,7 @@
         <v>300</v>
       </c>
       <c r="B301" t="s">
-        <v>840</v>
+        <v>857</v>
       </c>
     </row>
     <row r="302">
@@ -5713,7 +5815,7 @@
         <v>301</v>
       </c>
       <c r="B302" t="s">
-        <v>841</v>
+        <v>858</v>
       </c>
     </row>
     <row r="303">
@@ -5721,7 +5823,7 @@
         <v>302</v>
       </c>
       <c r="B303" t="s">
-        <v>842</v>
+        <v>859</v>
       </c>
     </row>
     <row r="304">
@@ -5729,7 +5831,7 @@
         <v>303</v>
       </c>
       <c r="B304" t="s">
-        <v>843</v>
+        <v>860</v>
       </c>
     </row>
     <row r="305">
@@ -5737,7 +5839,7 @@
         <v>304</v>
       </c>
       <c r="B305" t="s">
-        <v>844</v>
+        <v>861</v>
       </c>
     </row>
     <row r="306">
@@ -5745,7 +5847,7 @@
         <v>305</v>
       </c>
       <c r="B306" t="s">
-        <v>845</v>
+        <v>862</v>
       </c>
     </row>
     <row r="307">
@@ -5753,7 +5855,7 @@
         <v>306</v>
       </c>
       <c r="B307" t="s">
-        <v>846</v>
+        <v>863</v>
       </c>
     </row>
     <row r="308">
@@ -5761,7 +5863,7 @@
         <v>307</v>
       </c>
       <c r="B308" t="s">
-        <v>847</v>
+        <v>864</v>
       </c>
     </row>
     <row r="309">
@@ -5769,7 +5871,7 @@
         <v>308</v>
       </c>
       <c r="B309" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
     </row>
     <row r="310">
@@ -5777,7 +5879,7 @@
         <v>309</v>
       </c>
       <c r="B310" t="s">
-        <v>849</v>
+        <v>866</v>
       </c>
     </row>
     <row r="311">
@@ -5785,7 +5887,7 @@
         <v>310</v>
       </c>
       <c r="B311" t="s">
-        <v>850</v>
+        <v>867</v>
       </c>
     </row>
     <row r="312">
@@ -5793,7 +5895,7 @@
         <v>311</v>
       </c>
       <c r="B312" t="s">
-        <v>851</v>
+        <v>868</v>
       </c>
     </row>
     <row r="313">
@@ -5801,7 +5903,7 @@
         <v>312</v>
       </c>
       <c r="B313" t="s">
-        <v>852</v>
+        <v>869</v>
       </c>
     </row>
     <row r="314">
@@ -5809,7 +5911,7 @@
         <v>313</v>
       </c>
       <c r="B314" t="s">
-        <v>853</v>
+        <v>870</v>
       </c>
     </row>
     <row r="315">
@@ -5817,7 +5919,7 @@
         <v>314</v>
       </c>
       <c r="B315" t="s">
-        <v>854</v>
+        <v>871</v>
       </c>
     </row>
     <row r="316">
@@ -5825,7 +5927,7 @@
         <v>315</v>
       </c>
       <c r="B316" t="s">
-        <v>855</v>
+        <v>872</v>
       </c>
     </row>
     <row r="317">
@@ -5833,7 +5935,7 @@
         <v>316</v>
       </c>
       <c r="B317" t="s">
-        <v>856</v>
+        <v>873</v>
       </c>
     </row>
     <row r="318">
@@ -5841,7 +5943,7 @@
         <v>317</v>
       </c>
       <c r="B318" t="s">
-        <v>857</v>
+        <v>874</v>
       </c>
     </row>
     <row r="319">
@@ -5849,7 +5951,7 @@
         <v>318</v>
       </c>
       <c r="B319" t="s">
-        <v>858</v>
+        <v>875</v>
       </c>
     </row>
     <row r="320">
@@ -5857,7 +5959,7 @@
         <v>319</v>
       </c>
       <c r="B320" t="s">
-        <v>859</v>
+        <v>876</v>
       </c>
     </row>
     <row r="321">
@@ -5865,7 +5967,7 @@
         <v>320</v>
       </c>
       <c r="B321" t="s">
-        <v>860</v>
+        <v>877</v>
       </c>
     </row>
     <row r="322">
@@ -5873,7 +5975,7 @@
         <v>321</v>
       </c>
       <c r="B322" t="s">
-        <v>861</v>
+        <v>878</v>
       </c>
     </row>
     <row r="323">
@@ -5881,7 +5983,7 @@
         <v>322</v>
       </c>
       <c r="B323" t="s">
-        <v>862</v>
+        <v>879</v>
       </c>
     </row>
     <row r="324">
@@ -5889,7 +5991,7 @@
         <v>323</v>
       </c>
       <c r="B324" t="s">
-        <v>863</v>
+        <v>880</v>
       </c>
     </row>
     <row r="325">
@@ -5897,7 +5999,7 @@
         <v>324</v>
       </c>
       <c r="B325" t="s">
-        <v>864</v>
+        <v>881</v>
       </c>
     </row>
     <row r="326">
@@ -5905,7 +6007,7 @@
         <v>325</v>
       </c>
       <c r="B326" t="s">
-        <v>865</v>
+        <v>882</v>
       </c>
     </row>
     <row r="327">
@@ -5913,7 +6015,7 @@
         <v>326</v>
       </c>
       <c r="B327" t="s">
-        <v>866</v>
+        <v>883</v>
       </c>
     </row>
     <row r="328">
@@ -5921,7 +6023,7 @@
         <v>327</v>
       </c>
       <c r="B328" t="s">
-        <v>867</v>
+        <v>884</v>
       </c>
     </row>
     <row r="329">
@@ -5929,7 +6031,7 @@
         <v>328</v>
       </c>
       <c r="B329" t="s">
-        <v>868</v>
+        <v>885</v>
       </c>
     </row>
     <row r="330">
@@ -5937,7 +6039,7 @@
         <v>329</v>
       </c>
       <c r="B330" t="s">
-        <v>869</v>
+        <v>886</v>
       </c>
     </row>
     <row r="331">
@@ -5945,7 +6047,7 @@
         <v>330</v>
       </c>
       <c r="B331" t="s">
-        <v>870</v>
+        <v>887</v>
       </c>
     </row>
     <row r="332">
@@ -5953,7 +6055,7 @@
         <v>331</v>
       </c>
       <c r="B332" t="s">
-        <v>871</v>
+        <v>888</v>
       </c>
     </row>
     <row r="333">
@@ -5961,7 +6063,7 @@
         <v>332</v>
       </c>
       <c r="B333" t="s">
-        <v>872</v>
+        <v>889</v>
       </c>
     </row>
     <row r="334">
@@ -5969,7 +6071,7 @@
         <v>333</v>
       </c>
       <c r="B334" t="s">
-        <v>873</v>
+        <v>890</v>
       </c>
     </row>
     <row r="335">
@@ -5977,7 +6079,7 @@
         <v>334</v>
       </c>
       <c r="B335" t="s">
-        <v>874</v>
+        <v>891</v>
       </c>
     </row>
     <row r="336">
@@ -5985,7 +6087,7 @@
         <v>335</v>
       </c>
       <c r="B336" t="s">
-        <v>875</v>
+        <v>892</v>
       </c>
     </row>
     <row r="337">
@@ -5993,7 +6095,7 @@
         <v>336</v>
       </c>
       <c r="B337" t="s">
-        <v>876</v>
+        <v>893</v>
       </c>
     </row>
     <row r="338">
@@ -6001,7 +6103,7 @@
         <v>337</v>
       </c>
       <c r="B338" t="s">
-        <v>877</v>
+        <v>894</v>
       </c>
     </row>
     <row r="339">
@@ -6009,7 +6111,7 @@
         <v>338</v>
       </c>
       <c r="B339" t="s">
-        <v>878</v>
+        <v>895</v>
       </c>
     </row>
     <row r="340">
@@ -6017,7 +6119,7 @@
         <v>339</v>
       </c>
       <c r="B340" t="s">
-        <v>879</v>
+        <v>896</v>
       </c>
     </row>
     <row r="341">
@@ -6025,7 +6127,7 @@
         <v>340</v>
       </c>
       <c r="B341" t="s">
-        <v>880</v>
+        <v>897</v>
       </c>
     </row>
     <row r="342">
@@ -6033,7 +6135,7 @@
         <v>341</v>
       </c>
       <c r="B342" t="s">
-        <v>881</v>
+        <v>898</v>
       </c>
     </row>
     <row r="343">
@@ -6041,7 +6143,7 @@
         <v>342</v>
       </c>
       <c r="B343" t="s">
-        <v>882</v>
+        <v>899</v>
       </c>
     </row>
     <row r="344">
@@ -6049,7 +6151,7 @@
         <v>343</v>
       </c>
       <c r="B344" t="s">
-        <v>883</v>
+        <v>900</v>
       </c>
     </row>
     <row r="345">
@@ -6057,7 +6159,7 @@
         <v>344</v>
       </c>
       <c r="B345" t="s">
-        <v>884</v>
+        <v>901</v>
       </c>
     </row>
     <row r="346">
@@ -6065,7 +6167,7 @@
         <v>345</v>
       </c>
       <c r="B346" t="s">
-        <v>885</v>
+        <v>902</v>
       </c>
     </row>
     <row r="347">
@@ -6073,7 +6175,7 @@
         <v>346</v>
       </c>
       <c r="B347" t="s">
-        <v>886</v>
+        <v>903</v>
       </c>
     </row>
     <row r="348">
@@ -6081,7 +6183,7 @@
         <v>347</v>
       </c>
       <c r="B348" t="s">
-        <v>887</v>
+        <v>904</v>
       </c>
     </row>
     <row r="349">
@@ -6089,7 +6191,7 @@
         <v>348</v>
       </c>
       <c r="B349" t="s">
-        <v>888</v>
+        <v>905</v>
       </c>
     </row>
     <row r="350">
@@ -6097,7 +6199,7 @@
         <v>349</v>
       </c>
       <c r="B350" t="s">
-        <v>889</v>
+        <v>906</v>
       </c>
     </row>
     <row r="351">
@@ -6105,7 +6207,7 @@
         <v>350</v>
       </c>
       <c r="B351" t="s">
-        <v>890</v>
+        <v>907</v>
       </c>
     </row>
     <row r="352">
@@ -6113,7 +6215,7 @@
         <v>351</v>
       </c>
       <c r="B352" t="s">
-        <v>891</v>
+        <v>908</v>
       </c>
     </row>
     <row r="353">
@@ -6121,7 +6223,7 @@
         <v>352</v>
       </c>
       <c r="B353" t="s">
-        <v>892</v>
+        <v>909</v>
       </c>
     </row>
     <row r="354">
@@ -6129,7 +6231,7 @@
         <v>353</v>
       </c>
       <c r="B354" t="s">
-        <v>893</v>
+        <v>910</v>
       </c>
     </row>
     <row r="355">
@@ -6137,7 +6239,7 @@
         <v>354</v>
       </c>
       <c r="B355" t="s">
-        <v>894</v>
+        <v>911</v>
       </c>
     </row>
     <row r="356">
@@ -6145,7 +6247,7 @@
         <v>355</v>
       </c>
       <c r="B356" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
     </row>
     <row r="357">
@@ -6153,7 +6255,7 @@
         <v>356</v>
       </c>
       <c r="B357" t="s">
-        <v>896</v>
+        <v>913</v>
       </c>
     </row>
     <row r="358">
@@ -6161,7 +6263,7 @@
         <v>357</v>
       </c>
       <c r="B358" t="s">
-        <v>897</v>
+        <v>914</v>
       </c>
     </row>
     <row r="359">
@@ -6169,7 +6271,7 @@
         <v>358</v>
       </c>
       <c r="B359" t="s">
-        <v>898</v>
+        <v>915</v>
       </c>
     </row>
     <row r="360">
@@ -6177,7 +6279,7 @@
         <v>359</v>
       </c>
       <c r="B360" t="s">
-        <v>899</v>
+        <v>916</v>
       </c>
     </row>
     <row r="361">
@@ -6185,7 +6287,7 @@
         <v>360</v>
       </c>
       <c r="B361" t="s">
-        <v>900</v>
+        <v>917</v>
       </c>
     </row>
     <row r="362">
@@ -6193,7 +6295,7 @@
         <v>361</v>
       </c>
       <c r="B362" t="s">
-        <v>901</v>
+        <v>918</v>
       </c>
     </row>
     <row r="363">
@@ -6201,7 +6303,7 @@
         <v>362</v>
       </c>
       <c r="B363" t="s">
-        <v>902</v>
+        <v>919</v>
       </c>
     </row>
     <row r="364">
@@ -6209,7 +6311,7 @@
         <v>363</v>
       </c>
       <c r="B364" t="s">
-        <v>903</v>
+        <v>920</v>
       </c>
     </row>
     <row r="365">
@@ -6217,7 +6319,7 @@
         <v>364</v>
       </c>
       <c r="B365" t="s">
-        <v>904</v>
+        <v>921</v>
       </c>
     </row>
     <row r="366">
@@ -6225,7 +6327,7 @@
         <v>365</v>
       </c>
       <c r="B366" t="s">
-        <v>905</v>
+        <v>922</v>
       </c>
     </row>
     <row r="367">
@@ -6233,7 +6335,7 @@
         <v>366</v>
       </c>
       <c r="B367" t="s">
-        <v>906</v>
+        <v>923</v>
       </c>
     </row>
     <row r="368">
@@ -6241,7 +6343,7 @@
         <v>367</v>
       </c>
       <c r="B368" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
     </row>
     <row r="369">
@@ -6249,7 +6351,7 @@
         <v>368</v>
       </c>
       <c r="B369" t="s">
-        <v>908</v>
+        <v>925</v>
       </c>
     </row>
     <row r="370">
@@ -6257,7 +6359,7 @@
         <v>369</v>
       </c>
       <c r="B370" t="s">
-        <v>909</v>
+        <v>926</v>
       </c>
     </row>
     <row r="371">
@@ -6265,7 +6367,7 @@
         <v>370</v>
       </c>
       <c r="B371" t="s">
-        <v>910</v>
+        <v>927</v>
       </c>
     </row>
     <row r="372">
@@ -6273,7 +6375,7 @@
         <v>371</v>
       </c>
       <c r="B372" t="s">
-        <v>911</v>
+        <v>928</v>
       </c>
     </row>
     <row r="373">
@@ -6281,7 +6383,7 @@
         <v>372</v>
       </c>
       <c r="B373" t="s">
-        <v>912</v>
+        <v>929</v>
       </c>
     </row>
     <row r="374">
@@ -6289,7 +6391,7 @@
         <v>373</v>
       </c>
       <c r="B374" t="s">
-        <v>913</v>
+        <v>930</v>
       </c>
     </row>
     <row r="375">
@@ -6297,7 +6399,7 @@
         <v>374</v>
       </c>
       <c r="B375" t="s">
-        <v>914</v>
+        <v>931</v>
       </c>
     </row>
     <row r="376">
@@ -6305,7 +6407,7 @@
         <v>375</v>
       </c>
       <c r="B376" t="s">
-        <v>915</v>
+        <v>932</v>
       </c>
     </row>
     <row r="377">
@@ -6313,7 +6415,7 @@
         <v>376</v>
       </c>
       <c r="B377" t="s">
-        <v>916</v>
+        <v>933</v>
       </c>
     </row>
     <row r="378">
@@ -6321,7 +6423,7 @@
         <v>377</v>
       </c>
       <c r="B378" t="s">
-        <v>917</v>
+        <v>934</v>
       </c>
     </row>
     <row r="379">
@@ -6329,7 +6431,7 @@
         <v>378</v>
       </c>
       <c r="B379" t="s">
-        <v>918</v>
+        <v>935</v>
       </c>
     </row>
     <row r="380">
@@ -6337,7 +6439,7 @@
         <v>379</v>
       </c>
       <c r="B380" t="s">
-        <v>919</v>
+        <v>936</v>
       </c>
     </row>
     <row r="381">
@@ -6345,7 +6447,7 @@
         <v>380</v>
       </c>
       <c r="B381" t="s">
-        <v>920</v>
+        <v>937</v>
       </c>
     </row>
     <row r="382">
@@ -6353,7 +6455,7 @@
         <v>381</v>
       </c>
       <c r="B382" t="s">
-        <v>921</v>
+        <v>938</v>
       </c>
     </row>
     <row r="383">
@@ -6361,7 +6463,7 @@
         <v>382</v>
       </c>
       <c r="B383" t="s">
-        <v>922</v>
+        <v>939</v>
       </c>
     </row>
     <row r="384">
@@ -6369,7 +6471,7 @@
         <v>383</v>
       </c>
       <c r="B384" t="s">
-        <v>923</v>
+        <v>940</v>
       </c>
     </row>
     <row r="385">
@@ -6377,7 +6479,7 @@
         <v>384</v>
       </c>
       <c r="B385" t="s">
-        <v>924</v>
+        <v>941</v>
       </c>
     </row>
     <row r="386">
@@ -6385,7 +6487,7 @@
         <v>385</v>
       </c>
       <c r="B386" t="s">
-        <v>925</v>
+        <v>942</v>
       </c>
     </row>
     <row r="387">
@@ -6393,7 +6495,7 @@
         <v>386</v>
       </c>
       <c r="B387" t="s">
-        <v>926</v>
+        <v>943</v>
       </c>
     </row>
     <row r="388">
@@ -6401,7 +6503,7 @@
         <v>387</v>
       </c>
       <c r="B388" t="s">
-        <v>927</v>
+        <v>944</v>
       </c>
     </row>
     <row r="389">
@@ -6409,7 +6511,7 @@
         <v>388</v>
       </c>
       <c r="B389" t="s">
-        <v>928</v>
+        <v>945</v>
       </c>
     </row>
     <row r="390">
@@ -6417,7 +6519,7 @@
         <v>389</v>
       </c>
       <c r="B390" t="s">
-        <v>929</v>
+        <v>946</v>
       </c>
     </row>
     <row r="391">
@@ -6425,7 +6527,7 @@
         <v>390</v>
       </c>
       <c r="B391" t="s">
-        <v>930</v>
+        <v>947</v>
       </c>
     </row>
     <row r="392">
@@ -6433,7 +6535,7 @@
         <v>391</v>
       </c>
       <c r="B392" t="s">
-        <v>931</v>
+        <v>948</v>
       </c>
     </row>
     <row r="393">
@@ -6441,7 +6543,7 @@
         <v>392</v>
       </c>
       <c r="B393" t="s">
-        <v>932</v>
+        <v>949</v>
       </c>
     </row>
     <row r="394">
@@ -6449,7 +6551,7 @@
         <v>393</v>
       </c>
       <c r="B394" t="s">
-        <v>933</v>
+        <v>950</v>
       </c>
     </row>
     <row r="395">
@@ -6457,7 +6559,7 @@
         <v>394</v>
       </c>
       <c r="B395" t="s">
-        <v>934</v>
+        <v>951</v>
       </c>
     </row>
     <row r="396">
@@ -6465,7 +6567,7 @@
         <v>395</v>
       </c>
       <c r="B396" t="s">
-        <v>935</v>
+        <v>952</v>
       </c>
     </row>
     <row r="397">
@@ -6473,7 +6575,7 @@
         <v>396</v>
       </c>
       <c r="B397" t="s">
-        <v>936</v>
+        <v>953</v>
       </c>
     </row>
     <row r="398">
@@ -6481,7 +6583,7 @@
         <v>397</v>
       </c>
       <c r="B398" t="s">
-        <v>937</v>
+        <v>954</v>
       </c>
     </row>
     <row r="399">
@@ -6489,7 +6591,7 @@
         <v>398</v>
       </c>
       <c r="B399" t="s">
-        <v>938</v>
+        <v>955</v>
       </c>
     </row>
     <row r="400">
@@ -6497,7 +6599,7 @@
         <v>399</v>
       </c>
       <c r="B400" t="s">
-        <v>939</v>
+        <v>956</v>
       </c>
     </row>
     <row r="401">
@@ -6505,7 +6607,7 @@
         <v>400</v>
       </c>
       <c r="B401" t="s">
-        <v>940</v>
+        <v>957</v>
       </c>
     </row>
     <row r="402">
@@ -6513,7 +6615,7 @@
         <v>401</v>
       </c>
       <c r="B402" t="s">
-        <v>941</v>
+        <v>958</v>
       </c>
     </row>
     <row r="403">
@@ -6521,7 +6623,7 @@
         <v>402</v>
       </c>
       <c r="B403" t="s">
-        <v>942</v>
+        <v>959</v>
       </c>
     </row>
     <row r="404">
@@ -6529,7 +6631,7 @@
         <v>403</v>
       </c>
       <c r="B404" t="s">
-        <v>943</v>
+        <v>960</v>
       </c>
     </row>
     <row r="405">
@@ -6537,7 +6639,7 @@
         <v>404</v>
       </c>
       <c r="B405" t="s">
-        <v>944</v>
+        <v>961</v>
       </c>
     </row>
     <row r="406">
@@ -6545,7 +6647,7 @@
         <v>405</v>
       </c>
       <c r="B406" t="s">
-        <v>945</v>
+        <v>962</v>
       </c>
     </row>
     <row r="407">
@@ -6553,7 +6655,7 @@
         <v>406</v>
       </c>
       <c r="B407" t="s">
-        <v>946</v>
+        <v>963</v>
       </c>
     </row>
     <row r="408">
@@ -6561,7 +6663,7 @@
         <v>407</v>
       </c>
       <c r="B408" t="s">
-        <v>947</v>
+        <v>964</v>
       </c>
     </row>
     <row r="409">
@@ -6569,7 +6671,7 @@
         <v>408</v>
       </c>
       <c r="B409" t="s">
-        <v>948</v>
+        <v>965</v>
       </c>
     </row>
     <row r="410">
@@ -6577,7 +6679,7 @@
         <v>409</v>
       </c>
       <c r="B410" t="s">
-        <v>949</v>
+        <v>966</v>
       </c>
     </row>
     <row r="411">
@@ -6585,7 +6687,7 @@
         <v>410</v>
       </c>
       <c r="B411" t="s">
-        <v>950</v>
+        <v>967</v>
       </c>
     </row>
     <row r="412">
@@ -6593,7 +6695,7 @@
         <v>411</v>
       </c>
       <c r="B412" t="s">
-        <v>951</v>
+        <v>968</v>
       </c>
     </row>
     <row r="413">
@@ -6601,7 +6703,7 @@
         <v>412</v>
       </c>
       <c r="B413" t="s">
-        <v>952</v>
+        <v>969</v>
       </c>
     </row>
     <row r="414">
@@ -6609,7 +6711,7 @@
         <v>413</v>
       </c>
       <c r="B414" t="s">
-        <v>953</v>
+        <v>970</v>
       </c>
     </row>
     <row r="415">
@@ -6617,7 +6719,7 @@
         <v>414</v>
       </c>
       <c r="B415" t="s">
-        <v>954</v>
+        <v>971</v>
       </c>
     </row>
     <row r="416">
@@ -6625,7 +6727,7 @@
         <v>415</v>
       </c>
       <c r="B416" t="s">
-        <v>955</v>
+        <v>972</v>
       </c>
     </row>
     <row r="417">
@@ -6633,7 +6735,7 @@
         <v>416</v>
       </c>
       <c r="B417" t="s">
-        <v>956</v>
+        <v>973</v>
       </c>
     </row>
     <row r="418">
@@ -6641,7 +6743,7 @@
         <v>417</v>
       </c>
       <c r="B418" t="s">
-        <v>957</v>
+        <v>974</v>
       </c>
     </row>
     <row r="419">
@@ -6649,7 +6751,7 @@
         <v>418</v>
       </c>
       <c r="B419" t="s">
-        <v>958</v>
+        <v>975</v>
       </c>
     </row>
     <row r="420">
@@ -6657,7 +6759,7 @@
         <v>419</v>
       </c>
       <c r="B420" t="s">
-        <v>959</v>
+        <v>976</v>
       </c>
     </row>
     <row r="421">
@@ -6665,7 +6767,7 @@
         <v>420</v>
       </c>
       <c r="B421" t="s">
-        <v>960</v>
+        <v>977</v>
       </c>
     </row>
     <row r="422">
@@ -6673,7 +6775,7 @@
         <v>421</v>
       </c>
       <c r="B422" t="s">
-        <v>961</v>
+        <v>978</v>
       </c>
     </row>
     <row r="423">
@@ -6681,7 +6783,7 @@
         <v>422</v>
       </c>
       <c r="B423" t="s">
-        <v>962</v>
+        <v>979</v>
       </c>
     </row>
     <row r="424">
@@ -6689,7 +6791,7 @@
         <v>423</v>
       </c>
       <c r="B424" t="s">
-        <v>963</v>
+        <v>980</v>
       </c>
     </row>
     <row r="425">
@@ -6697,7 +6799,7 @@
         <v>424</v>
       </c>
       <c r="B425" t="s">
-        <v>964</v>
+        <v>981</v>
       </c>
     </row>
     <row r="426">
@@ -6705,7 +6807,7 @@
         <v>425</v>
       </c>
       <c r="B426" t="s">
-        <v>965</v>
+        <v>982</v>
       </c>
     </row>
     <row r="427">
@@ -6713,7 +6815,7 @@
         <v>426</v>
       </c>
       <c r="B427" t="s">
-        <v>966</v>
+        <v>983</v>
       </c>
     </row>
     <row r="428">
@@ -6721,7 +6823,7 @@
         <v>427</v>
       </c>
       <c r="B428" t="s">
-        <v>967</v>
+        <v>984</v>
       </c>
     </row>
     <row r="429">
@@ -6729,7 +6831,7 @@
         <v>428</v>
       </c>
       <c r="B429" t="s">
-        <v>968</v>
+        <v>985</v>
       </c>
     </row>
     <row r="430">
@@ -6737,7 +6839,7 @@
         <v>429</v>
       </c>
       <c r="B430" t="s">
-        <v>969</v>
+        <v>986</v>
       </c>
     </row>
     <row r="431">
@@ -6745,7 +6847,7 @@
         <v>430</v>
       </c>
       <c r="B431" t="s">
-        <v>970</v>
+        <v>987</v>
       </c>
     </row>
     <row r="432">
@@ -6753,7 +6855,7 @@
         <v>431</v>
       </c>
       <c r="B432" t="s">
-        <v>971</v>
+        <v>988</v>
       </c>
     </row>
     <row r="433">
@@ -6761,7 +6863,7 @@
         <v>432</v>
       </c>
       <c r="B433" t="s">
-        <v>972</v>
+        <v>989</v>
       </c>
     </row>
     <row r="434">
@@ -6769,7 +6871,7 @@
         <v>433</v>
       </c>
       <c r="B434" t="s">
-        <v>973</v>
+        <v>990</v>
       </c>
     </row>
     <row r="435">
@@ -6777,7 +6879,7 @@
         <v>434</v>
       </c>
       <c r="B435" t="s">
-        <v>974</v>
+        <v>991</v>
       </c>
     </row>
     <row r="436">
@@ -6785,7 +6887,7 @@
         <v>435</v>
       </c>
       <c r="B436" t="s">
-        <v>975</v>
+        <v>992</v>
       </c>
     </row>
     <row r="437">
@@ -6793,7 +6895,7 @@
         <v>436</v>
       </c>
       <c r="B437" t="s">
-        <v>976</v>
+        <v>993</v>
       </c>
     </row>
     <row r="438">
@@ -6801,7 +6903,7 @@
         <v>437</v>
       </c>
       <c r="B438" t="s">
-        <v>977</v>
+        <v>994</v>
       </c>
     </row>
     <row r="439">
@@ -6809,7 +6911,7 @@
         <v>438</v>
       </c>
       <c r="B439" t="s">
-        <v>978</v>
+        <v>995</v>
       </c>
     </row>
     <row r="440">
@@ -6817,7 +6919,7 @@
         <v>439</v>
       </c>
       <c r="B440" t="s">
-        <v>979</v>
+        <v>996</v>
       </c>
     </row>
     <row r="441">
@@ -6825,7 +6927,7 @@
         <v>440</v>
       </c>
       <c r="B441" t="s">
-        <v>980</v>
+        <v>997</v>
       </c>
     </row>
     <row r="442">
@@ -6833,7 +6935,7 @@
         <v>441</v>
       </c>
       <c r="B442" t="s">
-        <v>981</v>
+        <v>998</v>
       </c>
     </row>
     <row r="443">
@@ -6841,7 +6943,7 @@
         <v>442</v>
       </c>
       <c r="B443" t="s">
-        <v>982</v>
+        <v>999</v>
       </c>
     </row>
     <row r="444">
@@ -6849,7 +6951,7 @@
         <v>443</v>
       </c>
       <c r="B444" t="s">
-        <v>983</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="445">
@@ -6857,7 +6959,7 @@
         <v>444</v>
       </c>
       <c r="B445" t="s">
-        <v>984</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="446">
@@ -6865,7 +6967,7 @@
         <v>445</v>
       </c>
       <c r="B446" t="s">
-        <v>985</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="447">
@@ -6873,7 +6975,7 @@
         <v>446</v>
       </c>
       <c r="B447" t="s">
-        <v>986</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="448">
@@ -6881,7 +6983,7 @@
         <v>447</v>
       </c>
       <c r="B448" t="s">
-        <v>987</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="449">
@@ -6889,7 +6991,7 @@
         <v>448</v>
       </c>
       <c r="B449" t="s">
-        <v>988</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="450">
@@ -6897,7 +6999,7 @@
         <v>449</v>
       </c>
       <c r="B450" t="s">
-        <v>989</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="451">
@@ -6905,7 +7007,7 @@
         <v>450</v>
       </c>
       <c r="B451" t="s">
-        <v>990</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="452">
@@ -6913,7 +7015,7 @@
         <v>451</v>
       </c>
       <c r="B452" t="s">
-        <v>991</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="453">
@@ -6921,7 +7023,7 @@
         <v>452</v>
       </c>
       <c r="B453" t="s">
-        <v>992</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="454">
@@ -6929,7 +7031,7 @@
         <v>453</v>
       </c>
       <c r="B454" t="s">
-        <v>993</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="455">
@@ -6937,7 +7039,7 @@
         <v>454</v>
       </c>
       <c r="B455" t="s">
-        <v>994</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="456">
@@ -6945,7 +7047,7 @@
         <v>455</v>
       </c>
       <c r="B456" t="s">
-        <v>995</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="457">
@@ -6953,7 +7055,7 @@
         <v>456</v>
       </c>
       <c r="B457" t="s">
-        <v>996</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="458">
@@ -6961,7 +7063,7 @@
         <v>457</v>
       </c>
       <c r="B458" t="s">
-        <v>997</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="459">
@@ -6969,7 +7071,7 @@
         <v>458</v>
       </c>
       <c r="B459" t="s">
-        <v>998</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="460">
@@ -6977,7 +7079,7 @@
         <v>459</v>
       </c>
       <c r="B460" t="s">
-        <v>999</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="461">
@@ -6985,7 +7087,7 @@
         <v>460</v>
       </c>
       <c r="B461" t="s">
-        <v>1000</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="462">
@@ -6993,7 +7095,7 @@
         <v>461</v>
       </c>
       <c r="B462" t="s">
-        <v>1001</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="463">
@@ -7001,7 +7103,7 @@
         <v>462</v>
       </c>
       <c r="B463" t="s">
-        <v>1002</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="464">
@@ -7009,7 +7111,7 @@
         <v>463</v>
       </c>
       <c r="B464" t="s">
-        <v>1003</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="465">
@@ -7017,7 +7119,7 @@
         <v>464</v>
       </c>
       <c r="B465" t="s">
-        <v>1004</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="466">
@@ -7025,7 +7127,7 @@
         <v>465</v>
       </c>
       <c r="B466" t="s">
-        <v>1005</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="467">
@@ -7033,7 +7135,7 @@
         <v>466</v>
       </c>
       <c r="B467" t="s">
-        <v>1006</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="468">
@@ -7041,7 +7143,7 @@
         <v>467</v>
       </c>
       <c r="B468" t="s">
-        <v>1007</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="469">
@@ -7049,7 +7151,7 @@
         <v>468</v>
       </c>
       <c r="B469" t="s">
-        <v>1008</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="470">
@@ -7057,7 +7159,7 @@
         <v>469</v>
       </c>
       <c r="B470" t="s">
-        <v>1009</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="471">
@@ -7065,7 +7167,7 @@
         <v>470</v>
       </c>
       <c r="B471" t="s">
-        <v>1010</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="472">
@@ -7073,7 +7175,7 @@
         <v>471</v>
       </c>
       <c r="B472" t="s">
-        <v>1011</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="473">
@@ -7081,7 +7183,7 @@
         <v>472</v>
       </c>
       <c r="B473" t="s">
-        <v>1012</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="474">
@@ -7089,7 +7191,7 @@
         <v>473</v>
       </c>
       <c r="B474" t="s">
-        <v>1013</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="475">
@@ -7097,7 +7199,7 @@
         <v>474</v>
       </c>
       <c r="B475" t="s">
-        <v>1014</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="476">
@@ -7105,7 +7207,7 @@
         <v>475</v>
       </c>
       <c r="B476" t="s">
-        <v>1015</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="477">
@@ -7113,7 +7215,7 @@
         <v>476</v>
       </c>
       <c r="B477" t="s">
-        <v>1016</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="478">
@@ -7121,7 +7223,7 @@
         <v>477</v>
       </c>
       <c r="B478" t="s">
-        <v>1017</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="479">
@@ -7129,7 +7231,7 @@
         <v>478</v>
       </c>
       <c r="B479" t="s">
-        <v>1018</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="480">
@@ -7137,7 +7239,7 @@
         <v>479</v>
       </c>
       <c r="B480" t="s">
-        <v>1019</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="481">
@@ -7145,7 +7247,7 @@
         <v>480</v>
       </c>
       <c r="B481" t="s">
-        <v>1020</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="482">
@@ -7153,7 +7255,7 @@
         <v>481</v>
       </c>
       <c r="B482" t="s">
-        <v>1021</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="483">
@@ -7161,7 +7263,7 @@
         <v>482</v>
       </c>
       <c r="B483" t="s">
-        <v>1022</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="484">
@@ -7169,7 +7271,7 @@
         <v>483</v>
       </c>
       <c r="B484" t="s">
-        <v>1023</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="485">
@@ -7177,7 +7279,7 @@
         <v>484</v>
       </c>
       <c r="B485" t="s">
-        <v>1024</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="486">
@@ -7185,7 +7287,7 @@
         <v>485</v>
       </c>
       <c r="B486" t="s">
-        <v>1025</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="487">
@@ -7193,7 +7295,7 @@
         <v>486</v>
       </c>
       <c r="B487" t="s">
-        <v>1026</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="488">
@@ -7201,7 +7303,7 @@
         <v>487</v>
       </c>
       <c r="B488" t="s">
-        <v>1027</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="489">
@@ -7209,7 +7311,7 @@
         <v>488</v>
       </c>
       <c r="B489" t="s">
-        <v>1028</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="490">
@@ -7217,7 +7319,7 @@
         <v>489</v>
       </c>
       <c r="B490" t="s">
-        <v>1029</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="491">
@@ -7225,7 +7327,7 @@
         <v>490</v>
       </c>
       <c r="B491" t="s">
-        <v>1030</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="492">
@@ -7233,7 +7335,7 @@
         <v>491</v>
       </c>
       <c r="B492" t="s">
-        <v>1031</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="493">
@@ -7241,7 +7343,7 @@
         <v>492</v>
       </c>
       <c r="B493" t="s">
-        <v>1032</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="494">
@@ -7249,7 +7351,7 @@
         <v>493</v>
       </c>
       <c r="B494" t="s">
-        <v>1033</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="495">
@@ -7257,7 +7359,7 @@
         <v>494</v>
       </c>
       <c r="B495" t="s">
-        <v>1034</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="496">
@@ -7265,7 +7367,7 @@
         <v>495</v>
       </c>
       <c r="B496" t="s">
-        <v>1035</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="497">
@@ -7273,7 +7375,7 @@
         <v>496</v>
       </c>
       <c r="B497" t="s">
-        <v>1036</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="498">
@@ -7281,7 +7383,7 @@
         <v>497</v>
       </c>
       <c r="B498" t="s">
-        <v>1037</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="499">
@@ -7289,7 +7391,7 @@
         <v>498</v>
       </c>
       <c r="B499" t="s">
-        <v>1038</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="500">
@@ -7297,7 +7399,7 @@
         <v>499</v>
       </c>
       <c r="B500" t="s">
-        <v>1039</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="501">
@@ -7305,7 +7407,7 @@
         <v>500</v>
       </c>
       <c r="B501" t="s">
-        <v>1040</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="502">
@@ -7313,7 +7415,7 @@
         <v>501</v>
       </c>
       <c r="B502" t="s">
-        <v>1041</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="503">
@@ -7321,7 +7423,7 @@
         <v>502</v>
       </c>
       <c r="B503" t="s">
-        <v>1042</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="504">
@@ -7329,7 +7431,7 @@
         <v>503</v>
       </c>
       <c r="B504" t="s">
-        <v>1043</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="505">
@@ -7337,7 +7439,7 @@
         <v>504</v>
       </c>
       <c r="B505" t="s">
-        <v>1044</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="506">
@@ -7345,7 +7447,7 @@
         <v>505</v>
       </c>
       <c r="B506" t="s">
-        <v>1045</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="507">
@@ -7353,7 +7455,7 @@
         <v>506</v>
       </c>
       <c r="B507" t="s">
-        <v>1046</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="508">
@@ -7361,7 +7463,7 @@
         <v>507</v>
       </c>
       <c r="B508" t="s">
-        <v>1047</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="509">
@@ -7369,7 +7471,7 @@
         <v>508</v>
       </c>
       <c r="B509" t="s">
-        <v>1048</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="510">
@@ -7377,7 +7479,7 @@
         <v>509</v>
       </c>
       <c r="B510" t="s">
-        <v>1049</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="511">
@@ -7385,7 +7487,7 @@
         <v>510</v>
       </c>
       <c r="B511" t="s">
-        <v>1050</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="512">
@@ -7393,7 +7495,7 @@
         <v>511</v>
       </c>
       <c r="B512" t="s">
-        <v>1051</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="513">
@@ -7401,7 +7503,7 @@
         <v>512</v>
       </c>
       <c r="B513" t="s">
-        <v>1052</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="514">
@@ -7409,7 +7511,7 @@
         <v>513</v>
       </c>
       <c r="B514" t="s">
-        <v>1053</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="515">
@@ -7417,7 +7519,7 @@
         <v>514</v>
       </c>
       <c r="B515" t="s">
-        <v>1054</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="516">
@@ -7425,7 +7527,7 @@
         <v>515</v>
       </c>
       <c r="B516" t="s">
-        <v>1055</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="517">
@@ -7433,7 +7535,7 @@
         <v>516</v>
       </c>
       <c r="B517" t="s">
-        <v>1056</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="518">
@@ -7441,7 +7543,7 @@
         <v>517</v>
       </c>
       <c r="B518" t="s">
-        <v>1057</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="519">
@@ -7449,7 +7551,7 @@
         <v>518</v>
       </c>
       <c r="B519" t="s">
-        <v>1058</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="520">
@@ -7457,7 +7559,7 @@
         <v>519</v>
       </c>
       <c r="B520" t="s">
-        <v>1059</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="521">
@@ -7465,7 +7567,7 @@
         <v>520</v>
       </c>
       <c r="B521" t="s">
-        <v>1060</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="522">
@@ -7473,7 +7575,7 @@
         <v>521</v>
       </c>
       <c r="B522" t="s">
-        <v>1061</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="523">
@@ -7481,7 +7583,7 @@
         <v>522</v>
       </c>
       <c r="B523" t="s">
-        <v>1062</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="524">
@@ -7489,7 +7591,7 @@
         <v>523</v>
       </c>
       <c r="B524" t="s">
-        <v>1063</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="525">
@@ -7497,7 +7599,7 @@
         <v>524</v>
       </c>
       <c r="B525" t="s">
-        <v>1064</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="526">
@@ -7505,7 +7607,7 @@
         <v>525</v>
       </c>
       <c r="B526" t="s">
-        <v>1065</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="527">
@@ -7513,7 +7615,7 @@
         <v>526</v>
       </c>
       <c r="B527" t="s">
-        <v>1066</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="528">
@@ -7521,7 +7623,7 @@
         <v>527</v>
       </c>
       <c r="B528" t="s">
-        <v>1067</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="529">
@@ -7529,7 +7631,7 @@
         <v>528</v>
       </c>
       <c r="B529" t="s">
-        <v>1068</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="530">
@@ -7537,7 +7639,7 @@
         <v>529</v>
       </c>
       <c r="B530" t="s">
-        <v>1069</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="531">
@@ -7545,7 +7647,7 @@
         <v>530</v>
       </c>
       <c r="B531" t="s">
-        <v>1070</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="532">
@@ -7553,7 +7655,7 @@
         <v>531</v>
       </c>
       <c r="B532" t="s">
-        <v>1071</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="533">
@@ -7561,7 +7663,7 @@
         <v>532</v>
       </c>
       <c r="B533" t="s">
-        <v>1072</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="534">
@@ -7569,7 +7671,7 @@
         <v>533</v>
       </c>
       <c r="B534" t="s">
-        <v>1073</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="535">
@@ -7577,7 +7679,7 @@
         <v>534</v>
       </c>
       <c r="B535" t="s">
-        <v>1074</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="536">
@@ -7585,7 +7687,7 @@
         <v>535</v>
       </c>
       <c r="B536" t="s">
-        <v>1075</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="537">
@@ -7593,7 +7695,7 @@
         <v>536</v>
       </c>
       <c r="B537" t="s">
-        <v>1076</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="538">
@@ -7601,7 +7703,7 @@
         <v>537</v>
       </c>
       <c r="B538" t="s">
-        <v>1077</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="539">
@@ -7609,7 +7711,7 @@
         <v>538</v>
       </c>
       <c r="B539" t="s">
-        <v>1078</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="540">
@@ -7617,7 +7719,7 @@
         <v>539</v>
       </c>
       <c r="B540" t="s">
-        <v>1079</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="541">
@@ -7625,7 +7727,143 @@
         <v>540</v>
       </c>
       <c r="B541" t="s">
-        <v>1080</v>
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="s">
+        <v>541</v>
+      </c>
+      <c r="B542" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="s">
+        <v>542</v>
+      </c>
+      <c r="B543" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="s">
+        <v>543</v>
+      </c>
+      <c r="B544" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="s">
+        <v>544</v>
+      </c>
+      <c r="B545" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="s">
+        <v>545</v>
+      </c>
+      <c r="B546" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="s">
+        <v>546</v>
+      </c>
+      <c r="B547" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="s">
+        <v>547</v>
+      </c>
+      <c r="B548" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="s">
+        <v>548</v>
+      </c>
+      <c r="B549" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="s">
+        <v>549</v>
+      </c>
+      <c r="B550" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="s">
+        <v>550</v>
+      </c>
+      <c r="B551" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="s">
+        <v>551</v>
+      </c>
+      <c r="B552" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="s">
+        <v>552</v>
+      </c>
+      <c r="B553" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="s">
+        <v>553</v>
+      </c>
+      <c r="B554" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="s">
+        <v>554</v>
+      </c>
+      <c r="B555" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="s">
+        <v>555</v>
+      </c>
+      <c r="B556" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="s">
+        <v>556</v>
+      </c>
+      <c r="B557" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="s">
+        <v>557</v>
+      </c>
+      <c r="B558" t="s">
+        <v>1114</v>
       </c>
     </row>
   </sheetData>
